--- a/suivi/classeur-de-suivi.xlsx
+++ b/suivi/classeur-de-suivi.xlsx
@@ -173,12 +173,12 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1021,7 +1021,7 @@
           <t>Coder le jeu XO termine et le tester sur la machine de demo (c'est le WOW : sans lui, la seance perd son moteur)</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>Capitaine</t>
         </is>
@@ -1045,7 +1045,7 @@
           <t>Installer Python + Thonny sur TOUTES les machines, meme version</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Les deux</t>
         </is>
@@ -1069,7 +1069,7 @@
           <t>Lancer un programme sur CHAQUE poste pour verifier (lancer demo/verifier_le_jeu.py)</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>Les deux</t>
         </is>
@@ -1093,7 +1093,7 @@
           <t>Creer le dossier GEEKS sur le Bureau de chaque poste (cle-usb/installer_sur_ce_poste.py)</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Mecanicien</t>
         </is>
@@ -1117,7 +1117,7 @@
           <t>Regler la police de Thonny en taille 18 sur tous les postes et sur la machine de projection</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Mecanicien</t>
         </is>
@@ -1141,7 +1141,7 @@
           <t>Preparer la cle USB maitresse (outils/preparer_la_cle.py)</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>Capitaine</t>
         </is>
@@ -1165,7 +1165,7 @@
           <t>Verifier le videoprojecteur AVEC le cable et la machine du jour</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Capitaine</t>
         </is>
@@ -1189,7 +1189,7 @@
           <t>Reserver la salle 30 min avant (Sas Permis Machine)</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Les deux</t>
         </is>
@@ -1213,7 +1213,7 @@
           <t>Imprimer 01 - Cartes de signalisation (1 page par binome, papier epais)</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Mecanicien</t>
         </is>
@@ -1237,7 +1237,7 @@
           <t>Imprimer 02 - Affiche 3 avant moi (A3)</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Mecanicien</t>
         </is>
@@ -1261,7 +1261,7 @@
           <t>Imprimer 03 - Affiche Contrat des Geeks (A3)</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>Mecanicien</t>
         </is>
@@ -1285,7 +1285,7 @@
           <t>Imprimer 04 - Affiche Dictionnaire des erreurs (A3)</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>Mecanicien</t>
         </is>
@@ -1309,7 +1309,7 @@
           <t>Imprimer 05 - Mur de Mission (A3 paysage)</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Mecanicien</t>
         </is>
@@ -1333,7 +1333,7 @@
           <t>Imprimer 06 - Fiche memo eleve (1 par binome)</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Mecanicien</t>
         </is>
@@ -1357,7 +1357,7 @@
           <t>Imprimer 07 - Cartes-missions station 1 (6 ex.)</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Capitaine</t>
         </is>
@@ -1381,7 +1381,7 @@
           <t>Imprimer 08 - Enigmes station 2 (6 ex., recto-verso)</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>Capitaine</t>
         </is>
@@ -1405,7 +1405,7 @@
           <t>Imprimer 09 - Ma fiche de Geek (1 par eleve)</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>Capitaine</t>
         </is>
@@ -1426,10 +1426,10 @@
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>Imprimer 10 - Grille d'observation + corriges (2 ex.)</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
+          <t>Imprimer 10 - Grille d'observation + corriges (2 ex., A4 paysage, 3 pages)</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Capitaine</t>
         </is>
@@ -1453,7 +1453,7 @@
           <t>Imprimer 11 - Etiquettes prenoms (3 pages) et les decouper</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>Mecanicien</t>
         </is>
@@ -1477,7 +1477,7 @@
           <t>Imprimer 12 - Affiche Aider sans faire a la place (2 ex.)</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Capitaine</t>
         </is>
@@ -1501,7 +1501,7 @@
           <t>Imprimer 13 - Cartes des pistes Rouge et Noire (1 par binome)</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Mecanicien</t>
         </is>
@@ -1522,10 +1522,10 @@
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>Imprimer MON-SCRIPT d'animation (7 pages, agrafe)</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
+          <t>Imprimer MON-SCRIPT d'animation (14 pages A4, agrafe)</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>Capitaine</t>
         </is>
@@ -1549,7 +1549,7 @@
           <t>Acheter / preparer : post-it (2 par eleve), feutres, gommettes-badges, ruban adhesif</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>Mecanicien</t>
         </is>
@@ -1573,7 +1573,7 @@
           <t>Preparer la boite a post-it et le minuteur visible</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>Mecanicien</t>
         </is>
@@ -1597,7 +1597,7 @@
           <t>Relire la fiche de seance en entier, a deux</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>Les deux</t>
         </is>
@@ -1621,7 +1621,7 @@
           <t>Arriver 30 min avant. Machines allumees, Thonny ouvert, dossier GEEKS visible</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>Les deux</t>
         </is>
@@ -1645,7 +1645,7 @@
           <t>Lancer le jeu fini et le REDUIRE (ne jamais chercher le fichier devant la classe)</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>Capitaine</t>
         </is>
@@ -1669,7 +1669,7 @@
           <t>Machine de reserve allumee au fond de la salle</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>Mecanicien</t>
         </is>
@@ -1693,7 +1693,7 @@
           <t>Afficher les 4 affiches + le Mur de Mission</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>Mecanicien</t>
         </is>
@@ -1717,7 +1717,7 @@
           <t>Poser sur chaque poste : fiche memo, 4 cartes, carte des pistes, 2 post-it par eleve</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>Les deux</t>
         </is>
@@ -1741,7 +1741,7 @@
           <t>Verifier que mon_xo/jeu.py est bien present et s'ouvre sur chaque poste</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>Mecanicien</t>
         </is>
@@ -1765,7 +1765,7 @@
           <t>Decider et dire a voix haute : qui est Capitaine, qui est Mecanicien</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="13" t="inlineStr">
         <is>
           <t>Les deux</t>
         </is>
@@ -1789,7 +1789,7 @@
           <t>Choisir le signal de silence et s'accorder dessus</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>Les deux</t>
         </is>
@@ -1813,7 +1813,7 @@
           <t>A 104 min : verifier qu'AUCUN ecran n'est reste vide. Priorite absolue.</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>Les deux</t>
         </is>
@@ -1837,7 +1837,7 @@
           <t>Sauvegarder le travail de chaque binome sur la cle (4-SAUVEGARDES-ELEVES/S01)</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>Mecanicien</t>
         </is>
@@ -1861,7 +1861,7 @@
           <t>Finaliser le code officiel S01 et le copier sur la cle</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C39" s="13" t="inlineStr">
         <is>
           <t>Capitaine</t>
         </is>
@@ -1885,7 +1885,7 @@
           <t>Remplir 03_Presence et 04_Suivi-seances</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>Mecanicien</t>
         </is>
@@ -1909,7 +1909,7 @@
           <t>Saisir le diagnostic dans 02_Diagnostic</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>Mecanicien</t>
         </is>
@@ -1933,7 +1933,7 @@
           <t>Trier les post-it en 2 tas et noter la difficulte la plus citee</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="13" t="inlineStr">
         <is>
           <t>Les deux</t>
         </is>
@@ -1957,7 +1957,7 @@
           <t>Etablir la liste des 10 minutes pour la seance 2</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C43" s="13" t="inlineStr">
         <is>
           <t>Les deux</t>
         </is>
@@ -1981,7 +1981,7 @@
           <t>Envoyer le message aux familles</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>Capitaine</t>
         </is>
@@ -2005,7 +2005,7 @@
           <t>Repondre aux 3 questions de la revue (onglet 10)</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C45" s="13" t="inlineStr">
         <is>
           <t>Les deux</t>
         </is>
@@ -2029,7 +2029,7 @@
           <t>Echanger les roles pour la seance 2</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
         <is>
           <t>Les deux</t>
         </is>
@@ -2595,7 +2595,7 @@
           <t>Cartes de signalisation (1 page / binome)</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="13" t="n">
         <v>10</v>
       </c>
       <c r="D4" s="14" t="n"/>
@@ -2623,7 +2623,7 @@
           <t>Affiches A3 (3 avant moi, Contrat, Erreurs)</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="13" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="14" t="n"/>
@@ -2651,7 +2651,7 @@
           <t>Mur de Mission A3 paysage</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="14" t="n"/>
@@ -2679,7 +2679,7 @@
           <t>Fiche memo eleve</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="13" t="n">
         <v>10</v>
       </c>
       <c r="D7" s="14" t="n"/>
@@ -2707,7 +2707,7 @@
           <t>Cartes des pistes Rouge/Noire</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="13" t="n">
         <v>10</v>
       </c>
       <c r="D8" s="14" t="n"/>
@@ -2735,7 +2735,7 @@
           <t>Station 1 - cartes-missions</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="13" t="n">
         <v>6</v>
       </c>
       <c r="D9" s="14" t="n"/>
@@ -2763,7 +2763,7 @@
           <t>Station 2 - enigmes (recto-verso)</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C10" s="13" t="n">
         <v>6</v>
       </c>
       <c r="D10" s="14" t="n"/>
@@ -2787,7 +2787,7 @@
           <t>Station 3 - Ma fiche de Geek</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="13" t="n">
         <v>20</v>
       </c>
       <c r="D11" s="14" t="n"/>
@@ -2815,7 +2815,7 @@
           <t>Grille d'observation + corriges</t>
         </is>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="13" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="14" t="n"/>
@@ -2828,7 +2828,7 @@
       <c r="G12" s="14" t="n"/>
       <c r="H12" s="25" t="inlineStr">
         <is>
-          <t>PAGE 2 = CORRIGES, ne pas laisser trainer</t>
+          <t>PAGES 2-3 = CORRIGES, ne pas laisser trainer</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
           <t>Etiquettes prenoms</t>
         </is>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="13" t="n">
         <v>3</v>
       </c>
       <c r="D13" s="14" t="n"/>
@@ -2871,7 +2871,7 @@
           <t>Affiche Aider sans faire a la place</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C14" s="13" t="n">
         <v>2</v>
       </c>
       <c r="D14" s="14" t="n"/>
@@ -2899,7 +2899,7 @@
           <t>MON-SCRIPT d'animation</t>
         </is>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="14" t="n"/>
@@ -2912,7 +2912,7 @@
       <c r="G15" s="14" t="n"/>
       <c r="H15" s="25" t="inlineStr">
         <is>
-          <t>7 pages, agrafe</t>
+          <t>14 pages, agrafe</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2927,7 @@
           <t>Post-it</t>
         </is>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C16" s="13" t="n">
         <v>2</v>
       </c>
       <c r="D16" s="14" t="n"/>
@@ -2955,7 +2955,7 @@
           <t>Feutres noirs pointe large</t>
         </is>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C17" s="13" t="n">
         <v>4</v>
       </c>
       <c r="D17" s="14" t="n"/>
@@ -2983,7 +2983,7 @@
           <t>Gommettes de couleur (= badges)</t>
         </is>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C18" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="14" t="n"/>
@@ -3011,7 +3011,7 @@
           <t>Ruban adhesif / porte-badges</t>
         </is>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="14" t="n"/>
@@ -3035,7 +3035,7 @@
           <t>Boite ou bocal pour les post-it de sortie</t>
         </is>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C20" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="14" t="n"/>
@@ -3059,7 +3059,7 @@
           <t>Minuteur visible de toute la salle</t>
         </is>
       </c>
-      <c r="C21" s="8" t="n">
+      <c r="C21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="14" t="n"/>
@@ -3087,7 +3087,7 @@
           <t>Cle USB</t>
         </is>
       </c>
-      <c r="C22" s="8" t="n">
+      <c r="C22" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="14" t="n"/>
@@ -3115,7 +3115,7 @@
           <t>Videoprojecteur teste avec le cable du jour</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n">
+      <c r="C23" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="14" t="n"/>
@@ -3139,7 +3139,7 @@
           <t>Machine de reserve allumee au fond</t>
         </is>
       </c>
-      <c r="C24" s="8" t="n">
+      <c r="C24" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="14" t="n"/>
@@ -3163,7 +3163,7 @@
           <t>Mur libre pour les affiches</t>
         </is>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="14" t="n"/>
@@ -3187,7 +3187,7 @@
           <t>Disposition : tous les ecrans visibles depuis le fond</t>
         </is>
       </c>
-      <c r="C26" s="8" t="n">
+      <c r="C26" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="14" t="n"/>
@@ -3215,7 +3215,7 @@
           <t>Python 3 installe (meme version partout)</t>
         </is>
       </c>
-      <c r="C27" s="8" t="n"/>
+      <c r="C27" s="13" t="n"/>
       <c r="D27" s="14" t="n"/>
       <c r="E27" s="14" t="n"/>
       <c r="F27" s="14" t="inlineStr">
@@ -3241,7 +3241,7 @@
           <t>Thonny installe</t>
         </is>
       </c>
-      <c r="C28" s="8" t="n"/>
+      <c r="C28" s="13" t="n"/>
       <c r="D28" s="14" t="n"/>
       <c r="E28" s="14" t="n"/>
       <c r="F28" s="14" t="inlineStr">
@@ -3267,7 +3267,7 @@
           <t>Dossier GEEKS cree sur chaque Bureau</t>
         </is>
       </c>
-      <c r="C29" s="8" t="n"/>
+      <c r="C29" s="13" t="n"/>
       <c r="D29" s="14" t="n"/>
       <c r="E29" s="14" t="n"/>
       <c r="F29" s="14" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Eleves inscrits</t>
         </is>
@@ -3383,7 +3383,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>dont Jerusalem Geeks (9-12)</t>
         </is>
@@ -3396,7 +3396,7 @@
       <c r="D7" s="35" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>dont Jeremiah Geeks (12-18)</t>
         </is>
@@ -3409,7 +3409,7 @@
       <c r="D8" s="35" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Binomes a prevoir (arrondi au superieur)</t>
         </is>
@@ -3430,7 +3430,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Eleves actifs</t>
         </is>
@@ -3450,7 +3450,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>P0 Decouvreur - ne maitrise pas la machine</t>
         </is>
@@ -3467,7 +3467,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>P1 Initie - sait s'en servir, n'a jamais code</t>
         </is>
@@ -3484,7 +3484,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>P2 Autonome</t>
         </is>
@@ -3501,7 +3501,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>P3 Avance - sait deja coder</t>
         </is>
@@ -3518,7 +3518,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Eleves diagnostiques</t>
         </is>
@@ -3545,7 +3545,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Taux de presence moyen</t>
         </is>
@@ -3566,7 +3566,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Eleves sur la LISTE DES 10 MINUTES</t>
         </is>
@@ -3587,7 +3587,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>Briques produites (toutes seances, tous eleves)</t>
         </is>
@@ -3600,7 +3600,7 @@
       <c r="D22" s="35" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Seances manquees sans production</t>
         </is>
@@ -3617,7 +3617,7 @@
       <c r="D23" s="35" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Observations sans action realisee</t>
         </is>
@@ -3638,7 +3638,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Badges distribues</t>
         </is>
@@ -3662,7 +3662,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>Eleves SANS ordinateur a la maison</t>
         </is>
@@ -3679,7 +3679,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>Eleves sans internet a la maison</t>
         </is>
@@ -3696,7 +3696,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>Eleves n'ayant jamais code</t>
         </is>
@@ -3709,7 +3709,7 @@
       <c r="D30" s="35" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>Passeport Machine : moyenne des gestes acquis</t>
         </is>
@@ -3730,7 +3730,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Autorisations photo obtenues</t>
         </is>
@@ -3754,7 +3754,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>Taches de preparation restantes</t>
         </is>
@@ -3775,7 +3775,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>Taches faites</t>
         </is>
@@ -3788,7 +3788,7 @@
       <c r="D36" s="35" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>Avancement de la preparation</t>
         </is>
@@ -3805,7 +3805,7 @@
       <c r="D37" s="35" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>Materiel non encore pret</t>
         </is>
@@ -3986,587 +3986,587 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Jerusalem Geeks</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>P0 Decouvreur</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>P present</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>V-Bleue</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>abandonne</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>Novice</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>Reussite</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>Actif</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t>J-7</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>A faire</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="L4" s="13" t="inlineStr">
         <is>
           <t>Mere</t>
         </is>
       </c>
-      <c r="M4" s="8" t="inlineStr">
+      <c r="M4" s="13" t="inlineStr">
         <is>
           <t>Oui a moi</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="O4" s="13" t="inlineStr">
         <is>
           <t>Jamais</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="P4" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="Q4" s="13" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Jeremiah Geeks</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>P1 Initie</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>R retard</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>V-Rouge</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>demande</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>Apprenti Codeur</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>Difficulte</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>En pause</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t>J-1</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="K5" s="13" t="inlineStr">
         <is>
           <t>En cours</t>
         </is>
       </c>
-      <c r="L5" s="8" t="inlineStr">
+      <c r="L5" s="13" t="inlineStr">
         <is>
           <t>Pere</t>
         </is>
       </c>
-      <c r="M5" s="8" t="inlineStr">
+      <c r="M5" s="13" t="inlineStr">
         <is>
           <t>Oui partage</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="N5" s="13" t="inlineStr">
         <is>
           <t>Parfois</t>
         </is>
       </c>
-      <c r="O5" s="8" t="inlineStr">
+      <c r="O5" s="13" t="inlineStr">
         <is>
           <t>Scratch</t>
         </is>
       </c>
-      <c r="P5" s="8" t="inlineStr">
+      <c r="P5" s="13" t="inlineStr">
         <is>
           <t>Un peu</t>
         </is>
       </c>
-      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="Q5" s="13" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="A6" s="13" t="n"/>
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>P2 Autonome</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>E excuse</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>V-Noire</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>persevere</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>Codeur</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>Comportement</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>Parti</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t>Jour J</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t>Fait</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="L6" s="13" t="inlineStr">
         <is>
           <t>Tuteur/Tutrice</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="13" t="inlineStr">
         <is>
           <t>Python</t>
         </is>
       </c>
-      <c r="P6" s="8" t="inlineStr">
+      <c r="P6" s="13" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="n"/>
+      <c r="Q6" s="13" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n"/>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="A7" s="13" t="n"/>
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>P3 Avance</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>A absent</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Partielle</t>
         </is>
       </c>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>aide les autres</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>Ingenieur</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>Famille</t>
         </is>
       </c>
-      <c r="I7" s="8" t="n"/>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t>Pendant</t>
         </is>
       </c>
-      <c r="K7" s="8" t="n"/>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="K7" s="13" t="n"/>
+      <c r="L7" s="13" t="inlineStr">
         <is>
           <t>Grand-parent</t>
         </is>
       </c>
-      <c r="M7" s="8" t="n"/>
-      <c r="N7" s="8" t="n"/>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="M7" s="13" t="n"/>
+      <c r="N7" s="13" t="n"/>
+      <c r="O7" s="13" t="inlineStr">
         <is>
           <t>Autre</t>
         </is>
       </c>
-      <c r="P7" s="8" t="n"/>
-      <c r="Q7" s="8" t="n"/>
+      <c r="P7" s="13" t="n"/>
+      <c r="Q7" s="13" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n"/>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="A8" s="13" t="n"/>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Rien</t>
         </is>
       </c>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>Architecte</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>Sante</t>
         </is>
       </c>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="I8" s="13" t="n"/>
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t>Apres</t>
         </is>
       </c>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="8" t="inlineStr">
+      <c r="K8" s="13" t="n"/>
+      <c r="L8" s="13" t="inlineStr">
         <is>
           <t>Frere/Soeur</t>
         </is>
       </c>
-      <c r="M8" s="8" t="n"/>
-      <c r="N8" s="8" t="n"/>
-      <c r="O8" s="8" t="n"/>
-      <c r="P8" s="8" t="n"/>
-      <c r="Q8" s="8" t="n"/>
+      <c r="M8" s="13" t="n"/>
+      <c r="N8" s="13" t="n"/>
+      <c r="O8" s="13" t="n"/>
+      <c r="P8" s="13" t="n"/>
+      <c r="Q8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n"/>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="A9" s="13" t="n"/>
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>Maitre Geek</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>Materiel</t>
         </is>
       </c>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="8" t="n"/>
-      <c r="K9" s="8" t="n"/>
-      <c r="L9" s="8" t="inlineStr">
+      <c r="I9" s="13" t="n"/>
+      <c r="J9" s="13" t="n"/>
+      <c r="K9" s="13" t="n"/>
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t>Autre</t>
         </is>
       </c>
-      <c r="M9" s="8" t="n"/>
-      <c r="N9" s="8" t="n"/>
-      <c r="O9" s="8" t="n"/>
-      <c r="P9" s="8" t="n"/>
-      <c r="Q9" s="8" t="n"/>
+      <c r="M9" s="13" t="n"/>
+      <c r="N9" s="13" t="n"/>
+      <c r="O9" s="13" t="n"/>
+      <c r="P9" s="13" t="n"/>
+      <c r="Q9" s="13" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n"/>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t>Autre</t>
         </is>
       </c>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
-      <c r="K10" s="8" t="n"/>
-      <c r="L10" s="8" t="n"/>
-      <c r="M10" s="8" t="n"/>
-      <c r="N10" s="8" t="n"/>
-      <c r="O10" s="8" t="n"/>
-      <c r="P10" s="8" t="n"/>
-      <c r="Q10" s="8" t="n"/>
+      <c r="I10" s="13" t="n"/>
+      <c r="J10" s="13" t="n"/>
+      <c r="K10" s="13" t="n"/>
+      <c r="L10" s="13" t="n"/>
+      <c r="M10" s="13" t="n"/>
+      <c r="N10" s="13" t="n"/>
+      <c r="O10" s="13" t="n"/>
+      <c r="P10" s="13" t="n"/>
+      <c r="Q10" s="13" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n"/>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="8" t="n"/>
-      <c r="J11" s="8" t="n"/>
-      <c r="K11" s="8" t="n"/>
-      <c r="L11" s="8" t="n"/>
-      <c r="M11" s="8" t="n"/>
-      <c r="N11" s="8" t="n"/>
-      <c r="O11" s="8" t="n"/>
-      <c r="P11" s="8" t="n"/>
-      <c r="Q11" s="8" t="n"/>
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="13" t="n"/>
+      <c r="I11" s="13" t="n"/>
+      <c r="J11" s="13" t="n"/>
+      <c r="K11" s="13" t="n"/>
+      <c r="L11" s="13" t="n"/>
+      <c r="M11" s="13" t="n"/>
+      <c r="N11" s="13" t="n"/>
+      <c r="O11" s="13" t="n"/>
+      <c r="P11" s="13" t="n"/>
+      <c r="Q11" s="13" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n"/>
-      <c r="K12" s="8" t="n"/>
-      <c r="L12" s="8" t="n"/>
-      <c r="M12" s="8" t="n"/>
-      <c r="N12" s="8" t="n"/>
-      <c r="O12" s="8" t="n"/>
-      <c r="P12" s="8" t="n"/>
-      <c r="Q12" s="8" t="n"/>
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="13" t="n"/>
+      <c r="I12" s="13" t="n"/>
+      <c r="J12" s="13" t="n"/>
+      <c r="K12" s="13" t="n"/>
+      <c r="L12" s="13" t="n"/>
+      <c r="M12" s="13" t="n"/>
+      <c r="N12" s="13" t="n"/>
+      <c r="O12" s="13" t="n"/>
+      <c r="P12" s="13" t="n"/>
+      <c r="Q12" s="13" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n"/>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="8" t="n"/>
-      <c r="J13" s="8" t="n"/>
-      <c r="K13" s="8" t="n"/>
-      <c r="L13" s="8" t="n"/>
-      <c r="M13" s="8" t="n"/>
-      <c r="N13" s="8" t="n"/>
-      <c r="O13" s="8" t="n"/>
-      <c r="P13" s="8" t="n"/>
-      <c r="Q13" s="8" t="n"/>
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="13" t="n"/>
+      <c r="I13" s="13" t="n"/>
+      <c r="J13" s="13" t="n"/>
+      <c r="K13" s="13" t="n"/>
+      <c r="L13" s="13" t="n"/>
+      <c r="M13" s="13" t="n"/>
+      <c r="N13" s="13" t="n"/>
+      <c r="O13" s="13" t="n"/>
+      <c r="P13" s="13" t="n"/>
+      <c r="Q13" s="13" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n"/>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n"/>
-      <c r="K14" s="8" t="n"/>
-      <c r="L14" s="8" t="n"/>
-      <c r="M14" s="8" t="n"/>
-      <c r="N14" s="8" t="n"/>
-      <c r="O14" s="8" t="n"/>
-      <c r="P14" s="8" t="n"/>
-      <c r="Q14" s="8" t="n"/>
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="13" t="n"/>
+      <c r="I14" s="13" t="n"/>
+      <c r="J14" s="13" t="n"/>
+      <c r="K14" s="13" t="n"/>
+      <c r="L14" s="13" t="n"/>
+      <c r="M14" s="13" t="n"/>
+      <c r="N14" s="13" t="n"/>
+      <c r="O14" s="13" t="n"/>
+      <c r="P14" s="13" t="n"/>
+      <c r="Q14" s="13" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n"/>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
-      <c r="J15" s="8" t="n"/>
-      <c r="K15" s="8" t="n"/>
-      <c r="L15" s="8" t="n"/>
-      <c r="M15" s="8" t="n"/>
-      <c r="N15" s="8" t="n"/>
-      <c r="O15" s="8" t="n"/>
-      <c r="P15" s="8" t="n"/>
-      <c r="Q15" s="8" t="n"/>
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="13" t="n"/>
+      <c r="I15" s="13" t="n"/>
+      <c r="J15" s="13" t="n"/>
+      <c r="K15" s="13" t="n"/>
+      <c r="L15" s="13" t="n"/>
+      <c r="M15" s="13" t="n"/>
+      <c r="N15" s="13" t="n"/>
+      <c r="O15" s="13" t="n"/>
+      <c r="P15" s="13" t="n"/>
+      <c r="Q15" s="13" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n"/>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n"/>
-      <c r="K16" s="8" t="n"/>
-      <c r="L16" s="8" t="n"/>
-      <c r="M16" s="8" t="n"/>
-      <c r="N16" s="8" t="n"/>
-      <c r="O16" s="8" t="n"/>
-      <c r="P16" s="8" t="n"/>
-      <c r="Q16" s="8" t="n"/>
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="13" t="n"/>
+      <c r="I16" s="13" t="n"/>
+      <c r="J16" s="13" t="n"/>
+      <c r="K16" s="13" t="n"/>
+      <c r="L16" s="13" t="n"/>
+      <c r="M16" s="13" t="n"/>
+      <c r="N16" s="13" t="n"/>
+      <c r="O16" s="13" t="n"/>
+      <c r="P16" s="13" t="n"/>
+      <c r="Q16" s="13" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n"/>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
-      <c r="J17" s="8" t="n"/>
-      <c r="K17" s="8" t="n"/>
-      <c r="L17" s="8" t="n"/>
-      <c r="M17" s="8" t="n"/>
-      <c r="N17" s="8" t="n"/>
-      <c r="O17" s="8" t="n"/>
-      <c r="P17" s="8" t="n"/>
-      <c r="Q17" s="8" t="n"/>
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="13" t="n"/>
+      <c r="I17" s="13" t="n"/>
+      <c r="J17" s="13" t="n"/>
+      <c r="K17" s="13" t="n"/>
+      <c r="L17" s="13" t="n"/>
+      <c r="M17" s="13" t="n"/>
+      <c r="N17" s="13" t="n"/>
+      <c r="O17" s="13" t="n"/>
+      <c r="P17" s="13" t="n"/>
+      <c r="Q17" s="13" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
-      <c r="K18" s="8" t="n"/>
-      <c r="L18" s="8" t="n"/>
-      <c r="M18" s="8" t="n"/>
-      <c r="N18" s="8" t="n"/>
-      <c r="O18" s="8" t="n"/>
-      <c r="P18" s="8" t="n"/>
-      <c r="Q18" s="8" t="n"/>
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="13" t="n"/>
+      <c r="I18" s="13" t="n"/>
+      <c r="J18" s="13" t="n"/>
+      <c r="K18" s="13" t="n"/>
+      <c r="L18" s="13" t="n"/>
+      <c r="M18" s="13" t="n"/>
+      <c r="N18" s="13" t="n"/>
+      <c r="O18" s="13" t="n"/>
+      <c r="P18" s="13" t="n"/>
+      <c r="Q18" s="13" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n"/>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
-      <c r="L19" s="8" t="n"/>
-      <c r="M19" s="8" t="n"/>
-      <c r="N19" s="8" t="n"/>
-      <c r="O19" s="8" t="n"/>
-      <c r="P19" s="8" t="n"/>
-      <c r="Q19" s="8" t="n"/>
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="13" t="n"/>
+      <c r="I19" s="13" t="n"/>
+      <c r="J19" s="13" t="n"/>
+      <c r="K19" s="13" t="n"/>
+      <c r="L19" s="13" t="n"/>
+      <c r="M19" s="13" t="n"/>
+      <c r="N19" s="13" t="n"/>
+      <c r="O19" s="13" t="n"/>
+      <c r="P19" s="13" t="n"/>
+      <c r="Q19" s="13" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n"/>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n"/>
-      <c r="K20" s="8" t="n"/>
-      <c r="L20" s="8" t="n"/>
-      <c r="M20" s="8" t="n"/>
-      <c r="N20" s="8" t="n"/>
-      <c r="O20" s="8" t="n"/>
-      <c r="P20" s="8" t="n"/>
-      <c r="Q20" s="8" t="n"/>
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="13" t="n"/>
+      <c r="H20" s="13" t="n"/>
+      <c r="I20" s="13" t="n"/>
+      <c r="J20" s="13" t="n"/>
+      <c r="K20" s="13" t="n"/>
+      <c r="L20" s="13" t="n"/>
+      <c r="M20" s="13" t="n"/>
+      <c r="N20" s="13" t="n"/>
+      <c r="O20" s="13" t="n"/>
+      <c r="P20" s="13" t="n"/>
+      <c r="Q20" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4773,1150 +4773,1150 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n">
+      <c r="A4" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>KOUASSI</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Awa</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Jerusalem Geeks</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>12/03/2015</t>
         </is>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <f>IF(E4="","",DATEDIF(E4,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>EPP Riviera</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>CM2</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr"/>
-      <c r="J4" s="9" t="inlineStr"/>
-      <c r="K4" s="10" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr"/>
+      <c r="J4" s="8" t="inlineStr"/>
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>KOUASSI Marie</t>
         </is>
       </c>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Mere</t>
         </is>
       </c>
-      <c r="M4" s="10" t="inlineStr">
+      <c r="M4" s="9" t="inlineStr">
         <is>
           <t>07 00 00 00 00</t>
         </is>
       </c>
-      <c r="N4" s="9" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="O4" s="8" t="inlineStr">
         <is>
           <t>marie.k@exemple.com</t>
         </is>
       </c>
-      <c r="P4" s="10" t="inlineStr">
+      <c r="P4" s="9" t="inlineStr">
         <is>
           <t>KOUASSI Jean</t>
         </is>
       </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t>Pere</t>
         </is>
       </c>
-      <c r="R4" s="10" t="inlineStr">
+      <c r="R4" s="9" t="inlineStr">
         <is>
           <t>05 00 00 00 00</t>
         </is>
       </c>
-      <c r="S4" s="9" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>Riviera 2, rue des Jardins</t>
         </is>
       </c>
-      <c r="T4" s="10" t="inlineStr">
+      <c r="T4" s="9" t="inlineStr">
         <is>
           <t>KOUASSI Marie - 07 00 00 00 00</t>
         </is>
       </c>
-      <c r="U4" s="9" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>Asthme leger - inhalateur dans le sac</t>
         </is>
       </c>
-      <c r="V4" s="10" t="inlineStr">
+      <c r="V4" s="9" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="W4" s="10" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>Oui partage</t>
         </is>
       </c>
-      <c r="X4" s="10" t="inlineStr">
+      <c r="X4" s="9" t="inlineStr">
         <is>
           <t>Parfois</t>
         </is>
       </c>
-      <c r="Y4" s="9" t="inlineStr">
+      <c r="Y4" s="8" t="inlineStr">
         <is>
           <t>A pied avec sa soeur</t>
         </is>
       </c>
-      <c r="Z4" s="13" t="inlineStr">
+      <c r="Z4" s="12" t="inlineStr">
         <is>
           <t>05/09/2026</t>
         </is>
       </c>
-      <c r="AA4" s="9" t="inlineStr">
+      <c r="AA4" s="8" t="inlineStr">
         <is>
           <t>Actif</t>
         </is>
       </c>
-      <c r="AB4" s="9" t="inlineStr">
+      <c r="AB4" s="8" t="inlineStr">
         <is>
           <t>Tres timide, ne demande jamais d'aide</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="13" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="14" t="n"/>
       <c r="C5" s="14" t="n"/>
       <c r="D5" s="14" t="n"/>
       <c r="E5" s="15" t="n"/>
-      <c r="F5" s="12">
+      <c r="F5" s="11">
         <f>IF(E5="","",DATEDIF(E5,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G5" s="8" t="n"/>
-      <c r="H5" s="8" t="n"/>
-      <c r="I5" s="8" t="n"/>
-      <c r="J5" s="8" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13" t="n"/>
       <c r="K5" s="14" t="n"/>
-      <c r="L5" s="8" t="n"/>
+      <c r="L5" s="13" t="n"/>
       <c r="M5" s="14" t="n"/>
-      <c r="N5" s="8" t="n"/>
-      <c r="O5" s="8" t="n"/>
+      <c r="N5" s="13" t="n"/>
+      <c r="O5" s="13" t="n"/>
       <c r="P5" s="14" t="n"/>
-      <c r="Q5" s="8" t="n"/>
+      <c r="Q5" s="13" t="n"/>
       <c r="R5" s="14" t="n"/>
-      <c r="S5" s="8" t="n"/>
+      <c r="S5" s="13" t="n"/>
       <c r="T5" s="14" t="n"/>
-      <c r="U5" s="8" t="n"/>
+      <c r="U5" s="13" t="n"/>
       <c r="V5" s="14" t="n"/>
       <c r="W5" s="14" t="n"/>
       <c r="X5" s="14" t="n"/>
-      <c r="Y5" s="8" t="n"/>
+      <c r="Y5" s="13" t="n"/>
       <c r="Z5" s="16" t="n"/>
-      <c r="AA5" s="8" t="n"/>
-      <c r="AB5" s="8" t="n"/>
+      <c r="AA5" s="13" t="n"/>
+      <c r="AB5" s="13" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="13" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="14" t="n"/>
       <c r="C6" s="14" t="n"/>
       <c r="D6" s="14" t="n"/>
       <c r="E6" s="15" t="n"/>
-      <c r="F6" s="12">
+      <c r="F6" s="11">
         <f>IF(E6="","",DATEDIF(E6,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="n"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="13" t="n"/>
+      <c r="J6" s="13" t="n"/>
       <c r="K6" s="14" t="n"/>
-      <c r="L6" s="8" t="n"/>
+      <c r="L6" s="13" t="n"/>
       <c r="M6" s="14" t="n"/>
-      <c r="N6" s="8" t="n"/>
-      <c r="O6" s="8" t="n"/>
+      <c r="N6" s="13" t="n"/>
+      <c r="O6" s="13" t="n"/>
       <c r="P6" s="14" t="n"/>
-      <c r="Q6" s="8" t="n"/>
+      <c r="Q6" s="13" t="n"/>
       <c r="R6" s="14" t="n"/>
-      <c r="S6" s="8" t="n"/>
+      <c r="S6" s="13" t="n"/>
       <c r="T6" s="14" t="n"/>
-      <c r="U6" s="8" t="n"/>
+      <c r="U6" s="13" t="n"/>
       <c r="V6" s="14" t="n"/>
       <c r="W6" s="14" t="n"/>
       <c r="X6" s="14" t="n"/>
-      <c r="Y6" s="8" t="n"/>
+      <c r="Y6" s="13" t="n"/>
       <c r="Z6" s="16" t="n"/>
-      <c r="AA6" s="8" t="n"/>
-      <c r="AB6" s="8" t="n"/>
+      <c r="AA6" s="13" t="n"/>
+      <c r="AB6" s="13" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="13" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="14" t="n"/>
       <c r="C7" s="14" t="n"/>
       <c r="D7" s="14" t="n"/>
       <c r="E7" s="15" t="n"/>
-      <c r="F7" s="12">
+      <c r="F7" s="11">
         <f>IF(E7="","",DATEDIF(E7,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="8" t="n"/>
-      <c r="J7" s="8" t="n"/>
+      <c r="G7" s="13" t="n"/>
+      <c r="H7" s="13" t="n"/>
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="13" t="n"/>
       <c r="K7" s="14" t="n"/>
-      <c r="L7" s="8" t="n"/>
+      <c r="L7" s="13" t="n"/>
       <c r="M7" s="14" t="n"/>
-      <c r="N7" s="8" t="n"/>
-      <c r="O7" s="8" t="n"/>
+      <c r="N7" s="13" t="n"/>
+      <c r="O7" s="13" t="n"/>
       <c r="P7" s="14" t="n"/>
-      <c r="Q7" s="8" t="n"/>
+      <c r="Q7" s="13" t="n"/>
       <c r="R7" s="14" t="n"/>
-      <c r="S7" s="8" t="n"/>
+      <c r="S7" s="13" t="n"/>
       <c r="T7" s="14" t="n"/>
-      <c r="U7" s="8" t="n"/>
+      <c r="U7" s="13" t="n"/>
       <c r="V7" s="14" t="n"/>
       <c r="W7" s="14" t="n"/>
       <c r="X7" s="14" t="n"/>
-      <c r="Y7" s="8" t="n"/>
+      <c r="Y7" s="13" t="n"/>
       <c r="Z7" s="16" t="n"/>
-      <c r="AA7" s="8" t="n"/>
-      <c r="AB7" s="8" t="n"/>
+      <c r="AA7" s="13" t="n"/>
+      <c r="AB7" s="13" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="13" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="14" t="n"/>
       <c r="C8" s="14" t="n"/>
       <c r="D8" s="14" t="n"/>
       <c r="E8" s="15" t="n"/>
-      <c r="F8" s="12">
+      <c r="F8" s="11">
         <f>IF(E8="","",DATEDIF(E8,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
+      <c r="G8" s="13" t="n"/>
+      <c r="H8" s="13" t="n"/>
+      <c r="I8" s="13" t="n"/>
+      <c r="J8" s="13" t="n"/>
       <c r="K8" s="14" t="n"/>
-      <c r="L8" s="8" t="n"/>
+      <c r="L8" s="13" t="n"/>
       <c r="M8" s="14" t="n"/>
-      <c r="N8" s="8" t="n"/>
-      <c r="O8" s="8" t="n"/>
+      <c r="N8" s="13" t="n"/>
+      <c r="O8" s="13" t="n"/>
       <c r="P8" s="14" t="n"/>
-      <c r="Q8" s="8" t="n"/>
+      <c r="Q8" s="13" t="n"/>
       <c r="R8" s="14" t="n"/>
-      <c r="S8" s="8" t="n"/>
+      <c r="S8" s="13" t="n"/>
       <c r="T8" s="14" t="n"/>
-      <c r="U8" s="8" t="n"/>
+      <c r="U8" s="13" t="n"/>
       <c r="V8" s="14" t="n"/>
       <c r="W8" s="14" t="n"/>
       <c r="X8" s="14" t="n"/>
-      <c r="Y8" s="8" t="n"/>
+      <c r="Y8" s="13" t="n"/>
       <c r="Z8" s="16" t="n"/>
-      <c r="AA8" s="8" t="n"/>
-      <c r="AB8" s="8" t="n"/>
+      <c r="AA8" s="13" t="n"/>
+      <c r="AB8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="13" t="n">
         <v>6</v>
       </c>
       <c r="B9" s="14" t="n"/>
       <c r="C9" s="14" t="n"/>
       <c r="D9" s="14" t="n"/>
       <c r="E9" s="15" t="n"/>
-      <c r="F9" s="12">
+      <c r="F9" s="11">
         <f>IF(E9="","",DATEDIF(E9,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="8" t="n"/>
+      <c r="G9" s="13" t="n"/>
+      <c r="H9" s="13" t="n"/>
+      <c r="I9" s="13" t="n"/>
+      <c r="J9" s="13" t="n"/>
       <c r="K9" s="14" t="n"/>
-      <c r="L9" s="8" t="n"/>
+      <c r="L9" s="13" t="n"/>
       <c r="M9" s="14" t="n"/>
-      <c r="N9" s="8" t="n"/>
-      <c r="O9" s="8" t="n"/>
+      <c r="N9" s="13" t="n"/>
+      <c r="O9" s="13" t="n"/>
       <c r="P9" s="14" t="n"/>
-      <c r="Q9" s="8" t="n"/>
+      <c r="Q9" s="13" t="n"/>
       <c r="R9" s="14" t="n"/>
-      <c r="S9" s="8" t="n"/>
+      <c r="S9" s="13" t="n"/>
       <c r="T9" s="14" t="n"/>
-      <c r="U9" s="8" t="n"/>
+      <c r="U9" s="13" t="n"/>
       <c r="V9" s="14" t="n"/>
       <c r="W9" s="14" t="n"/>
       <c r="X9" s="14" t="n"/>
-      <c r="Y9" s="8" t="n"/>
+      <c r="Y9" s="13" t="n"/>
       <c r="Z9" s="16" t="n"/>
-      <c r="AA9" s="8" t="n"/>
-      <c r="AB9" s="8" t="n"/>
+      <c r="AA9" s="13" t="n"/>
+      <c r="AB9" s="13" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="13" t="n">
         <v>7</v>
       </c>
       <c r="B10" s="14" t="n"/>
       <c r="C10" s="14" t="n"/>
       <c r="D10" s="14" t="n"/>
       <c r="E10" s="15" t="n"/>
-      <c r="F10" s="12">
+      <c r="F10" s="11">
         <f>IF(E10="","",DATEDIF(E10,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="13" t="n"/>
+      <c r="I10" s="13" t="n"/>
+      <c r="J10" s="13" t="n"/>
       <c r="K10" s="14" t="n"/>
-      <c r="L10" s="8" t="n"/>
+      <c r="L10" s="13" t="n"/>
       <c r="M10" s="14" t="n"/>
-      <c r="N10" s="8" t="n"/>
-      <c r="O10" s="8" t="n"/>
+      <c r="N10" s="13" t="n"/>
+      <c r="O10" s="13" t="n"/>
       <c r="P10" s="14" t="n"/>
-      <c r="Q10" s="8" t="n"/>
+      <c r="Q10" s="13" t="n"/>
       <c r="R10" s="14" t="n"/>
-      <c r="S10" s="8" t="n"/>
+      <c r="S10" s="13" t="n"/>
       <c r="T10" s="14" t="n"/>
-      <c r="U10" s="8" t="n"/>
+      <c r="U10" s="13" t="n"/>
       <c r="V10" s="14" t="n"/>
       <c r="W10" s="14" t="n"/>
       <c r="X10" s="14" t="n"/>
-      <c r="Y10" s="8" t="n"/>
+      <c r="Y10" s="13" t="n"/>
       <c r="Z10" s="16" t="n"/>
-      <c r="AA10" s="8" t="n"/>
-      <c r="AB10" s="8" t="n"/>
+      <c r="AA10" s="13" t="n"/>
+      <c r="AB10" s="13" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="13" t="n">
         <v>8</v>
       </c>
       <c r="B11" s="14" t="n"/>
       <c r="C11" s="14" t="n"/>
       <c r="D11" s="14" t="n"/>
       <c r="E11" s="15" t="n"/>
-      <c r="F11" s="12">
+      <c r="F11" s="11">
         <f>IF(E11="","",DATEDIF(E11,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="8" t="n"/>
-      <c r="J11" s="8" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="13" t="n"/>
+      <c r="I11" s="13" t="n"/>
+      <c r="J11" s="13" t="n"/>
       <c r="K11" s="14" t="n"/>
-      <c r="L11" s="8" t="n"/>
+      <c r="L11" s="13" t="n"/>
       <c r="M11" s="14" t="n"/>
-      <c r="N11" s="8" t="n"/>
-      <c r="O11" s="8" t="n"/>
+      <c r="N11" s="13" t="n"/>
+      <c r="O11" s="13" t="n"/>
       <c r="P11" s="14" t="n"/>
-      <c r="Q11" s="8" t="n"/>
+      <c r="Q11" s="13" t="n"/>
       <c r="R11" s="14" t="n"/>
-      <c r="S11" s="8" t="n"/>
+      <c r="S11" s="13" t="n"/>
       <c r="T11" s="14" t="n"/>
-      <c r="U11" s="8" t="n"/>
+      <c r="U11" s="13" t="n"/>
       <c r="V11" s="14" t="n"/>
       <c r="W11" s="14" t="n"/>
       <c r="X11" s="14" t="n"/>
-      <c r="Y11" s="8" t="n"/>
+      <c r="Y11" s="13" t="n"/>
       <c r="Z11" s="16" t="n"/>
-      <c r="AA11" s="8" t="n"/>
-      <c r="AB11" s="8" t="n"/>
+      <c r="AA11" s="13" t="n"/>
+      <c r="AB11" s="13" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="13" t="n">
         <v>9</v>
       </c>
       <c r="B12" s="14" t="n"/>
       <c r="C12" s="14" t="n"/>
       <c r="D12" s="14" t="n"/>
       <c r="E12" s="15" t="n"/>
-      <c r="F12" s="12">
+      <c r="F12" s="11">
         <f>IF(E12="","",DATEDIF(E12,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="13" t="n"/>
+      <c r="I12" s="13" t="n"/>
+      <c r="J12" s="13" t="n"/>
       <c r="K12" s="14" t="n"/>
-      <c r="L12" s="8" t="n"/>
+      <c r="L12" s="13" t="n"/>
       <c r="M12" s="14" t="n"/>
-      <c r="N12" s="8" t="n"/>
-      <c r="O12" s="8" t="n"/>
+      <c r="N12" s="13" t="n"/>
+      <c r="O12" s="13" t="n"/>
       <c r="P12" s="14" t="n"/>
-      <c r="Q12" s="8" t="n"/>
+      <c r="Q12" s="13" t="n"/>
       <c r="R12" s="14" t="n"/>
-      <c r="S12" s="8" t="n"/>
+      <c r="S12" s="13" t="n"/>
       <c r="T12" s="14" t="n"/>
-      <c r="U12" s="8" t="n"/>
+      <c r="U12" s="13" t="n"/>
       <c r="V12" s="14" t="n"/>
       <c r="W12" s="14" t="n"/>
       <c r="X12" s="14" t="n"/>
-      <c r="Y12" s="8" t="n"/>
+      <c r="Y12" s="13" t="n"/>
       <c r="Z12" s="16" t="n"/>
-      <c r="AA12" s="8" t="n"/>
-      <c r="AB12" s="8" t="n"/>
+      <c r="AA12" s="13" t="n"/>
+      <c r="AB12" s="13" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="13" t="n">
         <v>10</v>
       </c>
       <c r="B13" s="14" t="n"/>
       <c r="C13" s="14" t="n"/>
       <c r="D13" s="14" t="n"/>
       <c r="E13" s="15" t="n"/>
-      <c r="F13" s="12">
+      <c r="F13" s="11">
         <f>IF(E13="","",DATEDIF(E13,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G13" s="8" t="n"/>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="8" t="n"/>
-      <c r="J13" s="8" t="n"/>
+      <c r="G13" s="13" t="n"/>
+      <c r="H13" s="13" t="n"/>
+      <c r="I13" s="13" t="n"/>
+      <c r="J13" s="13" t="n"/>
       <c r="K13" s="14" t="n"/>
-      <c r="L13" s="8" t="n"/>
+      <c r="L13" s="13" t="n"/>
       <c r="M13" s="14" t="n"/>
-      <c r="N13" s="8" t="n"/>
-      <c r="O13" s="8" t="n"/>
+      <c r="N13" s="13" t="n"/>
+      <c r="O13" s="13" t="n"/>
       <c r="P13" s="14" t="n"/>
-      <c r="Q13" s="8" t="n"/>
+      <c r="Q13" s="13" t="n"/>
       <c r="R13" s="14" t="n"/>
-      <c r="S13" s="8" t="n"/>
+      <c r="S13" s="13" t="n"/>
       <c r="T13" s="14" t="n"/>
-      <c r="U13" s="8" t="n"/>
+      <c r="U13" s="13" t="n"/>
       <c r="V13" s="14" t="n"/>
       <c r="W13" s="14" t="n"/>
       <c r="X13" s="14" t="n"/>
-      <c r="Y13" s="8" t="n"/>
+      <c r="Y13" s="13" t="n"/>
       <c r="Z13" s="16" t="n"/>
-      <c r="AA13" s="8" t="n"/>
-      <c r="AB13" s="8" t="n"/>
+      <c r="AA13" s="13" t="n"/>
+      <c r="AB13" s="13" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="13" t="n">
         <v>11</v>
       </c>
       <c r="B14" s="14" t="n"/>
       <c r="C14" s="14" t="n"/>
       <c r="D14" s="14" t="n"/>
       <c r="E14" s="15" t="n"/>
-      <c r="F14" s="12">
+      <c r="F14" s="11">
         <f>IF(E14="","",DATEDIF(E14,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="13" t="n"/>
+      <c r="I14" s="13" t="n"/>
+      <c r="J14" s="13" t="n"/>
       <c r="K14" s="14" t="n"/>
-      <c r="L14" s="8" t="n"/>
+      <c r="L14" s="13" t="n"/>
       <c r="M14" s="14" t="n"/>
-      <c r="N14" s="8" t="n"/>
-      <c r="O14" s="8" t="n"/>
+      <c r="N14" s="13" t="n"/>
+      <c r="O14" s="13" t="n"/>
       <c r="P14" s="14" t="n"/>
-      <c r="Q14" s="8" t="n"/>
+      <c r="Q14" s="13" t="n"/>
       <c r="R14" s="14" t="n"/>
-      <c r="S14" s="8" t="n"/>
+      <c r="S14" s="13" t="n"/>
       <c r="T14" s="14" t="n"/>
-      <c r="U14" s="8" t="n"/>
+      <c r="U14" s="13" t="n"/>
       <c r="V14" s="14" t="n"/>
       <c r="W14" s="14" t="n"/>
       <c r="X14" s="14" t="n"/>
-      <c r="Y14" s="8" t="n"/>
+      <c r="Y14" s="13" t="n"/>
       <c r="Z14" s="16" t="n"/>
-      <c r="AA14" s="8" t="n"/>
-      <c r="AB14" s="8" t="n"/>
+      <c r="AA14" s="13" t="n"/>
+      <c r="AB14" s="13" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="13" t="n">
         <v>12</v>
       </c>
       <c r="B15" s="14" t="n"/>
       <c r="C15" s="14" t="n"/>
       <c r="D15" s="14" t="n"/>
       <c r="E15" s="15" t="n"/>
-      <c r="F15" s="12">
+      <c r="F15" s="11">
         <f>IF(E15="","",DATEDIF(E15,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
-      <c r="J15" s="8" t="n"/>
+      <c r="G15" s="13" t="n"/>
+      <c r="H15" s="13" t="n"/>
+      <c r="I15" s="13" t="n"/>
+      <c r="J15" s="13" t="n"/>
       <c r="K15" s="14" t="n"/>
-      <c r="L15" s="8" t="n"/>
+      <c r="L15" s="13" t="n"/>
       <c r="M15" s="14" t="n"/>
-      <c r="N15" s="8" t="n"/>
-      <c r="O15" s="8" t="n"/>
+      <c r="N15" s="13" t="n"/>
+      <c r="O15" s="13" t="n"/>
       <c r="P15" s="14" t="n"/>
-      <c r="Q15" s="8" t="n"/>
+      <c r="Q15" s="13" t="n"/>
       <c r="R15" s="14" t="n"/>
-      <c r="S15" s="8" t="n"/>
+      <c r="S15" s="13" t="n"/>
       <c r="T15" s="14" t="n"/>
-      <c r="U15" s="8" t="n"/>
+      <c r="U15" s="13" t="n"/>
       <c r="V15" s="14" t="n"/>
       <c r="W15" s="14" t="n"/>
       <c r="X15" s="14" t="n"/>
-      <c r="Y15" s="8" t="n"/>
+      <c r="Y15" s="13" t="n"/>
       <c r="Z15" s="16" t="n"/>
-      <c r="AA15" s="8" t="n"/>
-      <c r="AB15" s="8" t="n"/>
+      <c r="AA15" s="13" t="n"/>
+      <c r="AB15" s="13" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="13" t="n">
         <v>13</v>
       </c>
       <c r="B16" s="14" t="n"/>
       <c r="C16" s="14" t="n"/>
       <c r="D16" s="14" t="n"/>
       <c r="E16" s="15" t="n"/>
-      <c r="F16" s="12">
+      <c r="F16" s="11">
         <f>IF(E16="","",DATEDIF(E16,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="13" t="n"/>
+      <c r="I16" s="13" t="n"/>
+      <c r="J16" s="13" t="n"/>
       <c r="K16" s="14" t="n"/>
-      <c r="L16" s="8" t="n"/>
+      <c r="L16" s="13" t="n"/>
       <c r="M16" s="14" t="n"/>
-      <c r="N16" s="8" t="n"/>
-      <c r="O16" s="8" t="n"/>
+      <c r="N16" s="13" t="n"/>
+      <c r="O16" s="13" t="n"/>
       <c r="P16" s="14" t="n"/>
-      <c r="Q16" s="8" t="n"/>
+      <c r="Q16" s="13" t="n"/>
       <c r="R16" s="14" t="n"/>
-      <c r="S16" s="8" t="n"/>
+      <c r="S16" s="13" t="n"/>
       <c r="T16" s="14" t="n"/>
-      <c r="U16" s="8" t="n"/>
+      <c r="U16" s="13" t="n"/>
       <c r="V16" s="14" t="n"/>
       <c r="W16" s="14" t="n"/>
       <c r="X16" s="14" t="n"/>
-      <c r="Y16" s="8" t="n"/>
+      <c r="Y16" s="13" t="n"/>
       <c r="Z16" s="16" t="n"/>
-      <c r="AA16" s="8" t="n"/>
-      <c r="AB16" s="8" t="n"/>
+      <c r="AA16" s="13" t="n"/>
+      <c r="AB16" s="13" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="13" t="n">
         <v>14</v>
       </c>
       <c r="B17" s="14" t="n"/>
       <c r="C17" s="14" t="n"/>
       <c r="D17" s="14" t="n"/>
       <c r="E17" s="15" t="n"/>
-      <c r="F17" s="12">
+      <c r="F17" s="11">
         <f>IF(E17="","",DATEDIF(E17,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="8" t="n"/>
-      <c r="J17" s="8" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="13" t="n"/>
+      <c r="I17" s="13" t="n"/>
+      <c r="J17" s="13" t="n"/>
       <c r="K17" s="14" t="n"/>
-      <c r="L17" s="8" t="n"/>
+      <c r="L17" s="13" t="n"/>
       <c r="M17" s="14" t="n"/>
-      <c r="N17" s="8" t="n"/>
-      <c r="O17" s="8" t="n"/>
+      <c r="N17" s="13" t="n"/>
+      <c r="O17" s="13" t="n"/>
       <c r="P17" s="14" t="n"/>
-      <c r="Q17" s="8" t="n"/>
+      <c r="Q17" s="13" t="n"/>
       <c r="R17" s="14" t="n"/>
-      <c r="S17" s="8" t="n"/>
+      <c r="S17" s="13" t="n"/>
       <c r="T17" s="14" t="n"/>
-      <c r="U17" s="8" t="n"/>
+      <c r="U17" s="13" t="n"/>
       <c r="V17" s="14" t="n"/>
       <c r="W17" s="14" t="n"/>
       <c r="X17" s="14" t="n"/>
-      <c r="Y17" s="8" t="n"/>
+      <c r="Y17" s="13" t="n"/>
       <c r="Z17" s="16" t="n"/>
-      <c r="AA17" s="8" t="n"/>
-      <c r="AB17" s="8" t="n"/>
+      <c r="AA17" s="13" t="n"/>
+      <c r="AB17" s="13" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="13" t="n">
         <v>15</v>
       </c>
       <c r="B18" s="14" t="n"/>
       <c r="C18" s="14" t="n"/>
       <c r="D18" s="14" t="n"/>
       <c r="E18" s="15" t="n"/>
-      <c r="F18" s="12">
+      <c r="F18" s="11">
         <f>IF(E18="","",DATEDIF(E18,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="13" t="n"/>
+      <c r="I18" s="13" t="n"/>
+      <c r="J18" s="13" t="n"/>
       <c r="K18" s="14" t="n"/>
-      <c r="L18" s="8" t="n"/>
+      <c r="L18" s="13" t="n"/>
       <c r="M18" s="14" t="n"/>
-      <c r="N18" s="8" t="n"/>
-      <c r="O18" s="8" t="n"/>
+      <c r="N18" s="13" t="n"/>
+      <c r="O18" s="13" t="n"/>
       <c r="P18" s="14" t="n"/>
-      <c r="Q18" s="8" t="n"/>
+      <c r="Q18" s="13" t="n"/>
       <c r="R18" s="14" t="n"/>
-      <c r="S18" s="8" t="n"/>
+      <c r="S18" s="13" t="n"/>
       <c r="T18" s="14" t="n"/>
-      <c r="U18" s="8" t="n"/>
+      <c r="U18" s="13" t="n"/>
       <c r="V18" s="14" t="n"/>
       <c r="W18" s="14" t="n"/>
       <c r="X18" s="14" t="n"/>
-      <c r="Y18" s="8" t="n"/>
+      <c r="Y18" s="13" t="n"/>
       <c r="Z18" s="16" t="n"/>
-      <c r="AA18" s="8" t="n"/>
-      <c r="AB18" s="8" t="n"/>
+      <c r="AA18" s="13" t="n"/>
+      <c r="AB18" s="13" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="13" t="n">
         <v>16</v>
       </c>
       <c r="B19" s="14" t="n"/>
       <c r="C19" s="14" t="n"/>
       <c r="D19" s="14" t="n"/>
       <c r="E19" s="15" t="n"/>
-      <c r="F19" s="12">
+      <c r="F19" s="11">
         <f>IF(E19="","",DATEDIF(E19,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="13" t="n"/>
+      <c r="I19" s="13" t="n"/>
+      <c r="J19" s="13" t="n"/>
       <c r="K19" s="14" t="n"/>
-      <c r="L19" s="8" t="n"/>
+      <c r="L19" s="13" t="n"/>
       <c r="M19" s="14" t="n"/>
-      <c r="N19" s="8" t="n"/>
-      <c r="O19" s="8" t="n"/>
+      <c r="N19" s="13" t="n"/>
+      <c r="O19" s="13" t="n"/>
       <c r="P19" s="14" t="n"/>
-      <c r="Q19" s="8" t="n"/>
+      <c r="Q19" s="13" t="n"/>
       <c r="R19" s="14" t="n"/>
-      <c r="S19" s="8" t="n"/>
+      <c r="S19" s="13" t="n"/>
       <c r="T19" s="14" t="n"/>
-      <c r="U19" s="8" t="n"/>
+      <c r="U19" s="13" t="n"/>
       <c r="V19" s="14" t="n"/>
       <c r="W19" s="14" t="n"/>
       <c r="X19" s="14" t="n"/>
-      <c r="Y19" s="8" t="n"/>
+      <c r="Y19" s="13" t="n"/>
       <c r="Z19" s="16" t="n"/>
-      <c r="AA19" s="8" t="n"/>
-      <c r="AB19" s="8" t="n"/>
+      <c r="AA19" s="13" t="n"/>
+      <c r="AB19" s="13" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="13" t="n">
         <v>17</v>
       </c>
       <c r="B20" s="14" t="n"/>
       <c r="C20" s="14" t="n"/>
       <c r="D20" s="14" t="n"/>
       <c r="E20" s="15" t="n"/>
-      <c r="F20" s="12">
+      <c r="F20" s="11">
         <f>IF(E20="","",DATEDIF(E20,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n"/>
+      <c r="G20" s="13" t="n"/>
+      <c r="H20" s="13" t="n"/>
+      <c r="I20" s="13" t="n"/>
+      <c r="J20" s="13" t="n"/>
       <c r="K20" s="14" t="n"/>
-      <c r="L20" s="8" t="n"/>
+      <c r="L20" s="13" t="n"/>
       <c r="M20" s="14" t="n"/>
-      <c r="N20" s="8" t="n"/>
-      <c r="O20" s="8" t="n"/>
+      <c r="N20" s="13" t="n"/>
+      <c r="O20" s="13" t="n"/>
       <c r="P20" s="14" t="n"/>
-      <c r="Q20" s="8" t="n"/>
+      <c r="Q20" s="13" t="n"/>
       <c r="R20" s="14" t="n"/>
-      <c r="S20" s="8" t="n"/>
+      <c r="S20" s="13" t="n"/>
       <c r="T20" s="14" t="n"/>
-      <c r="U20" s="8" t="n"/>
+      <c r="U20" s="13" t="n"/>
       <c r="V20" s="14" t="n"/>
       <c r="W20" s="14" t="n"/>
       <c r="X20" s="14" t="n"/>
-      <c r="Y20" s="8" t="n"/>
+      <c r="Y20" s="13" t="n"/>
       <c r="Z20" s="16" t="n"/>
-      <c r="AA20" s="8" t="n"/>
-      <c r="AB20" s="8" t="n"/>
+      <c r="AA20" s="13" t="n"/>
+      <c r="AB20" s="13" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="13" t="n">
         <v>18</v>
       </c>
       <c r="B21" s="14" t="n"/>
       <c r="C21" s="14" t="n"/>
       <c r="D21" s="14" t="n"/>
       <c r="E21" s="15" t="n"/>
-      <c r="F21" s="12">
+      <c r="F21" s="11">
         <f>IF(E21="","",DATEDIF(E21,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-      <c r="J21" s="8" t="n"/>
+      <c r="G21" s="13" t="n"/>
+      <c r="H21" s="13" t="n"/>
+      <c r="I21" s="13" t="n"/>
+      <c r="J21" s="13" t="n"/>
       <c r="K21" s="14" t="n"/>
-      <c r="L21" s="8" t="n"/>
+      <c r="L21" s="13" t="n"/>
       <c r="M21" s="14" t="n"/>
-      <c r="N21" s="8" t="n"/>
-      <c r="O21" s="8" t="n"/>
+      <c r="N21" s="13" t="n"/>
+      <c r="O21" s="13" t="n"/>
       <c r="P21" s="14" t="n"/>
-      <c r="Q21" s="8" t="n"/>
+      <c r="Q21" s="13" t="n"/>
       <c r="R21" s="14" t="n"/>
-      <c r="S21" s="8" t="n"/>
+      <c r="S21" s="13" t="n"/>
       <c r="T21" s="14" t="n"/>
-      <c r="U21" s="8" t="n"/>
+      <c r="U21" s="13" t="n"/>
       <c r="V21" s="14" t="n"/>
       <c r="W21" s="14" t="n"/>
       <c r="X21" s="14" t="n"/>
-      <c r="Y21" s="8" t="n"/>
+      <c r="Y21" s="13" t="n"/>
       <c r="Z21" s="16" t="n"/>
-      <c r="AA21" s="8" t="n"/>
-      <c r="AB21" s="8" t="n"/>
+      <c r="AA21" s="13" t="n"/>
+      <c r="AB21" s="13" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="13" t="n">
         <v>19</v>
       </c>
       <c r="B22" s="14" t="n"/>
       <c r="C22" s="14" t="n"/>
       <c r="D22" s="14" t="n"/>
       <c r="E22" s="15" t="n"/>
-      <c r="F22" s="12">
+      <c r="F22" s="11">
         <f>IF(E22="","",DATEDIF(E22,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n"/>
+      <c r="G22" s="13" t="n"/>
+      <c r="H22" s="13" t="n"/>
+      <c r="I22" s="13" t="n"/>
+      <c r="J22" s="13" t="n"/>
       <c r="K22" s="14" t="n"/>
-      <c r="L22" s="8" t="n"/>
+      <c r="L22" s="13" t="n"/>
       <c r="M22" s="14" t="n"/>
-      <c r="N22" s="8" t="n"/>
-      <c r="O22" s="8" t="n"/>
+      <c r="N22" s="13" t="n"/>
+      <c r="O22" s="13" t="n"/>
       <c r="P22" s="14" t="n"/>
-      <c r="Q22" s="8" t="n"/>
+      <c r="Q22" s="13" t="n"/>
       <c r="R22" s="14" t="n"/>
-      <c r="S22" s="8" t="n"/>
+      <c r="S22" s="13" t="n"/>
       <c r="T22" s="14" t="n"/>
-      <c r="U22" s="8" t="n"/>
+      <c r="U22" s="13" t="n"/>
       <c r="V22" s="14" t="n"/>
       <c r="W22" s="14" t="n"/>
       <c r="X22" s="14" t="n"/>
-      <c r="Y22" s="8" t="n"/>
+      <c r="Y22" s="13" t="n"/>
       <c r="Z22" s="16" t="n"/>
-      <c r="AA22" s="8" t="n"/>
-      <c r="AB22" s="8" t="n"/>
+      <c r="AA22" s="13" t="n"/>
+      <c r="AB22" s="13" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="13" t="n">
         <v>20</v>
       </c>
       <c r="B23" s="14" t="n"/>
       <c r="C23" s="14" t="n"/>
       <c r="D23" s="14" t="n"/>
       <c r="E23" s="15" t="n"/>
-      <c r="F23" s="12">
+      <c r="F23" s="11">
         <f>IF(E23="","",DATEDIF(E23,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="8" t="n"/>
+      <c r="G23" s="13" t="n"/>
+      <c r="H23" s="13" t="n"/>
+      <c r="I23" s="13" t="n"/>
+      <c r="J23" s="13" t="n"/>
       <c r="K23" s="14" t="n"/>
-      <c r="L23" s="8" t="n"/>
+      <c r="L23" s="13" t="n"/>
       <c r="M23" s="14" t="n"/>
-      <c r="N23" s="8" t="n"/>
-      <c r="O23" s="8" t="n"/>
+      <c r="N23" s="13" t="n"/>
+      <c r="O23" s="13" t="n"/>
       <c r="P23" s="14" t="n"/>
-      <c r="Q23" s="8" t="n"/>
+      <c r="Q23" s="13" t="n"/>
       <c r="R23" s="14" t="n"/>
-      <c r="S23" s="8" t="n"/>
+      <c r="S23" s="13" t="n"/>
       <c r="T23" s="14" t="n"/>
-      <c r="U23" s="8" t="n"/>
+      <c r="U23" s="13" t="n"/>
       <c r="V23" s="14" t="n"/>
       <c r="W23" s="14" t="n"/>
       <c r="X23" s="14" t="n"/>
-      <c r="Y23" s="8" t="n"/>
+      <c r="Y23" s="13" t="n"/>
       <c r="Z23" s="16" t="n"/>
-      <c r="AA23" s="8" t="n"/>
-      <c r="AB23" s="8" t="n"/>
+      <c r="AA23" s="13" t="n"/>
+      <c r="AB23" s="13" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="13" t="n">
         <v>21</v>
       </c>
       <c r="B24" s="14" t="n"/>
       <c r="C24" s="14" t="n"/>
       <c r="D24" s="14" t="n"/>
       <c r="E24" s="15" t="n"/>
-      <c r="F24" s="12">
+      <c r="F24" s="11">
         <f>IF(E24="","",DATEDIF(E24,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
+      <c r="G24" s="13" t="n"/>
+      <c r="H24" s="13" t="n"/>
+      <c r="I24" s="13" t="n"/>
+      <c r="J24" s="13" t="n"/>
       <c r="K24" s="14" t="n"/>
-      <c r="L24" s="8" t="n"/>
+      <c r="L24" s="13" t="n"/>
       <c r="M24" s="14" t="n"/>
-      <c r="N24" s="8" t="n"/>
-      <c r="O24" s="8" t="n"/>
+      <c r="N24" s="13" t="n"/>
+      <c r="O24" s="13" t="n"/>
       <c r="P24" s="14" t="n"/>
-      <c r="Q24" s="8" t="n"/>
+      <c r="Q24" s="13" t="n"/>
       <c r="R24" s="14" t="n"/>
-      <c r="S24" s="8" t="n"/>
+      <c r="S24" s="13" t="n"/>
       <c r="T24" s="14" t="n"/>
-      <c r="U24" s="8" t="n"/>
+      <c r="U24" s="13" t="n"/>
       <c r="V24" s="14" t="n"/>
       <c r="W24" s="14" t="n"/>
       <c r="X24" s="14" t="n"/>
-      <c r="Y24" s="8" t="n"/>
+      <c r="Y24" s="13" t="n"/>
       <c r="Z24" s="16" t="n"/>
-      <c r="AA24" s="8" t="n"/>
-      <c r="AB24" s="8" t="n"/>
+      <c r="AA24" s="13" t="n"/>
+      <c r="AB24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="n">
+      <c r="A25" s="13" t="n">
         <v>22</v>
       </c>
       <c r="B25" s="14" t="n"/>
       <c r="C25" s="14" t="n"/>
       <c r="D25" s="14" t="n"/>
       <c r="E25" s="15" t="n"/>
-      <c r="F25" s="12">
+      <c r="F25" s="11">
         <f>IF(E25="","",DATEDIF(E25,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="8" t="n"/>
+      <c r="G25" s="13" t="n"/>
+      <c r="H25" s="13" t="n"/>
+      <c r="I25" s="13" t="n"/>
+      <c r="J25" s="13" t="n"/>
       <c r="K25" s="14" t="n"/>
-      <c r="L25" s="8" t="n"/>
+      <c r="L25" s="13" t="n"/>
       <c r="M25" s="14" t="n"/>
-      <c r="N25" s="8" t="n"/>
-      <c r="O25" s="8" t="n"/>
+      <c r="N25" s="13" t="n"/>
+      <c r="O25" s="13" t="n"/>
       <c r="P25" s="14" t="n"/>
-      <c r="Q25" s="8" t="n"/>
+      <c r="Q25" s="13" t="n"/>
       <c r="R25" s="14" t="n"/>
-      <c r="S25" s="8" t="n"/>
+      <c r="S25" s="13" t="n"/>
       <c r="T25" s="14" t="n"/>
-      <c r="U25" s="8" t="n"/>
+      <c r="U25" s="13" t="n"/>
       <c r="V25" s="14" t="n"/>
       <c r="W25" s="14" t="n"/>
       <c r="X25" s="14" t="n"/>
-      <c r="Y25" s="8" t="n"/>
+      <c r="Y25" s="13" t="n"/>
       <c r="Z25" s="16" t="n"/>
-      <c r="AA25" s="8" t="n"/>
-      <c r="AB25" s="8" t="n"/>
+      <c r="AA25" s="13" t="n"/>
+      <c r="AB25" s="13" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="13" t="n">
         <v>23</v>
       </c>
       <c r="B26" s="14" t="n"/>
       <c r="C26" s="14" t="n"/>
       <c r="D26" s="14" t="n"/>
       <c r="E26" s="15" t="n"/>
-      <c r="F26" s="12">
+      <c r="F26" s="11">
         <f>IF(E26="","",DATEDIF(E26,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8" t="n"/>
-      <c r="J26" s="8" t="n"/>
+      <c r="G26" s="13" t="n"/>
+      <c r="H26" s="13" t="n"/>
+      <c r="I26" s="13" t="n"/>
+      <c r="J26" s="13" t="n"/>
       <c r="K26" s="14" t="n"/>
-      <c r="L26" s="8" t="n"/>
+      <c r="L26" s="13" t="n"/>
       <c r="M26" s="14" t="n"/>
-      <c r="N26" s="8" t="n"/>
-      <c r="O26" s="8" t="n"/>
+      <c r="N26" s="13" t="n"/>
+      <c r="O26" s="13" t="n"/>
       <c r="P26" s="14" t="n"/>
-      <c r="Q26" s="8" t="n"/>
+      <c r="Q26" s="13" t="n"/>
       <c r="R26" s="14" t="n"/>
-      <c r="S26" s="8" t="n"/>
+      <c r="S26" s="13" t="n"/>
       <c r="T26" s="14" t="n"/>
-      <c r="U26" s="8" t="n"/>
+      <c r="U26" s="13" t="n"/>
       <c r="V26" s="14" t="n"/>
       <c r="W26" s="14" t="n"/>
       <c r="X26" s="14" t="n"/>
-      <c r="Y26" s="8" t="n"/>
+      <c r="Y26" s="13" t="n"/>
       <c r="Z26" s="16" t="n"/>
-      <c r="AA26" s="8" t="n"/>
-      <c r="AB26" s="8" t="n"/>
+      <c r="AA26" s="13" t="n"/>
+      <c r="AB26" s="13" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n">
+      <c r="A27" s="13" t="n">
         <v>24</v>
       </c>
       <c r="B27" s="14" t="n"/>
       <c r="C27" s="14" t="n"/>
       <c r="D27" s="14" t="n"/>
       <c r="E27" s="15" t="n"/>
-      <c r="F27" s="12">
+      <c r="F27" s="11">
         <f>IF(E27="","",DATEDIF(E27,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
-      <c r="J27" s="8" t="n"/>
+      <c r="G27" s="13" t="n"/>
+      <c r="H27" s="13" t="n"/>
+      <c r="I27" s="13" t="n"/>
+      <c r="J27" s="13" t="n"/>
       <c r="K27" s="14" t="n"/>
-      <c r="L27" s="8" t="n"/>
+      <c r="L27" s="13" t="n"/>
       <c r="M27" s="14" t="n"/>
-      <c r="N27" s="8" t="n"/>
-      <c r="O27" s="8" t="n"/>
+      <c r="N27" s="13" t="n"/>
+      <c r="O27" s="13" t="n"/>
       <c r="P27" s="14" t="n"/>
-      <c r="Q27" s="8" t="n"/>
+      <c r="Q27" s="13" t="n"/>
       <c r="R27" s="14" t="n"/>
-      <c r="S27" s="8" t="n"/>
+      <c r="S27" s="13" t="n"/>
       <c r="T27" s="14" t="n"/>
-      <c r="U27" s="8" t="n"/>
+      <c r="U27" s="13" t="n"/>
       <c r="V27" s="14" t="n"/>
       <c r="W27" s="14" t="n"/>
       <c r="X27" s="14" t="n"/>
-      <c r="Y27" s="8" t="n"/>
+      <c r="Y27" s="13" t="n"/>
       <c r="Z27" s="16" t="n"/>
-      <c r="AA27" s="8" t="n"/>
-      <c r="AB27" s="8" t="n"/>
+      <c r="AA27" s="13" t="n"/>
+      <c r="AB27" s="13" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n">
+      <c r="A28" s="13" t="n">
         <v>25</v>
       </c>
       <c r="B28" s="14" t="n"/>
       <c r="C28" s="14" t="n"/>
       <c r="D28" s="14" t="n"/>
       <c r="E28" s="15" t="n"/>
-      <c r="F28" s="12">
+      <c r="F28" s="11">
         <f>IF(E28="","",DATEDIF(E28,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n"/>
-      <c r="J28" s="8" t="n"/>
+      <c r="G28" s="13" t="n"/>
+      <c r="H28" s="13" t="n"/>
+      <c r="I28" s="13" t="n"/>
+      <c r="J28" s="13" t="n"/>
       <c r="K28" s="14" t="n"/>
-      <c r="L28" s="8" t="n"/>
+      <c r="L28" s="13" t="n"/>
       <c r="M28" s="14" t="n"/>
-      <c r="N28" s="8" t="n"/>
-      <c r="O28" s="8" t="n"/>
+      <c r="N28" s="13" t="n"/>
+      <c r="O28" s="13" t="n"/>
       <c r="P28" s="14" t="n"/>
-      <c r="Q28" s="8" t="n"/>
+      <c r="Q28" s="13" t="n"/>
       <c r="R28" s="14" t="n"/>
-      <c r="S28" s="8" t="n"/>
+      <c r="S28" s="13" t="n"/>
       <c r="T28" s="14" t="n"/>
-      <c r="U28" s="8" t="n"/>
+      <c r="U28" s="13" t="n"/>
       <c r="V28" s="14" t="n"/>
       <c r="W28" s="14" t="n"/>
       <c r="X28" s="14" t="n"/>
-      <c r="Y28" s="8" t="n"/>
+      <c r="Y28" s="13" t="n"/>
       <c r="Z28" s="16" t="n"/>
-      <c r="AA28" s="8" t="n"/>
-      <c r="AB28" s="8" t="n"/>
+      <c r="AA28" s="13" t="n"/>
+      <c r="AB28" s="13" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n">
+      <c r="A29" s="13" t="n">
         <v>26</v>
       </c>
       <c r="B29" s="14" t="n"/>
       <c r="C29" s="14" t="n"/>
       <c r="D29" s="14" t="n"/>
       <c r="E29" s="15" t="n"/>
-      <c r="F29" s="12">
+      <c r="F29" s="11">
         <f>IF(E29="","",DATEDIF(E29,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
-      <c r="J29" s="8" t="n"/>
+      <c r="G29" s="13" t="n"/>
+      <c r="H29" s="13" t="n"/>
+      <c r="I29" s="13" t="n"/>
+      <c r="J29" s="13" t="n"/>
       <c r="K29" s="14" t="n"/>
-      <c r="L29" s="8" t="n"/>
+      <c r="L29" s="13" t="n"/>
       <c r="M29" s="14" t="n"/>
-      <c r="N29" s="8" t="n"/>
-      <c r="O29" s="8" t="n"/>
+      <c r="N29" s="13" t="n"/>
+      <c r="O29" s="13" t="n"/>
       <c r="P29" s="14" t="n"/>
-      <c r="Q29" s="8" t="n"/>
+      <c r="Q29" s="13" t="n"/>
       <c r="R29" s="14" t="n"/>
-      <c r="S29" s="8" t="n"/>
+      <c r="S29" s="13" t="n"/>
       <c r="T29" s="14" t="n"/>
-      <c r="U29" s="8" t="n"/>
+      <c r="U29" s="13" t="n"/>
       <c r="V29" s="14" t="n"/>
       <c r="W29" s="14" t="n"/>
       <c r="X29" s="14" t="n"/>
-      <c r="Y29" s="8" t="n"/>
+      <c r="Y29" s="13" t="n"/>
       <c r="Z29" s="16" t="n"/>
-      <c r="AA29" s="8" t="n"/>
-      <c r="AB29" s="8" t="n"/>
+      <c r="AA29" s="13" t="n"/>
+      <c r="AB29" s="13" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n">
+      <c r="A30" s="13" t="n">
         <v>27</v>
       </c>
       <c r="B30" s="14" t="n"/>
       <c r="C30" s="14" t="n"/>
       <c r="D30" s="14" t="n"/>
       <c r="E30" s="15" t="n"/>
-      <c r="F30" s="12">
+      <c r="F30" s="11">
         <f>IF(E30="","",DATEDIF(E30,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8" t="n"/>
-      <c r="J30" s="8" t="n"/>
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="13" t="n"/>
+      <c r="I30" s="13" t="n"/>
+      <c r="J30" s="13" t="n"/>
       <c r="K30" s="14" t="n"/>
-      <c r="L30" s="8" t="n"/>
+      <c r="L30" s="13" t="n"/>
       <c r="M30" s="14" t="n"/>
-      <c r="N30" s="8" t="n"/>
-      <c r="O30" s="8" t="n"/>
+      <c r="N30" s="13" t="n"/>
+      <c r="O30" s="13" t="n"/>
       <c r="P30" s="14" t="n"/>
-      <c r="Q30" s="8" t="n"/>
+      <c r="Q30" s="13" t="n"/>
       <c r="R30" s="14" t="n"/>
-      <c r="S30" s="8" t="n"/>
+      <c r="S30" s="13" t="n"/>
       <c r="T30" s="14" t="n"/>
-      <c r="U30" s="8" t="n"/>
+      <c r="U30" s="13" t="n"/>
       <c r="V30" s="14" t="n"/>
       <c r="W30" s="14" t="n"/>
       <c r="X30" s="14" t="n"/>
-      <c r="Y30" s="8" t="n"/>
+      <c r="Y30" s="13" t="n"/>
       <c r="Z30" s="16" t="n"/>
-      <c r="AA30" s="8" t="n"/>
-      <c r="AB30" s="8" t="n"/>
+      <c r="AA30" s="13" t="n"/>
+      <c r="AB30" s="13" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n">
+      <c r="A31" s="13" t="n">
         <v>28</v>
       </c>
       <c r="B31" s="14" t="n"/>
       <c r="C31" s="14" t="n"/>
       <c r="D31" s="14" t="n"/>
       <c r="E31" s="15" t="n"/>
-      <c r="F31" s="12">
+      <c r="F31" s="11">
         <f>IF(E31="","",DATEDIF(E31,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="n"/>
-      <c r="J31" s="8" t="n"/>
+      <c r="G31" s="13" t="n"/>
+      <c r="H31" s="13" t="n"/>
+      <c r="I31" s="13" t="n"/>
+      <c r="J31" s="13" t="n"/>
       <c r="K31" s="14" t="n"/>
-      <c r="L31" s="8" t="n"/>
+      <c r="L31" s="13" t="n"/>
       <c r="M31" s="14" t="n"/>
-      <c r="N31" s="8" t="n"/>
-      <c r="O31" s="8" t="n"/>
+      <c r="N31" s="13" t="n"/>
+      <c r="O31" s="13" t="n"/>
       <c r="P31" s="14" t="n"/>
-      <c r="Q31" s="8" t="n"/>
+      <c r="Q31" s="13" t="n"/>
       <c r="R31" s="14" t="n"/>
-      <c r="S31" s="8" t="n"/>
+      <c r="S31" s="13" t="n"/>
       <c r="T31" s="14" t="n"/>
-      <c r="U31" s="8" t="n"/>
+      <c r="U31" s="13" t="n"/>
       <c r="V31" s="14" t="n"/>
       <c r="W31" s="14" t="n"/>
       <c r="X31" s="14" t="n"/>
-      <c r="Y31" s="8" t="n"/>
+      <c r="Y31" s="13" t="n"/>
       <c r="Z31" s="16" t="n"/>
-      <c r="AA31" s="8" t="n"/>
-      <c r="AB31" s="8" t="n"/>
+      <c r="AA31" s="13" t="n"/>
+      <c r="AB31" s="13" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n">
+      <c r="A32" s="13" t="n">
         <v>29</v>
       </c>
       <c r="B32" s="14" t="n"/>
       <c r="C32" s="14" t="n"/>
       <c r="D32" s="14" t="n"/>
       <c r="E32" s="15" t="n"/>
-      <c r="F32" s="12">
+      <c r="F32" s="11">
         <f>IF(E32="","",DATEDIF(E32,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="n"/>
-      <c r="J32" s="8" t="n"/>
+      <c r="G32" s="13" t="n"/>
+      <c r="H32" s="13" t="n"/>
+      <c r="I32" s="13" t="n"/>
+      <c r="J32" s="13" t="n"/>
       <c r="K32" s="14" t="n"/>
-      <c r="L32" s="8" t="n"/>
+      <c r="L32" s="13" t="n"/>
       <c r="M32" s="14" t="n"/>
-      <c r="N32" s="8" t="n"/>
-      <c r="O32" s="8" t="n"/>
+      <c r="N32" s="13" t="n"/>
+      <c r="O32" s="13" t="n"/>
       <c r="P32" s="14" t="n"/>
-      <c r="Q32" s="8" t="n"/>
+      <c r="Q32" s="13" t="n"/>
       <c r="R32" s="14" t="n"/>
-      <c r="S32" s="8" t="n"/>
+      <c r="S32" s="13" t="n"/>
       <c r="T32" s="14" t="n"/>
-      <c r="U32" s="8" t="n"/>
+      <c r="U32" s="13" t="n"/>
       <c r="V32" s="14" t="n"/>
       <c r="W32" s="14" t="n"/>
       <c r="X32" s="14" t="n"/>
-      <c r="Y32" s="8" t="n"/>
+      <c r="Y32" s="13" t="n"/>
       <c r="Z32" s="16" t="n"/>
-      <c r="AA32" s="8" t="n"/>
-      <c r="AB32" s="8" t="n"/>
+      <c r="AA32" s="13" t="n"/>
+      <c r="AB32" s="13" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n">
+      <c r="A33" s="13" t="n">
         <v>30</v>
       </c>
       <c r="B33" s="14" t="n"/>
       <c r="C33" s="14" t="n"/>
       <c r="D33" s="14" t="n"/>
       <c r="E33" s="15" t="n"/>
-      <c r="F33" s="12">
+      <c r="F33" s="11">
         <f>IF(E33="","",DATEDIF(E33,TODAY(),"Y"))</f>
         <v/>
       </c>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="n"/>
+      <c r="G33" s="13" t="n"/>
+      <c r="H33" s="13" t="n"/>
+      <c r="I33" s="13" t="n"/>
+      <c r="J33" s="13" t="n"/>
       <c r="K33" s="14" t="n"/>
-      <c r="L33" s="8" t="n"/>
+      <c r="L33" s="13" t="n"/>
       <c r="M33" s="14" t="n"/>
-      <c r="N33" s="8" t="n"/>
-      <c r="O33" s="8" t="n"/>
+      <c r="N33" s="13" t="n"/>
+      <c r="O33" s="13" t="n"/>
       <c r="P33" s="14" t="n"/>
-      <c r="Q33" s="8" t="n"/>
+      <c r="Q33" s="13" t="n"/>
       <c r="R33" s="14" t="n"/>
-      <c r="S33" s="8" t="n"/>
+      <c r="S33" s="13" t="n"/>
       <c r="T33" s="14" t="n"/>
-      <c r="U33" s="8" t="n"/>
+      <c r="U33" s="13" t="n"/>
       <c r="V33" s="14" t="n"/>
       <c r="W33" s="14" t="n"/>
       <c r="X33" s="14" t="n"/>
-      <c r="Y33" s="8" t="n"/>
+      <c r="Y33" s="13" t="n"/>
       <c r="Z33" s="16" t="n"/>
-      <c r="AA33" s="8" t="n"/>
-      <c r="AB33" s="8" t="n"/>
+      <c r="AA33" s="13" t="n"/>
+      <c r="AB33" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6071,18 +6071,18 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <f>IF('01_Apprenants'!B4="","",'01_Apprenants'!B4)</f>
         <v/>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <f>IF('01_Apprenants'!C4="","",'01_Apprenants'!C4)</f>
         <v/>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <f>IF('01_Apprenants'!D4="","",'01_Apprenants'!D4)</f>
         <v/>
       </c>
@@ -6102,18 +6102,18 @@
       <c r="O4" s="14" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <f>IF('01_Apprenants'!B5="","",'01_Apprenants'!B5)</f>
         <v/>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <f>IF('01_Apprenants'!C5="","",'01_Apprenants'!C5)</f>
         <v/>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11">
         <f>IF('01_Apprenants'!D5="","",'01_Apprenants'!D5)</f>
         <v/>
       </c>
@@ -6133,18 +6133,18 @@
       <c r="O5" s="14" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <f>IF('01_Apprenants'!B6="","",'01_Apprenants'!B6)</f>
         <v/>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <f>IF('01_Apprenants'!C6="","",'01_Apprenants'!C6)</f>
         <v/>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="11">
         <f>IF('01_Apprenants'!D6="","",'01_Apprenants'!D6)</f>
         <v/>
       </c>
@@ -6164,18 +6164,18 @@
       <c r="O6" s="14" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <f>IF('01_Apprenants'!B7="","",'01_Apprenants'!B7)</f>
         <v/>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <f>IF('01_Apprenants'!C7="","",'01_Apprenants'!C7)</f>
         <v/>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <f>IF('01_Apprenants'!D7="","",'01_Apprenants'!D7)</f>
         <v/>
       </c>
@@ -6195,18 +6195,18 @@
       <c r="O7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <f>IF('01_Apprenants'!B8="","",'01_Apprenants'!B8)</f>
         <v/>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <f>IF('01_Apprenants'!C8="","",'01_Apprenants'!C8)</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <f>IF('01_Apprenants'!D8="","",'01_Apprenants'!D8)</f>
         <v/>
       </c>
@@ -6226,18 +6226,18 @@
       <c r="O8" s="14" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <f>IF('01_Apprenants'!B9="","",'01_Apprenants'!B9)</f>
         <v/>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="11">
         <f>IF('01_Apprenants'!C9="","",'01_Apprenants'!C9)</f>
         <v/>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11">
         <f>IF('01_Apprenants'!D9="","",'01_Apprenants'!D9)</f>
         <v/>
       </c>
@@ -6257,18 +6257,18 @@
       <c r="O9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <f>IF('01_Apprenants'!B10="","",'01_Apprenants'!B10)</f>
         <v/>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="11">
         <f>IF('01_Apprenants'!C10="","",'01_Apprenants'!C10)</f>
         <v/>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <f>IF('01_Apprenants'!D10="","",'01_Apprenants'!D10)</f>
         <v/>
       </c>
@@ -6288,18 +6288,18 @@
       <c r="O10" s="14" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <f>IF('01_Apprenants'!B11="","",'01_Apprenants'!B11)</f>
         <v/>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="11">
         <f>IF('01_Apprenants'!C11="","",'01_Apprenants'!C11)</f>
         <v/>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <f>IF('01_Apprenants'!D11="","",'01_Apprenants'!D11)</f>
         <v/>
       </c>
@@ -6319,18 +6319,18 @@
       <c r="O11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <f>IF('01_Apprenants'!B12="","",'01_Apprenants'!B12)</f>
         <v/>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="11">
         <f>IF('01_Apprenants'!C12="","",'01_Apprenants'!C12)</f>
         <v/>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <f>IF('01_Apprenants'!D12="","",'01_Apprenants'!D12)</f>
         <v/>
       </c>
@@ -6350,18 +6350,18 @@
       <c r="O12" s="14" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <f>IF('01_Apprenants'!B13="","",'01_Apprenants'!B13)</f>
         <v/>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <f>IF('01_Apprenants'!C13="","",'01_Apprenants'!C13)</f>
         <v/>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <f>IF('01_Apprenants'!D13="","",'01_Apprenants'!D13)</f>
         <v/>
       </c>
@@ -6381,18 +6381,18 @@
       <c r="O13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <f>IF('01_Apprenants'!B14="","",'01_Apprenants'!B14)</f>
         <v/>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <f>IF('01_Apprenants'!C14="","",'01_Apprenants'!C14)</f>
         <v/>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="11">
         <f>IF('01_Apprenants'!D14="","",'01_Apprenants'!D14)</f>
         <v/>
       </c>
@@ -6412,18 +6412,18 @@
       <c r="O14" s="14" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <f>IF('01_Apprenants'!B15="","",'01_Apprenants'!B15)</f>
         <v/>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="11">
         <f>IF('01_Apprenants'!C15="","",'01_Apprenants'!C15)</f>
         <v/>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <f>IF('01_Apprenants'!D15="","",'01_Apprenants'!D15)</f>
         <v/>
       </c>
@@ -6443,18 +6443,18 @@
       <c r="O15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <f>IF('01_Apprenants'!B16="","",'01_Apprenants'!B16)</f>
         <v/>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="11">
         <f>IF('01_Apprenants'!C16="","",'01_Apprenants'!C16)</f>
         <v/>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="11">
         <f>IF('01_Apprenants'!D16="","",'01_Apprenants'!D16)</f>
         <v/>
       </c>
@@ -6474,18 +6474,18 @@
       <c r="O16" s="14" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <f>IF('01_Apprenants'!B17="","",'01_Apprenants'!B17)</f>
         <v/>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <f>IF('01_Apprenants'!C17="","",'01_Apprenants'!C17)</f>
         <v/>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="11">
         <f>IF('01_Apprenants'!D17="","",'01_Apprenants'!D17)</f>
         <v/>
       </c>
@@ -6505,18 +6505,18 @@
       <c r="O17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <f>IF('01_Apprenants'!B18="","",'01_Apprenants'!B18)</f>
         <v/>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="11">
         <f>IF('01_Apprenants'!C18="","",'01_Apprenants'!C18)</f>
         <v/>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="11">
         <f>IF('01_Apprenants'!D18="","",'01_Apprenants'!D18)</f>
         <v/>
       </c>
@@ -6536,18 +6536,18 @@
       <c r="O18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="11">
         <f>IF('01_Apprenants'!B19="","",'01_Apprenants'!B19)</f>
         <v/>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="11">
         <f>IF('01_Apprenants'!C19="","",'01_Apprenants'!C19)</f>
         <v/>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="11">
         <f>IF('01_Apprenants'!D19="","",'01_Apprenants'!D19)</f>
         <v/>
       </c>
@@ -6567,18 +6567,18 @@
       <c r="O19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="11">
         <f>IF('01_Apprenants'!B20="","",'01_Apprenants'!B20)</f>
         <v/>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="11">
         <f>IF('01_Apprenants'!C20="","",'01_Apprenants'!C20)</f>
         <v/>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="11">
         <f>IF('01_Apprenants'!D20="","",'01_Apprenants'!D20)</f>
         <v/>
       </c>
@@ -6598,18 +6598,18 @@
       <c r="O20" s="14" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="11">
         <f>IF('01_Apprenants'!B21="","",'01_Apprenants'!B21)</f>
         <v/>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="11">
         <f>IF('01_Apprenants'!C21="","",'01_Apprenants'!C21)</f>
         <v/>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="11">
         <f>IF('01_Apprenants'!D21="","",'01_Apprenants'!D21)</f>
         <v/>
       </c>
@@ -6629,18 +6629,18 @@
       <c r="O21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="11">
         <f>IF('01_Apprenants'!B22="","",'01_Apprenants'!B22)</f>
         <v/>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="11">
         <f>IF('01_Apprenants'!C22="","",'01_Apprenants'!C22)</f>
         <v/>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="11">
         <f>IF('01_Apprenants'!D22="","",'01_Apprenants'!D22)</f>
         <v/>
       </c>
@@ -6660,18 +6660,18 @@
       <c r="O22" s="14" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="11">
         <f>IF('01_Apprenants'!B23="","",'01_Apprenants'!B23)</f>
         <v/>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="11">
         <f>IF('01_Apprenants'!C23="","",'01_Apprenants'!C23)</f>
         <v/>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="11">
         <f>IF('01_Apprenants'!D23="","",'01_Apprenants'!D23)</f>
         <v/>
       </c>
@@ -6691,18 +6691,18 @@
       <c r="O23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="11">
         <f>IF('01_Apprenants'!B24="","",'01_Apprenants'!B24)</f>
         <v/>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="11">
         <f>IF('01_Apprenants'!C24="","",'01_Apprenants'!C24)</f>
         <v/>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="11">
         <f>IF('01_Apprenants'!D24="","",'01_Apprenants'!D24)</f>
         <v/>
       </c>
@@ -6722,18 +6722,18 @@
       <c r="O24" s="14" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="n">
+      <c r="A25" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="11">
         <f>IF('01_Apprenants'!B25="","",'01_Apprenants'!B25)</f>
         <v/>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="11">
         <f>IF('01_Apprenants'!C25="","",'01_Apprenants'!C25)</f>
         <v/>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="11">
         <f>IF('01_Apprenants'!D25="","",'01_Apprenants'!D25)</f>
         <v/>
       </c>
@@ -6753,18 +6753,18 @@
       <c r="O25" s="14" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="11">
         <f>IF('01_Apprenants'!B26="","",'01_Apprenants'!B26)</f>
         <v/>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="11">
         <f>IF('01_Apprenants'!C26="","",'01_Apprenants'!C26)</f>
         <v/>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="11">
         <f>IF('01_Apprenants'!D26="","",'01_Apprenants'!D26)</f>
         <v/>
       </c>
@@ -6784,18 +6784,18 @@
       <c r="O26" s="14" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n">
+      <c r="A27" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="11">
         <f>IF('01_Apprenants'!B27="","",'01_Apprenants'!B27)</f>
         <v/>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="11">
         <f>IF('01_Apprenants'!C27="","",'01_Apprenants'!C27)</f>
         <v/>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="11">
         <f>IF('01_Apprenants'!D27="","",'01_Apprenants'!D27)</f>
         <v/>
       </c>
@@ -6815,18 +6815,18 @@
       <c r="O27" s="14" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n">
+      <c r="A28" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="11">
         <f>IF('01_Apprenants'!B28="","",'01_Apprenants'!B28)</f>
         <v/>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="11">
         <f>IF('01_Apprenants'!C28="","",'01_Apprenants'!C28)</f>
         <v/>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="11">
         <f>IF('01_Apprenants'!D28="","",'01_Apprenants'!D28)</f>
         <v/>
       </c>
@@ -6846,18 +6846,18 @@
       <c r="O28" s="14" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n">
+      <c r="A29" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="11">
         <f>IF('01_Apprenants'!B29="","",'01_Apprenants'!B29)</f>
         <v/>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="11">
         <f>IF('01_Apprenants'!C29="","",'01_Apprenants'!C29)</f>
         <v/>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="11">
         <f>IF('01_Apprenants'!D29="","",'01_Apprenants'!D29)</f>
         <v/>
       </c>
@@ -6877,18 +6877,18 @@
       <c r="O29" s="14" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n">
+      <c r="A30" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="11">
         <f>IF('01_Apprenants'!B30="","",'01_Apprenants'!B30)</f>
         <v/>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="11">
         <f>IF('01_Apprenants'!C30="","",'01_Apprenants'!C30)</f>
         <v/>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="11">
         <f>IF('01_Apprenants'!D30="","",'01_Apprenants'!D30)</f>
         <v/>
       </c>
@@ -6908,18 +6908,18 @@
       <c r="O30" s="14" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n">
+      <c r="A31" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="11">
         <f>IF('01_Apprenants'!B31="","",'01_Apprenants'!B31)</f>
         <v/>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="11">
         <f>IF('01_Apprenants'!C31="","",'01_Apprenants'!C31)</f>
         <v/>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="11">
         <f>IF('01_Apprenants'!D31="","",'01_Apprenants'!D31)</f>
         <v/>
       </c>
@@ -6939,18 +6939,18 @@
       <c r="O31" s="14" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n">
+      <c r="A32" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="11">
         <f>IF('01_Apprenants'!B32="","",'01_Apprenants'!B32)</f>
         <v/>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="11">
         <f>IF('01_Apprenants'!C32="","",'01_Apprenants'!C32)</f>
         <v/>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="11">
         <f>IF('01_Apprenants'!D32="","",'01_Apprenants'!D32)</f>
         <v/>
       </c>
@@ -6970,18 +6970,18 @@
       <c r="O32" s="14" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n">
+      <c r="A33" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="11">
         <f>IF('01_Apprenants'!B33="","",'01_Apprenants'!B33)</f>
         <v/>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="11">
         <f>IF('01_Apprenants'!C33="","",'01_Apprenants'!C33)</f>
         <v/>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="11">
         <f>IF('01_Apprenants'!D33="","",'01_Apprenants'!D33)</f>
         <v/>
       </c>
@@ -7242,18 +7242,18 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <f>IF('01_Apprenants'!B4="","",'01_Apprenants'!B4)</f>
         <v/>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <f>IF('01_Apprenants'!C4="","",'01_Apprenants'!C4)</f>
         <v/>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <f>IF('01_Apprenants'!D4="","",'01_Apprenants'!D4)</f>
         <v/>
       </c>
@@ -7279,11 +7279,11 @@
       <c r="X4" s="18" t="n"/>
       <c r="Y4" s="18" t="n"/>
       <c r="Z4" s="18" t="n"/>
-      <c r="AA4" s="12">
+      <c r="AA4" s="11">
         <f>IF('01_Apprenants'!B4="","",COUNTIF(E4:Z4,"P*")+COUNTIF(E4:Z4,"R*"))</f>
         <v/>
       </c>
-      <c r="AB4" s="12">
+      <c r="AB4" s="11">
         <f>IF('01_Apprenants'!B4="","",COUNTIF(E4:Z4,"A*"))</f>
         <v/>
       </c>
@@ -7293,18 +7293,18 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <f>IF('01_Apprenants'!B5="","",'01_Apprenants'!B5)</f>
         <v/>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <f>IF('01_Apprenants'!C5="","",'01_Apprenants'!C5)</f>
         <v/>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11">
         <f>IF('01_Apprenants'!D5="","",'01_Apprenants'!D5)</f>
         <v/>
       </c>
@@ -7330,11 +7330,11 @@
       <c r="X5" s="18" t="n"/>
       <c r="Y5" s="18" t="n"/>
       <c r="Z5" s="18" t="n"/>
-      <c r="AA5" s="12">
+      <c r="AA5" s="11">
         <f>IF('01_Apprenants'!B5="","",COUNTIF(E5:Z5,"P*")+COUNTIF(E5:Z5,"R*"))</f>
         <v/>
       </c>
-      <c r="AB5" s="12">
+      <c r="AB5" s="11">
         <f>IF('01_Apprenants'!B5="","",COUNTIF(E5:Z5,"A*"))</f>
         <v/>
       </c>
@@ -7344,18 +7344,18 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <f>IF('01_Apprenants'!B6="","",'01_Apprenants'!B6)</f>
         <v/>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <f>IF('01_Apprenants'!C6="","",'01_Apprenants'!C6)</f>
         <v/>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="11">
         <f>IF('01_Apprenants'!D6="","",'01_Apprenants'!D6)</f>
         <v/>
       </c>
@@ -7381,11 +7381,11 @@
       <c r="X6" s="18" t="n"/>
       <c r="Y6" s="18" t="n"/>
       <c r="Z6" s="18" t="n"/>
-      <c r="AA6" s="12">
+      <c r="AA6" s="11">
         <f>IF('01_Apprenants'!B6="","",COUNTIF(E6:Z6,"P*")+COUNTIF(E6:Z6,"R*"))</f>
         <v/>
       </c>
-      <c r="AB6" s="12">
+      <c r="AB6" s="11">
         <f>IF('01_Apprenants'!B6="","",COUNTIF(E6:Z6,"A*"))</f>
         <v/>
       </c>
@@ -7395,18 +7395,18 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <f>IF('01_Apprenants'!B7="","",'01_Apprenants'!B7)</f>
         <v/>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <f>IF('01_Apprenants'!C7="","",'01_Apprenants'!C7)</f>
         <v/>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <f>IF('01_Apprenants'!D7="","",'01_Apprenants'!D7)</f>
         <v/>
       </c>
@@ -7432,11 +7432,11 @@
       <c r="X7" s="18" t="n"/>
       <c r="Y7" s="18" t="n"/>
       <c r="Z7" s="18" t="n"/>
-      <c r="AA7" s="12">
+      <c r="AA7" s="11">
         <f>IF('01_Apprenants'!B7="","",COUNTIF(E7:Z7,"P*")+COUNTIF(E7:Z7,"R*"))</f>
         <v/>
       </c>
-      <c r="AB7" s="12">
+      <c r="AB7" s="11">
         <f>IF('01_Apprenants'!B7="","",COUNTIF(E7:Z7,"A*"))</f>
         <v/>
       </c>
@@ -7446,18 +7446,18 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <f>IF('01_Apprenants'!B8="","",'01_Apprenants'!B8)</f>
         <v/>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <f>IF('01_Apprenants'!C8="","",'01_Apprenants'!C8)</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <f>IF('01_Apprenants'!D8="","",'01_Apprenants'!D8)</f>
         <v/>
       </c>
@@ -7483,11 +7483,11 @@
       <c r="X8" s="18" t="n"/>
       <c r="Y8" s="18" t="n"/>
       <c r="Z8" s="18" t="n"/>
-      <c r="AA8" s="12">
+      <c r="AA8" s="11">
         <f>IF('01_Apprenants'!B8="","",COUNTIF(E8:Z8,"P*")+COUNTIF(E8:Z8,"R*"))</f>
         <v/>
       </c>
-      <c r="AB8" s="12">
+      <c r="AB8" s="11">
         <f>IF('01_Apprenants'!B8="","",COUNTIF(E8:Z8,"A*"))</f>
         <v/>
       </c>
@@ -7497,18 +7497,18 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <f>IF('01_Apprenants'!B9="","",'01_Apprenants'!B9)</f>
         <v/>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="11">
         <f>IF('01_Apprenants'!C9="","",'01_Apprenants'!C9)</f>
         <v/>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11">
         <f>IF('01_Apprenants'!D9="","",'01_Apprenants'!D9)</f>
         <v/>
       </c>
@@ -7534,11 +7534,11 @@
       <c r="X9" s="18" t="n"/>
       <c r="Y9" s="18" t="n"/>
       <c r="Z9" s="18" t="n"/>
-      <c r="AA9" s="12">
+      <c r="AA9" s="11">
         <f>IF('01_Apprenants'!B9="","",COUNTIF(E9:Z9,"P*")+COUNTIF(E9:Z9,"R*"))</f>
         <v/>
       </c>
-      <c r="AB9" s="12">
+      <c r="AB9" s="11">
         <f>IF('01_Apprenants'!B9="","",COUNTIF(E9:Z9,"A*"))</f>
         <v/>
       </c>
@@ -7548,18 +7548,18 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <f>IF('01_Apprenants'!B10="","",'01_Apprenants'!B10)</f>
         <v/>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="11">
         <f>IF('01_Apprenants'!C10="","",'01_Apprenants'!C10)</f>
         <v/>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <f>IF('01_Apprenants'!D10="","",'01_Apprenants'!D10)</f>
         <v/>
       </c>
@@ -7585,11 +7585,11 @@
       <c r="X10" s="18" t="n"/>
       <c r="Y10" s="18" t="n"/>
       <c r="Z10" s="18" t="n"/>
-      <c r="AA10" s="12">
+      <c r="AA10" s="11">
         <f>IF('01_Apprenants'!B10="","",COUNTIF(E10:Z10,"P*")+COUNTIF(E10:Z10,"R*"))</f>
         <v/>
       </c>
-      <c r="AB10" s="12">
+      <c r="AB10" s="11">
         <f>IF('01_Apprenants'!B10="","",COUNTIF(E10:Z10,"A*"))</f>
         <v/>
       </c>
@@ -7599,18 +7599,18 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <f>IF('01_Apprenants'!B11="","",'01_Apprenants'!B11)</f>
         <v/>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="11">
         <f>IF('01_Apprenants'!C11="","",'01_Apprenants'!C11)</f>
         <v/>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <f>IF('01_Apprenants'!D11="","",'01_Apprenants'!D11)</f>
         <v/>
       </c>
@@ -7636,11 +7636,11 @@
       <c r="X11" s="18" t="n"/>
       <c r="Y11" s="18" t="n"/>
       <c r="Z11" s="18" t="n"/>
-      <c r="AA11" s="12">
+      <c r="AA11" s="11">
         <f>IF('01_Apprenants'!B11="","",COUNTIF(E11:Z11,"P*")+COUNTIF(E11:Z11,"R*"))</f>
         <v/>
       </c>
-      <c r="AB11" s="12">
+      <c r="AB11" s="11">
         <f>IF('01_Apprenants'!B11="","",COUNTIF(E11:Z11,"A*"))</f>
         <v/>
       </c>
@@ -7650,18 +7650,18 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <f>IF('01_Apprenants'!B12="","",'01_Apprenants'!B12)</f>
         <v/>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="11">
         <f>IF('01_Apprenants'!C12="","",'01_Apprenants'!C12)</f>
         <v/>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <f>IF('01_Apprenants'!D12="","",'01_Apprenants'!D12)</f>
         <v/>
       </c>
@@ -7687,11 +7687,11 @@
       <c r="X12" s="18" t="n"/>
       <c r="Y12" s="18" t="n"/>
       <c r="Z12" s="18" t="n"/>
-      <c r="AA12" s="12">
+      <c r="AA12" s="11">
         <f>IF('01_Apprenants'!B12="","",COUNTIF(E12:Z12,"P*")+COUNTIF(E12:Z12,"R*"))</f>
         <v/>
       </c>
-      <c r="AB12" s="12">
+      <c r="AB12" s="11">
         <f>IF('01_Apprenants'!B12="","",COUNTIF(E12:Z12,"A*"))</f>
         <v/>
       </c>
@@ -7701,18 +7701,18 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <f>IF('01_Apprenants'!B13="","",'01_Apprenants'!B13)</f>
         <v/>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <f>IF('01_Apprenants'!C13="","",'01_Apprenants'!C13)</f>
         <v/>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <f>IF('01_Apprenants'!D13="","",'01_Apprenants'!D13)</f>
         <v/>
       </c>
@@ -7738,11 +7738,11 @@
       <c r="X13" s="18" t="n"/>
       <c r="Y13" s="18" t="n"/>
       <c r="Z13" s="18" t="n"/>
-      <c r="AA13" s="12">
+      <c r="AA13" s="11">
         <f>IF('01_Apprenants'!B13="","",COUNTIF(E13:Z13,"P*")+COUNTIF(E13:Z13,"R*"))</f>
         <v/>
       </c>
-      <c r="AB13" s="12">
+      <c r="AB13" s="11">
         <f>IF('01_Apprenants'!B13="","",COUNTIF(E13:Z13,"A*"))</f>
         <v/>
       </c>
@@ -7752,18 +7752,18 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <f>IF('01_Apprenants'!B14="","",'01_Apprenants'!B14)</f>
         <v/>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <f>IF('01_Apprenants'!C14="","",'01_Apprenants'!C14)</f>
         <v/>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="11">
         <f>IF('01_Apprenants'!D14="","",'01_Apprenants'!D14)</f>
         <v/>
       </c>
@@ -7789,11 +7789,11 @@
       <c r="X14" s="18" t="n"/>
       <c r="Y14" s="18" t="n"/>
       <c r="Z14" s="18" t="n"/>
-      <c r="AA14" s="12">
+      <c r="AA14" s="11">
         <f>IF('01_Apprenants'!B14="","",COUNTIF(E14:Z14,"P*")+COUNTIF(E14:Z14,"R*"))</f>
         <v/>
       </c>
-      <c r="AB14" s="12">
+      <c r="AB14" s="11">
         <f>IF('01_Apprenants'!B14="","",COUNTIF(E14:Z14,"A*"))</f>
         <v/>
       </c>
@@ -7803,18 +7803,18 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <f>IF('01_Apprenants'!B15="","",'01_Apprenants'!B15)</f>
         <v/>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="11">
         <f>IF('01_Apprenants'!C15="","",'01_Apprenants'!C15)</f>
         <v/>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <f>IF('01_Apprenants'!D15="","",'01_Apprenants'!D15)</f>
         <v/>
       </c>
@@ -7840,11 +7840,11 @@
       <c r="X15" s="18" t="n"/>
       <c r="Y15" s="18" t="n"/>
       <c r="Z15" s="18" t="n"/>
-      <c r="AA15" s="12">
+      <c r="AA15" s="11">
         <f>IF('01_Apprenants'!B15="","",COUNTIF(E15:Z15,"P*")+COUNTIF(E15:Z15,"R*"))</f>
         <v/>
       </c>
-      <c r="AB15" s="12">
+      <c r="AB15" s="11">
         <f>IF('01_Apprenants'!B15="","",COUNTIF(E15:Z15,"A*"))</f>
         <v/>
       </c>
@@ -7854,18 +7854,18 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <f>IF('01_Apprenants'!B16="","",'01_Apprenants'!B16)</f>
         <v/>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="11">
         <f>IF('01_Apprenants'!C16="","",'01_Apprenants'!C16)</f>
         <v/>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="11">
         <f>IF('01_Apprenants'!D16="","",'01_Apprenants'!D16)</f>
         <v/>
       </c>
@@ -7891,11 +7891,11 @@
       <c r="X16" s="18" t="n"/>
       <c r="Y16" s="18" t="n"/>
       <c r="Z16" s="18" t="n"/>
-      <c r="AA16" s="12">
+      <c r="AA16" s="11">
         <f>IF('01_Apprenants'!B16="","",COUNTIF(E16:Z16,"P*")+COUNTIF(E16:Z16,"R*"))</f>
         <v/>
       </c>
-      <c r="AB16" s="12">
+      <c r="AB16" s="11">
         <f>IF('01_Apprenants'!B16="","",COUNTIF(E16:Z16,"A*"))</f>
         <v/>
       </c>
@@ -7905,18 +7905,18 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <f>IF('01_Apprenants'!B17="","",'01_Apprenants'!B17)</f>
         <v/>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <f>IF('01_Apprenants'!C17="","",'01_Apprenants'!C17)</f>
         <v/>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="11">
         <f>IF('01_Apprenants'!D17="","",'01_Apprenants'!D17)</f>
         <v/>
       </c>
@@ -7942,11 +7942,11 @@
       <c r="X17" s="18" t="n"/>
       <c r="Y17" s="18" t="n"/>
       <c r="Z17" s="18" t="n"/>
-      <c r="AA17" s="12">
+      <c r="AA17" s="11">
         <f>IF('01_Apprenants'!B17="","",COUNTIF(E17:Z17,"P*")+COUNTIF(E17:Z17,"R*"))</f>
         <v/>
       </c>
-      <c r="AB17" s="12">
+      <c r="AB17" s="11">
         <f>IF('01_Apprenants'!B17="","",COUNTIF(E17:Z17,"A*"))</f>
         <v/>
       </c>
@@ -7956,18 +7956,18 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <f>IF('01_Apprenants'!B18="","",'01_Apprenants'!B18)</f>
         <v/>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="11">
         <f>IF('01_Apprenants'!C18="","",'01_Apprenants'!C18)</f>
         <v/>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="11">
         <f>IF('01_Apprenants'!D18="","",'01_Apprenants'!D18)</f>
         <v/>
       </c>
@@ -7993,11 +7993,11 @@
       <c r="X18" s="18" t="n"/>
       <c r="Y18" s="18" t="n"/>
       <c r="Z18" s="18" t="n"/>
-      <c r="AA18" s="12">
+      <c r="AA18" s="11">
         <f>IF('01_Apprenants'!B18="","",COUNTIF(E18:Z18,"P*")+COUNTIF(E18:Z18,"R*"))</f>
         <v/>
       </c>
-      <c r="AB18" s="12">
+      <c r="AB18" s="11">
         <f>IF('01_Apprenants'!B18="","",COUNTIF(E18:Z18,"A*"))</f>
         <v/>
       </c>
@@ -8007,18 +8007,18 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="11">
         <f>IF('01_Apprenants'!B19="","",'01_Apprenants'!B19)</f>
         <v/>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="11">
         <f>IF('01_Apprenants'!C19="","",'01_Apprenants'!C19)</f>
         <v/>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="11">
         <f>IF('01_Apprenants'!D19="","",'01_Apprenants'!D19)</f>
         <v/>
       </c>
@@ -8044,11 +8044,11 @@
       <c r="X19" s="18" t="n"/>
       <c r="Y19" s="18" t="n"/>
       <c r="Z19" s="18" t="n"/>
-      <c r="AA19" s="12">
+      <c r="AA19" s="11">
         <f>IF('01_Apprenants'!B19="","",COUNTIF(E19:Z19,"P*")+COUNTIF(E19:Z19,"R*"))</f>
         <v/>
       </c>
-      <c r="AB19" s="12">
+      <c r="AB19" s="11">
         <f>IF('01_Apprenants'!B19="","",COUNTIF(E19:Z19,"A*"))</f>
         <v/>
       </c>
@@ -8058,18 +8058,18 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="11">
         <f>IF('01_Apprenants'!B20="","",'01_Apprenants'!B20)</f>
         <v/>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="11">
         <f>IF('01_Apprenants'!C20="","",'01_Apprenants'!C20)</f>
         <v/>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="11">
         <f>IF('01_Apprenants'!D20="","",'01_Apprenants'!D20)</f>
         <v/>
       </c>
@@ -8095,11 +8095,11 @@
       <c r="X20" s="18" t="n"/>
       <c r="Y20" s="18" t="n"/>
       <c r="Z20" s="18" t="n"/>
-      <c r="AA20" s="12">
+      <c r="AA20" s="11">
         <f>IF('01_Apprenants'!B20="","",COUNTIF(E20:Z20,"P*")+COUNTIF(E20:Z20,"R*"))</f>
         <v/>
       </c>
-      <c r="AB20" s="12">
+      <c r="AB20" s="11">
         <f>IF('01_Apprenants'!B20="","",COUNTIF(E20:Z20,"A*"))</f>
         <v/>
       </c>
@@ -8109,18 +8109,18 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="11">
         <f>IF('01_Apprenants'!B21="","",'01_Apprenants'!B21)</f>
         <v/>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="11">
         <f>IF('01_Apprenants'!C21="","",'01_Apprenants'!C21)</f>
         <v/>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="11">
         <f>IF('01_Apprenants'!D21="","",'01_Apprenants'!D21)</f>
         <v/>
       </c>
@@ -8146,11 +8146,11 @@
       <c r="X21" s="18" t="n"/>
       <c r="Y21" s="18" t="n"/>
       <c r="Z21" s="18" t="n"/>
-      <c r="AA21" s="12">
+      <c r="AA21" s="11">
         <f>IF('01_Apprenants'!B21="","",COUNTIF(E21:Z21,"P*")+COUNTIF(E21:Z21,"R*"))</f>
         <v/>
       </c>
-      <c r="AB21" s="12">
+      <c r="AB21" s="11">
         <f>IF('01_Apprenants'!B21="","",COUNTIF(E21:Z21,"A*"))</f>
         <v/>
       </c>
@@ -8160,18 +8160,18 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="11">
         <f>IF('01_Apprenants'!B22="","",'01_Apprenants'!B22)</f>
         <v/>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="11">
         <f>IF('01_Apprenants'!C22="","",'01_Apprenants'!C22)</f>
         <v/>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="11">
         <f>IF('01_Apprenants'!D22="","",'01_Apprenants'!D22)</f>
         <v/>
       </c>
@@ -8197,11 +8197,11 @@
       <c r="X22" s="18" t="n"/>
       <c r="Y22" s="18" t="n"/>
       <c r="Z22" s="18" t="n"/>
-      <c r="AA22" s="12">
+      <c r="AA22" s="11">
         <f>IF('01_Apprenants'!B22="","",COUNTIF(E22:Z22,"P*")+COUNTIF(E22:Z22,"R*"))</f>
         <v/>
       </c>
-      <c r="AB22" s="12">
+      <c r="AB22" s="11">
         <f>IF('01_Apprenants'!B22="","",COUNTIF(E22:Z22,"A*"))</f>
         <v/>
       </c>
@@ -8211,18 +8211,18 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="11">
         <f>IF('01_Apprenants'!B23="","",'01_Apprenants'!B23)</f>
         <v/>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="11">
         <f>IF('01_Apprenants'!C23="","",'01_Apprenants'!C23)</f>
         <v/>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="11">
         <f>IF('01_Apprenants'!D23="","",'01_Apprenants'!D23)</f>
         <v/>
       </c>
@@ -8248,11 +8248,11 @@
       <c r="X23" s="18" t="n"/>
       <c r="Y23" s="18" t="n"/>
       <c r="Z23" s="18" t="n"/>
-      <c r="AA23" s="12">
+      <c r="AA23" s="11">
         <f>IF('01_Apprenants'!B23="","",COUNTIF(E23:Z23,"P*")+COUNTIF(E23:Z23,"R*"))</f>
         <v/>
       </c>
-      <c r="AB23" s="12">
+      <c r="AB23" s="11">
         <f>IF('01_Apprenants'!B23="","",COUNTIF(E23:Z23,"A*"))</f>
         <v/>
       </c>
@@ -8262,18 +8262,18 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="11">
         <f>IF('01_Apprenants'!B24="","",'01_Apprenants'!B24)</f>
         <v/>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="11">
         <f>IF('01_Apprenants'!C24="","",'01_Apprenants'!C24)</f>
         <v/>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="11">
         <f>IF('01_Apprenants'!D24="","",'01_Apprenants'!D24)</f>
         <v/>
       </c>
@@ -8299,11 +8299,11 @@
       <c r="X24" s="18" t="n"/>
       <c r="Y24" s="18" t="n"/>
       <c r="Z24" s="18" t="n"/>
-      <c r="AA24" s="12">
+      <c r="AA24" s="11">
         <f>IF('01_Apprenants'!B24="","",COUNTIF(E24:Z24,"P*")+COUNTIF(E24:Z24,"R*"))</f>
         <v/>
       </c>
-      <c r="AB24" s="12">
+      <c r="AB24" s="11">
         <f>IF('01_Apprenants'!B24="","",COUNTIF(E24:Z24,"A*"))</f>
         <v/>
       </c>
@@ -8313,18 +8313,18 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="n">
+      <c r="A25" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="11">
         <f>IF('01_Apprenants'!B25="","",'01_Apprenants'!B25)</f>
         <v/>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="11">
         <f>IF('01_Apprenants'!C25="","",'01_Apprenants'!C25)</f>
         <v/>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="11">
         <f>IF('01_Apprenants'!D25="","",'01_Apprenants'!D25)</f>
         <v/>
       </c>
@@ -8350,11 +8350,11 @@
       <c r="X25" s="18" t="n"/>
       <c r="Y25" s="18" t="n"/>
       <c r="Z25" s="18" t="n"/>
-      <c r="AA25" s="12">
+      <c r="AA25" s="11">
         <f>IF('01_Apprenants'!B25="","",COUNTIF(E25:Z25,"P*")+COUNTIF(E25:Z25,"R*"))</f>
         <v/>
       </c>
-      <c r="AB25" s="12">
+      <c r="AB25" s="11">
         <f>IF('01_Apprenants'!B25="","",COUNTIF(E25:Z25,"A*"))</f>
         <v/>
       </c>
@@ -8364,18 +8364,18 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="11">
         <f>IF('01_Apprenants'!B26="","",'01_Apprenants'!B26)</f>
         <v/>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="11">
         <f>IF('01_Apprenants'!C26="","",'01_Apprenants'!C26)</f>
         <v/>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="11">
         <f>IF('01_Apprenants'!D26="","",'01_Apprenants'!D26)</f>
         <v/>
       </c>
@@ -8401,11 +8401,11 @@
       <c r="X26" s="18" t="n"/>
       <c r="Y26" s="18" t="n"/>
       <c r="Z26" s="18" t="n"/>
-      <c r="AA26" s="12">
+      <c r="AA26" s="11">
         <f>IF('01_Apprenants'!B26="","",COUNTIF(E26:Z26,"P*")+COUNTIF(E26:Z26,"R*"))</f>
         <v/>
       </c>
-      <c r="AB26" s="12">
+      <c r="AB26" s="11">
         <f>IF('01_Apprenants'!B26="","",COUNTIF(E26:Z26,"A*"))</f>
         <v/>
       </c>
@@ -8415,18 +8415,18 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n">
+      <c r="A27" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="11">
         <f>IF('01_Apprenants'!B27="","",'01_Apprenants'!B27)</f>
         <v/>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="11">
         <f>IF('01_Apprenants'!C27="","",'01_Apprenants'!C27)</f>
         <v/>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="11">
         <f>IF('01_Apprenants'!D27="","",'01_Apprenants'!D27)</f>
         <v/>
       </c>
@@ -8452,11 +8452,11 @@
       <c r="X27" s="18" t="n"/>
       <c r="Y27" s="18" t="n"/>
       <c r="Z27" s="18" t="n"/>
-      <c r="AA27" s="12">
+      <c r="AA27" s="11">
         <f>IF('01_Apprenants'!B27="","",COUNTIF(E27:Z27,"P*")+COUNTIF(E27:Z27,"R*"))</f>
         <v/>
       </c>
-      <c r="AB27" s="12">
+      <c r="AB27" s="11">
         <f>IF('01_Apprenants'!B27="","",COUNTIF(E27:Z27,"A*"))</f>
         <v/>
       </c>
@@ -8466,18 +8466,18 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n">
+      <c r="A28" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="11">
         <f>IF('01_Apprenants'!B28="","",'01_Apprenants'!B28)</f>
         <v/>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="11">
         <f>IF('01_Apprenants'!C28="","",'01_Apprenants'!C28)</f>
         <v/>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="11">
         <f>IF('01_Apprenants'!D28="","",'01_Apprenants'!D28)</f>
         <v/>
       </c>
@@ -8503,11 +8503,11 @@
       <c r="X28" s="18" t="n"/>
       <c r="Y28" s="18" t="n"/>
       <c r="Z28" s="18" t="n"/>
-      <c r="AA28" s="12">
+      <c r="AA28" s="11">
         <f>IF('01_Apprenants'!B28="","",COUNTIF(E28:Z28,"P*")+COUNTIF(E28:Z28,"R*"))</f>
         <v/>
       </c>
-      <c r="AB28" s="12">
+      <c r="AB28" s="11">
         <f>IF('01_Apprenants'!B28="","",COUNTIF(E28:Z28,"A*"))</f>
         <v/>
       </c>
@@ -8517,18 +8517,18 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n">
+      <c r="A29" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="11">
         <f>IF('01_Apprenants'!B29="","",'01_Apprenants'!B29)</f>
         <v/>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="11">
         <f>IF('01_Apprenants'!C29="","",'01_Apprenants'!C29)</f>
         <v/>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="11">
         <f>IF('01_Apprenants'!D29="","",'01_Apprenants'!D29)</f>
         <v/>
       </c>
@@ -8554,11 +8554,11 @@
       <c r="X29" s="18" t="n"/>
       <c r="Y29" s="18" t="n"/>
       <c r="Z29" s="18" t="n"/>
-      <c r="AA29" s="12">
+      <c r="AA29" s="11">
         <f>IF('01_Apprenants'!B29="","",COUNTIF(E29:Z29,"P*")+COUNTIF(E29:Z29,"R*"))</f>
         <v/>
       </c>
-      <c r="AB29" s="12">
+      <c r="AB29" s="11">
         <f>IF('01_Apprenants'!B29="","",COUNTIF(E29:Z29,"A*"))</f>
         <v/>
       </c>
@@ -8568,18 +8568,18 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n">
+      <c r="A30" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="11">
         <f>IF('01_Apprenants'!B30="","",'01_Apprenants'!B30)</f>
         <v/>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="11">
         <f>IF('01_Apprenants'!C30="","",'01_Apprenants'!C30)</f>
         <v/>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="11">
         <f>IF('01_Apprenants'!D30="","",'01_Apprenants'!D30)</f>
         <v/>
       </c>
@@ -8605,11 +8605,11 @@
       <c r="X30" s="18" t="n"/>
       <c r="Y30" s="18" t="n"/>
       <c r="Z30" s="18" t="n"/>
-      <c r="AA30" s="12">
+      <c r="AA30" s="11">
         <f>IF('01_Apprenants'!B30="","",COUNTIF(E30:Z30,"P*")+COUNTIF(E30:Z30,"R*"))</f>
         <v/>
       </c>
-      <c r="AB30" s="12">
+      <c r="AB30" s="11">
         <f>IF('01_Apprenants'!B30="","",COUNTIF(E30:Z30,"A*"))</f>
         <v/>
       </c>
@@ -8619,18 +8619,18 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n">
+      <c r="A31" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="11">
         <f>IF('01_Apprenants'!B31="","",'01_Apprenants'!B31)</f>
         <v/>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="11">
         <f>IF('01_Apprenants'!C31="","",'01_Apprenants'!C31)</f>
         <v/>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="11">
         <f>IF('01_Apprenants'!D31="","",'01_Apprenants'!D31)</f>
         <v/>
       </c>
@@ -8656,11 +8656,11 @@
       <c r="X31" s="18" t="n"/>
       <c r="Y31" s="18" t="n"/>
       <c r="Z31" s="18" t="n"/>
-      <c r="AA31" s="12">
+      <c r="AA31" s="11">
         <f>IF('01_Apprenants'!B31="","",COUNTIF(E31:Z31,"P*")+COUNTIF(E31:Z31,"R*"))</f>
         <v/>
       </c>
-      <c r="AB31" s="12">
+      <c r="AB31" s="11">
         <f>IF('01_Apprenants'!B31="","",COUNTIF(E31:Z31,"A*"))</f>
         <v/>
       </c>
@@ -8670,18 +8670,18 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n">
+      <c r="A32" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="11">
         <f>IF('01_Apprenants'!B32="","",'01_Apprenants'!B32)</f>
         <v/>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="11">
         <f>IF('01_Apprenants'!C32="","",'01_Apprenants'!C32)</f>
         <v/>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="11">
         <f>IF('01_Apprenants'!D32="","",'01_Apprenants'!D32)</f>
         <v/>
       </c>
@@ -8707,11 +8707,11 @@
       <c r="X32" s="18" t="n"/>
       <c r="Y32" s="18" t="n"/>
       <c r="Z32" s="18" t="n"/>
-      <c r="AA32" s="12">
+      <c r="AA32" s="11">
         <f>IF('01_Apprenants'!B32="","",COUNTIF(E32:Z32,"P*")+COUNTIF(E32:Z32,"R*"))</f>
         <v/>
       </c>
-      <c r="AB32" s="12">
+      <c r="AB32" s="11">
         <f>IF('01_Apprenants'!B32="","",COUNTIF(E32:Z32,"A*"))</f>
         <v/>
       </c>
@@ -8721,18 +8721,18 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n">
+      <c r="A33" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="11">
         <f>IF('01_Apprenants'!B33="","",'01_Apprenants'!B33)</f>
         <v/>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="11">
         <f>IF('01_Apprenants'!C33="","",'01_Apprenants'!C33)</f>
         <v/>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="11">
         <f>IF('01_Apprenants'!D33="","",'01_Apprenants'!D33)</f>
         <v/>
       </c>
@@ -8758,11 +8758,11 @@
       <c r="X33" s="18" t="n"/>
       <c r="Y33" s="18" t="n"/>
       <c r="Z33" s="18" t="n"/>
-      <c r="AA33" s="12">
+      <c r="AA33" s="11">
         <f>IF('01_Apprenants'!B33="","",COUNTIF(E33:Z33,"P*")+COUNTIF(E33:Z33,"R*"))</f>
         <v/>
       </c>
-      <c r="AB33" s="12">
+      <c r="AB33" s="11">
         <f>IF('01_Apprenants'!B33="","",COUNTIF(E33:Z33,"A*"))</f>
         <v/>
       </c>
@@ -8998,18 +8998,18 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <f>IF('01_Apprenants'!B4="","",'01_Apprenants'!B4)</f>
         <v/>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <f>IF('01_Apprenants'!C4="","",'01_Apprenants'!C4)</f>
         <v/>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <f>IF('01_Apprenants'!D4="","",'01_Apprenants'!D4)</f>
         <v/>
       </c>
@@ -9035,36 +9035,36 @@
       <c r="X4" s="18" t="n"/>
       <c r="Y4" s="18" t="n"/>
       <c r="Z4" s="18" t="n"/>
-      <c r="AA4" s="12">
+      <c r="AA4" s="11">
         <f>IF('01_Apprenants'!B4="","",COUNTIF(E4:Z4,"V*"))</f>
         <v/>
       </c>
-      <c r="AB4" s="12">
+      <c r="AB4" s="11">
         <f>IF('01_Apprenants'!B4="","",COUNTIF(E4:Z4,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC4" s="12">
+      <c r="AC4" s="11">
         <f>IF('01_Apprenants'!B4="","",COUNTIF(E4:Z4,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD4" s="12">
+      <c r="AD4" s="11">
         <f>IF(SUMPRODUCT(((E4:Y4="Partielle")+(E4:Y4="Rien"))*((F4:Z4="Partielle")+(F4:Z4="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <f>IF('01_Apprenants'!B5="","",'01_Apprenants'!B5)</f>
         <v/>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <f>IF('01_Apprenants'!C5="","",'01_Apprenants'!C5)</f>
         <v/>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11">
         <f>IF('01_Apprenants'!D5="","",'01_Apprenants'!D5)</f>
         <v/>
       </c>
@@ -9090,36 +9090,36 @@
       <c r="X5" s="18" t="n"/>
       <c r="Y5" s="18" t="n"/>
       <c r="Z5" s="18" t="n"/>
-      <c r="AA5" s="12">
+      <c r="AA5" s="11">
         <f>IF('01_Apprenants'!B5="","",COUNTIF(E5:Z5,"V*"))</f>
         <v/>
       </c>
-      <c r="AB5" s="12">
+      <c r="AB5" s="11">
         <f>IF('01_Apprenants'!B5="","",COUNTIF(E5:Z5,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC5" s="12">
+      <c r="AC5" s="11">
         <f>IF('01_Apprenants'!B5="","",COUNTIF(E5:Z5,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD5" s="12">
+      <c r="AD5" s="11">
         <f>IF(SUMPRODUCT(((E5:Y5="Partielle")+(E5:Y5="Rien"))*((F5:Z5="Partielle")+(F5:Z5="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <f>IF('01_Apprenants'!B6="","",'01_Apprenants'!B6)</f>
         <v/>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <f>IF('01_Apprenants'!C6="","",'01_Apprenants'!C6)</f>
         <v/>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="11">
         <f>IF('01_Apprenants'!D6="","",'01_Apprenants'!D6)</f>
         <v/>
       </c>
@@ -9145,36 +9145,36 @@
       <c r="X6" s="18" t="n"/>
       <c r="Y6" s="18" t="n"/>
       <c r="Z6" s="18" t="n"/>
-      <c r="AA6" s="12">
+      <c r="AA6" s="11">
         <f>IF('01_Apprenants'!B6="","",COUNTIF(E6:Z6,"V*"))</f>
         <v/>
       </c>
-      <c r="AB6" s="12">
+      <c r="AB6" s="11">
         <f>IF('01_Apprenants'!B6="","",COUNTIF(E6:Z6,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC6" s="12">
+      <c r="AC6" s="11">
         <f>IF('01_Apprenants'!B6="","",COUNTIF(E6:Z6,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD6" s="12">
+      <c r="AD6" s="11">
         <f>IF(SUMPRODUCT(((E6:Y6="Partielle")+(E6:Y6="Rien"))*((F6:Z6="Partielle")+(F6:Z6="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <f>IF('01_Apprenants'!B7="","",'01_Apprenants'!B7)</f>
         <v/>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <f>IF('01_Apprenants'!C7="","",'01_Apprenants'!C7)</f>
         <v/>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <f>IF('01_Apprenants'!D7="","",'01_Apprenants'!D7)</f>
         <v/>
       </c>
@@ -9200,36 +9200,36 @@
       <c r="X7" s="18" t="n"/>
       <c r="Y7" s="18" t="n"/>
       <c r="Z7" s="18" t="n"/>
-      <c r="AA7" s="12">
+      <c r="AA7" s="11">
         <f>IF('01_Apprenants'!B7="","",COUNTIF(E7:Z7,"V*"))</f>
         <v/>
       </c>
-      <c r="AB7" s="12">
+      <c r="AB7" s="11">
         <f>IF('01_Apprenants'!B7="","",COUNTIF(E7:Z7,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC7" s="12">
+      <c r="AC7" s="11">
         <f>IF('01_Apprenants'!B7="","",COUNTIF(E7:Z7,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD7" s="12">
+      <c r="AD7" s="11">
         <f>IF(SUMPRODUCT(((E7:Y7="Partielle")+(E7:Y7="Rien"))*((F7:Z7="Partielle")+(F7:Z7="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <f>IF('01_Apprenants'!B8="","",'01_Apprenants'!B8)</f>
         <v/>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <f>IF('01_Apprenants'!C8="","",'01_Apprenants'!C8)</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <f>IF('01_Apprenants'!D8="","",'01_Apprenants'!D8)</f>
         <v/>
       </c>
@@ -9255,36 +9255,36 @@
       <c r="X8" s="18" t="n"/>
       <c r="Y8" s="18" t="n"/>
       <c r="Z8" s="18" t="n"/>
-      <c r="AA8" s="12">
+      <c r="AA8" s="11">
         <f>IF('01_Apprenants'!B8="","",COUNTIF(E8:Z8,"V*"))</f>
         <v/>
       </c>
-      <c r="AB8" s="12">
+      <c r="AB8" s="11">
         <f>IF('01_Apprenants'!B8="","",COUNTIF(E8:Z8,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC8" s="12">
+      <c r="AC8" s="11">
         <f>IF('01_Apprenants'!B8="","",COUNTIF(E8:Z8,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD8" s="12">
+      <c r="AD8" s="11">
         <f>IF(SUMPRODUCT(((E8:Y8="Partielle")+(E8:Y8="Rien"))*((F8:Z8="Partielle")+(F8:Z8="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <f>IF('01_Apprenants'!B9="","",'01_Apprenants'!B9)</f>
         <v/>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="11">
         <f>IF('01_Apprenants'!C9="","",'01_Apprenants'!C9)</f>
         <v/>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11">
         <f>IF('01_Apprenants'!D9="","",'01_Apprenants'!D9)</f>
         <v/>
       </c>
@@ -9310,36 +9310,36 @@
       <c r="X9" s="18" t="n"/>
       <c r="Y9" s="18" t="n"/>
       <c r="Z9" s="18" t="n"/>
-      <c r="AA9" s="12">
+      <c r="AA9" s="11">
         <f>IF('01_Apprenants'!B9="","",COUNTIF(E9:Z9,"V*"))</f>
         <v/>
       </c>
-      <c r="AB9" s="12">
+      <c r="AB9" s="11">
         <f>IF('01_Apprenants'!B9="","",COUNTIF(E9:Z9,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC9" s="12">
+      <c r="AC9" s="11">
         <f>IF('01_Apprenants'!B9="","",COUNTIF(E9:Z9,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD9" s="12">
+      <c r="AD9" s="11">
         <f>IF(SUMPRODUCT(((E9:Y9="Partielle")+(E9:Y9="Rien"))*((F9:Z9="Partielle")+(F9:Z9="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <f>IF('01_Apprenants'!B10="","",'01_Apprenants'!B10)</f>
         <v/>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="11">
         <f>IF('01_Apprenants'!C10="","",'01_Apprenants'!C10)</f>
         <v/>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <f>IF('01_Apprenants'!D10="","",'01_Apprenants'!D10)</f>
         <v/>
       </c>
@@ -9365,36 +9365,36 @@
       <c r="X10" s="18" t="n"/>
       <c r="Y10" s="18" t="n"/>
       <c r="Z10" s="18" t="n"/>
-      <c r="AA10" s="12">
+      <c r="AA10" s="11">
         <f>IF('01_Apprenants'!B10="","",COUNTIF(E10:Z10,"V*"))</f>
         <v/>
       </c>
-      <c r="AB10" s="12">
+      <c r="AB10" s="11">
         <f>IF('01_Apprenants'!B10="","",COUNTIF(E10:Z10,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC10" s="12">
+      <c r="AC10" s="11">
         <f>IF('01_Apprenants'!B10="","",COUNTIF(E10:Z10,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD10" s="12">
+      <c r="AD10" s="11">
         <f>IF(SUMPRODUCT(((E10:Y10="Partielle")+(E10:Y10="Rien"))*((F10:Z10="Partielle")+(F10:Z10="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <f>IF('01_Apprenants'!B11="","",'01_Apprenants'!B11)</f>
         <v/>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="11">
         <f>IF('01_Apprenants'!C11="","",'01_Apprenants'!C11)</f>
         <v/>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <f>IF('01_Apprenants'!D11="","",'01_Apprenants'!D11)</f>
         <v/>
       </c>
@@ -9420,36 +9420,36 @@
       <c r="X11" s="18" t="n"/>
       <c r="Y11" s="18" t="n"/>
       <c r="Z11" s="18" t="n"/>
-      <c r="AA11" s="12">
+      <c r="AA11" s="11">
         <f>IF('01_Apprenants'!B11="","",COUNTIF(E11:Z11,"V*"))</f>
         <v/>
       </c>
-      <c r="AB11" s="12">
+      <c r="AB11" s="11">
         <f>IF('01_Apprenants'!B11="","",COUNTIF(E11:Z11,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC11" s="12">
+      <c r="AC11" s="11">
         <f>IF('01_Apprenants'!B11="","",COUNTIF(E11:Z11,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD11" s="12">
+      <c r="AD11" s="11">
         <f>IF(SUMPRODUCT(((E11:Y11="Partielle")+(E11:Y11="Rien"))*((F11:Z11="Partielle")+(F11:Z11="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <f>IF('01_Apprenants'!B12="","",'01_Apprenants'!B12)</f>
         <v/>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="11">
         <f>IF('01_Apprenants'!C12="","",'01_Apprenants'!C12)</f>
         <v/>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <f>IF('01_Apprenants'!D12="","",'01_Apprenants'!D12)</f>
         <v/>
       </c>
@@ -9475,36 +9475,36 @@
       <c r="X12" s="18" t="n"/>
       <c r="Y12" s="18" t="n"/>
       <c r="Z12" s="18" t="n"/>
-      <c r="AA12" s="12">
+      <c r="AA12" s="11">
         <f>IF('01_Apprenants'!B12="","",COUNTIF(E12:Z12,"V*"))</f>
         <v/>
       </c>
-      <c r="AB12" s="12">
+      <c r="AB12" s="11">
         <f>IF('01_Apprenants'!B12="","",COUNTIF(E12:Z12,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC12" s="12">
+      <c r="AC12" s="11">
         <f>IF('01_Apprenants'!B12="","",COUNTIF(E12:Z12,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD12" s="12">
+      <c r="AD12" s="11">
         <f>IF(SUMPRODUCT(((E12:Y12="Partielle")+(E12:Y12="Rien"))*((F12:Z12="Partielle")+(F12:Z12="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <f>IF('01_Apprenants'!B13="","",'01_Apprenants'!B13)</f>
         <v/>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <f>IF('01_Apprenants'!C13="","",'01_Apprenants'!C13)</f>
         <v/>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <f>IF('01_Apprenants'!D13="","",'01_Apprenants'!D13)</f>
         <v/>
       </c>
@@ -9530,36 +9530,36 @@
       <c r="X13" s="18" t="n"/>
       <c r="Y13" s="18" t="n"/>
       <c r="Z13" s="18" t="n"/>
-      <c r="AA13" s="12">
+      <c r="AA13" s="11">
         <f>IF('01_Apprenants'!B13="","",COUNTIF(E13:Z13,"V*"))</f>
         <v/>
       </c>
-      <c r="AB13" s="12">
+      <c r="AB13" s="11">
         <f>IF('01_Apprenants'!B13="","",COUNTIF(E13:Z13,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC13" s="12">
+      <c r="AC13" s="11">
         <f>IF('01_Apprenants'!B13="","",COUNTIF(E13:Z13,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD13" s="12">
+      <c r="AD13" s="11">
         <f>IF(SUMPRODUCT(((E13:Y13="Partielle")+(E13:Y13="Rien"))*((F13:Z13="Partielle")+(F13:Z13="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <f>IF('01_Apprenants'!B14="","",'01_Apprenants'!B14)</f>
         <v/>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <f>IF('01_Apprenants'!C14="","",'01_Apprenants'!C14)</f>
         <v/>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="11">
         <f>IF('01_Apprenants'!D14="","",'01_Apprenants'!D14)</f>
         <v/>
       </c>
@@ -9585,36 +9585,36 @@
       <c r="X14" s="18" t="n"/>
       <c r="Y14" s="18" t="n"/>
       <c r="Z14" s="18" t="n"/>
-      <c r="AA14" s="12">
+      <c r="AA14" s="11">
         <f>IF('01_Apprenants'!B14="","",COUNTIF(E14:Z14,"V*"))</f>
         <v/>
       </c>
-      <c r="AB14" s="12">
+      <c r="AB14" s="11">
         <f>IF('01_Apprenants'!B14="","",COUNTIF(E14:Z14,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC14" s="12">
+      <c r="AC14" s="11">
         <f>IF('01_Apprenants'!B14="","",COUNTIF(E14:Z14,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD14" s="12">
+      <c r="AD14" s="11">
         <f>IF(SUMPRODUCT(((E14:Y14="Partielle")+(E14:Y14="Rien"))*((F14:Z14="Partielle")+(F14:Z14="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <f>IF('01_Apprenants'!B15="","",'01_Apprenants'!B15)</f>
         <v/>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="11">
         <f>IF('01_Apprenants'!C15="","",'01_Apprenants'!C15)</f>
         <v/>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <f>IF('01_Apprenants'!D15="","",'01_Apprenants'!D15)</f>
         <v/>
       </c>
@@ -9640,36 +9640,36 @@
       <c r="X15" s="18" t="n"/>
       <c r="Y15" s="18" t="n"/>
       <c r="Z15" s="18" t="n"/>
-      <c r="AA15" s="12">
+      <c r="AA15" s="11">
         <f>IF('01_Apprenants'!B15="","",COUNTIF(E15:Z15,"V*"))</f>
         <v/>
       </c>
-      <c r="AB15" s="12">
+      <c r="AB15" s="11">
         <f>IF('01_Apprenants'!B15="","",COUNTIF(E15:Z15,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC15" s="12">
+      <c r="AC15" s="11">
         <f>IF('01_Apprenants'!B15="","",COUNTIF(E15:Z15,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD15" s="12">
+      <c r="AD15" s="11">
         <f>IF(SUMPRODUCT(((E15:Y15="Partielle")+(E15:Y15="Rien"))*((F15:Z15="Partielle")+(F15:Z15="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <f>IF('01_Apprenants'!B16="","",'01_Apprenants'!B16)</f>
         <v/>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="11">
         <f>IF('01_Apprenants'!C16="","",'01_Apprenants'!C16)</f>
         <v/>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="11">
         <f>IF('01_Apprenants'!D16="","",'01_Apprenants'!D16)</f>
         <v/>
       </c>
@@ -9695,36 +9695,36 @@
       <c r="X16" s="18" t="n"/>
       <c r="Y16" s="18" t="n"/>
       <c r="Z16" s="18" t="n"/>
-      <c r="AA16" s="12">
+      <c r="AA16" s="11">
         <f>IF('01_Apprenants'!B16="","",COUNTIF(E16:Z16,"V*"))</f>
         <v/>
       </c>
-      <c r="AB16" s="12">
+      <c r="AB16" s="11">
         <f>IF('01_Apprenants'!B16="","",COUNTIF(E16:Z16,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC16" s="12">
+      <c r="AC16" s="11">
         <f>IF('01_Apprenants'!B16="","",COUNTIF(E16:Z16,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD16" s="12">
+      <c r="AD16" s="11">
         <f>IF(SUMPRODUCT(((E16:Y16="Partielle")+(E16:Y16="Rien"))*((F16:Z16="Partielle")+(F16:Z16="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <f>IF('01_Apprenants'!B17="","",'01_Apprenants'!B17)</f>
         <v/>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <f>IF('01_Apprenants'!C17="","",'01_Apprenants'!C17)</f>
         <v/>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="11">
         <f>IF('01_Apprenants'!D17="","",'01_Apprenants'!D17)</f>
         <v/>
       </c>
@@ -9750,36 +9750,36 @@
       <c r="X17" s="18" t="n"/>
       <c r="Y17" s="18" t="n"/>
       <c r="Z17" s="18" t="n"/>
-      <c r="AA17" s="12">
+      <c r="AA17" s="11">
         <f>IF('01_Apprenants'!B17="","",COUNTIF(E17:Z17,"V*"))</f>
         <v/>
       </c>
-      <c r="AB17" s="12">
+      <c r="AB17" s="11">
         <f>IF('01_Apprenants'!B17="","",COUNTIF(E17:Z17,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC17" s="12">
+      <c r="AC17" s="11">
         <f>IF('01_Apprenants'!B17="","",COUNTIF(E17:Z17,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD17" s="12">
+      <c r="AD17" s="11">
         <f>IF(SUMPRODUCT(((E17:Y17="Partielle")+(E17:Y17="Rien"))*((F17:Z17="Partielle")+(F17:Z17="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <f>IF('01_Apprenants'!B18="","",'01_Apprenants'!B18)</f>
         <v/>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="11">
         <f>IF('01_Apprenants'!C18="","",'01_Apprenants'!C18)</f>
         <v/>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="11">
         <f>IF('01_Apprenants'!D18="","",'01_Apprenants'!D18)</f>
         <v/>
       </c>
@@ -9805,36 +9805,36 @@
       <c r="X18" s="18" t="n"/>
       <c r="Y18" s="18" t="n"/>
       <c r="Z18" s="18" t="n"/>
-      <c r="AA18" s="12">
+      <c r="AA18" s="11">
         <f>IF('01_Apprenants'!B18="","",COUNTIF(E18:Z18,"V*"))</f>
         <v/>
       </c>
-      <c r="AB18" s="12">
+      <c r="AB18" s="11">
         <f>IF('01_Apprenants'!B18="","",COUNTIF(E18:Z18,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC18" s="12">
+      <c r="AC18" s="11">
         <f>IF('01_Apprenants'!B18="","",COUNTIF(E18:Z18,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD18" s="12">
+      <c r="AD18" s="11">
         <f>IF(SUMPRODUCT(((E18:Y18="Partielle")+(E18:Y18="Rien"))*((F18:Z18="Partielle")+(F18:Z18="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="11">
         <f>IF('01_Apprenants'!B19="","",'01_Apprenants'!B19)</f>
         <v/>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="11">
         <f>IF('01_Apprenants'!C19="","",'01_Apprenants'!C19)</f>
         <v/>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="11">
         <f>IF('01_Apprenants'!D19="","",'01_Apprenants'!D19)</f>
         <v/>
       </c>
@@ -9860,36 +9860,36 @@
       <c r="X19" s="18" t="n"/>
       <c r="Y19" s="18" t="n"/>
       <c r="Z19" s="18" t="n"/>
-      <c r="AA19" s="12">
+      <c r="AA19" s="11">
         <f>IF('01_Apprenants'!B19="","",COUNTIF(E19:Z19,"V*"))</f>
         <v/>
       </c>
-      <c r="AB19" s="12">
+      <c r="AB19" s="11">
         <f>IF('01_Apprenants'!B19="","",COUNTIF(E19:Z19,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC19" s="12">
+      <c r="AC19" s="11">
         <f>IF('01_Apprenants'!B19="","",COUNTIF(E19:Z19,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD19" s="12">
+      <c r="AD19" s="11">
         <f>IF(SUMPRODUCT(((E19:Y19="Partielle")+(E19:Y19="Rien"))*((F19:Z19="Partielle")+(F19:Z19="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="11">
         <f>IF('01_Apprenants'!B20="","",'01_Apprenants'!B20)</f>
         <v/>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="11">
         <f>IF('01_Apprenants'!C20="","",'01_Apprenants'!C20)</f>
         <v/>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="11">
         <f>IF('01_Apprenants'!D20="","",'01_Apprenants'!D20)</f>
         <v/>
       </c>
@@ -9915,36 +9915,36 @@
       <c r="X20" s="18" t="n"/>
       <c r="Y20" s="18" t="n"/>
       <c r="Z20" s="18" t="n"/>
-      <c r="AA20" s="12">
+      <c r="AA20" s="11">
         <f>IF('01_Apprenants'!B20="","",COUNTIF(E20:Z20,"V*"))</f>
         <v/>
       </c>
-      <c r="AB20" s="12">
+      <c r="AB20" s="11">
         <f>IF('01_Apprenants'!B20="","",COUNTIF(E20:Z20,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC20" s="12">
+      <c r="AC20" s="11">
         <f>IF('01_Apprenants'!B20="","",COUNTIF(E20:Z20,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD20" s="12">
+      <c r="AD20" s="11">
         <f>IF(SUMPRODUCT(((E20:Y20="Partielle")+(E20:Y20="Rien"))*((F20:Z20="Partielle")+(F20:Z20="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="11">
         <f>IF('01_Apprenants'!B21="","",'01_Apprenants'!B21)</f>
         <v/>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="11">
         <f>IF('01_Apprenants'!C21="","",'01_Apprenants'!C21)</f>
         <v/>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="11">
         <f>IF('01_Apprenants'!D21="","",'01_Apprenants'!D21)</f>
         <v/>
       </c>
@@ -9970,36 +9970,36 @@
       <c r="X21" s="18" t="n"/>
       <c r="Y21" s="18" t="n"/>
       <c r="Z21" s="18" t="n"/>
-      <c r="AA21" s="12">
+      <c r="AA21" s="11">
         <f>IF('01_Apprenants'!B21="","",COUNTIF(E21:Z21,"V*"))</f>
         <v/>
       </c>
-      <c r="AB21" s="12">
+      <c r="AB21" s="11">
         <f>IF('01_Apprenants'!B21="","",COUNTIF(E21:Z21,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC21" s="12">
+      <c r="AC21" s="11">
         <f>IF('01_Apprenants'!B21="","",COUNTIF(E21:Z21,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD21" s="12">
+      <c r="AD21" s="11">
         <f>IF(SUMPRODUCT(((E21:Y21="Partielle")+(E21:Y21="Rien"))*((F21:Z21="Partielle")+(F21:Z21="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="11">
         <f>IF('01_Apprenants'!B22="","",'01_Apprenants'!B22)</f>
         <v/>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="11">
         <f>IF('01_Apprenants'!C22="","",'01_Apprenants'!C22)</f>
         <v/>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="11">
         <f>IF('01_Apprenants'!D22="","",'01_Apprenants'!D22)</f>
         <v/>
       </c>
@@ -10025,36 +10025,36 @@
       <c r="X22" s="18" t="n"/>
       <c r="Y22" s="18" t="n"/>
       <c r="Z22" s="18" t="n"/>
-      <c r="AA22" s="12">
+      <c r="AA22" s="11">
         <f>IF('01_Apprenants'!B22="","",COUNTIF(E22:Z22,"V*"))</f>
         <v/>
       </c>
-      <c r="AB22" s="12">
+      <c r="AB22" s="11">
         <f>IF('01_Apprenants'!B22="","",COUNTIF(E22:Z22,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC22" s="12">
+      <c r="AC22" s="11">
         <f>IF('01_Apprenants'!B22="","",COUNTIF(E22:Z22,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD22" s="12">
+      <c r="AD22" s="11">
         <f>IF(SUMPRODUCT(((E22:Y22="Partielle")+(E22:Y22="Rien"))*((F22:Z22="Partielle")+(F22:Z22="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="11">
         <f>IF('01_Apprenants'!B23="","",'01_Apprenants'!B23)</f>
         <v/>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="11">
         <f>IF('01_Apprenants'!C23="","",'01_Apprenants'!C23)</f>
         <v/>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="11">
         <f>IF('01_Apprenants'!D23="","",'01_Apprenants'!D23)</f>
         <v/>
       </c>
@@ -10080,36 +10080,36 @@
       <c r="X23" s="18" t="n"/>
       <c r="Y23" s="18" t="n"/>
       <c r="Z23" s="18" t="n"/>
-      <c r="AA23" s="12">
+      <c r="AA23" s="11">
         <f>IF('01_Apprenants'!B23="","",COUNTIF(E23:Z23,"V*"))</f>
         <v/>
       </c>
-      <c r="AB23" s="12">
+      <c r="AB23" s="11">
         <f>IF('01_Apprenants'!B23="","",COUNTIF(E23:Z23,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC23" s="12">
+      <c r="AC23" s="11">
         <f>IF('01_Apprenants'!B23="","",COUNTIF(E23:Z23,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD23" s="12">
+      <c r="AD23" s="11">
         <f>IF(SUMPRODUCT(((E23:Y23="Partielle")+(E23:Y23="Rien"))*((F23:Z23="Partielle")+(F23:Z23="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="11">
         <f>IF('01_Apprenants'!B24="","",'01_Apprenants'!B24)</f>
         <v/>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="11">
         <f>IF('01_Apprenants'!C24="","",'01_Apprenants'!C24)</f>
         <v/>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="11">
         <f>IF('01_Apprenants'!D24="","",'01_Apprenants'!D24)</f>
         <v/>
       </c>
@@ -10135,36 +10135,36 @@
       <c r="X24" s="18" t="n"/>
       <c r="Y24" s="18" t="n"/>
       <c r="Z24" s="18" t="n"/>
-      <c r="AA24" s="12">
+      <c r="AA24" s="11">
         <f>IF('01_Apprenants'!B24="","",COUNTIF(E24:Z24,"V*"))</f>
         <v/>
       </c>
-      <c r="AB24" s="12">
+      <c r="AB24" s="11">
         <f>IF('01_Apprenants'!B24="","",COUNTIF(E24:Z24,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC24" s="12">
+      <c r="AC24" s="11">
         <f>IF('01_Apprenants'!B24="","",COUNTIF(E24:Z24,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD24" s="12">
+      <c r="AD24" s="11">
         <f>IF(SUMPRODUCT(((E24:Y24="Partielle")+(E24:Y24="Rien"))*((F24:Z24="Partielle")+(F24:Z24="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="n">
+      <c r="A25" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="11">
         <f>IF('01_Apprenants'!B25="","",'01_Apprenants'!B25)</f>
         <v/>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="11">
         <f>IF('01_Apprenants'!C25="","",'01_Apprenants'!C25)</f>
         <v/>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="11">
         <f>IF('01_Apprenants'!D25="","",'01_Apprenants'!D25)</f>
         <v/>
       </c>
@@ -10190,36 +10190,36 @@
       <c r="X25" s="18" t="n"/>
       <c r="Y25" s="18" t="n"/>
       <c r="Z25" s="18" t="n"/>
-      <c r="AA25" s="12">
+      <c r="AA25" s="11">
         <f>IF('01_Apprenants'!B25="","",COUNTIF(E25:Z25,"V*"))</f>
         <v/>
       </c>
-      <c r="AB25" s="12">
+      <c r="AB25" s="11">
         <f>IF('01_Apprenants'!B25="","",COUNTIF(E25:Z25,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC25" s="12">
+      <c r="AC25" s="11">
         <f>IF('01_Apprenants'!B25="","",COUNTIF(E25:Z25,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD25" s="12">
+      <c r="AD25" s="11">
         <f>IF(SUMPRODUCT(((E25:Y25="Partielle")+(E25:Y25="Rien"))*((F25:Z25="Partielle")+(F25:Z25="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="11">
         <f>IF('01_Apprenants'!B26="","",'01_Apprenants'!B26)</f>
         <v/>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="11">
         <f>IF('01_Apprenants'!C26="","",'01_Apprenants'!C26)</f>
         <v/>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="11">
         <f>IF('01_Apprenants'!D26="","",'01_Apprenants'!D26)</f>
         <v/>
       </c>
@@ -10245,36 +10245,36 @@
       <c r="X26" s="18" t="n"/>
       <c r="Y26" s="18" t="n"/>
       <c r="Z26" s="18" t="n"/>
-      <c r="AA26" s="12">
+      <c r="AA26" s="11">
         <f>IF('01_Apprenants'!B26="","",COUNTIF(E26:Z26,"V*"))</f>
         <v/>
       </c>
-      <c r="AB26" s="12">
+      <c r="AB26" s="11">
         <f>IF('01_Apprenants'!B26="","",COUNTIF(E26:Z26,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC26" s="12">
+      <c r="AC26" s="11">
         <f>IF('01_Apprenants'!B26="","",COUNTIF(E26:Z26,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD26" s="12">
+      <c r="AD26" s="11">
         <f>IF(SUMPRODUCT(((E26:Y26="Partielle")+(E26:Y26="Rien"))*((F26:Z26="Partielle")+(F26:Z26="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n">
+      <c r="A27" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="11">
         <f>IF('01_Apprenants'!B27="","",'01_Apprenants'!B27)</f>
         <v/>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="11">
         <f>IF('01_Apprenants'!C27="","",'01_Apprenants'!C27)</f>
         <v/>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="11">
         <f>IF('01_Apprenants'!D27="","",'01_Apprenants'!D27)</f>
         <v/>
       </c>
@@ -10300,36 +10300,36 @@
       <c r="X27" s="18" t="n"/>
       <c r="Y27" s="18" t="n"/>
       <c r="Z27" s="18" t="n"/>
-      <c r="AA27" s="12">
+      <c r="AA27" s="11">
         <f>IF('01_Apprenants'!B27="","",COUNTIF(E27:Z27,"V*"))</f>
         <v/>
       </c>
-      <c r="AB27" s="12">
+      <c r="AB27" s="11">
         <f>IF('01_Apprenants'!B27="","",COUNTIF(E27:Z27,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC27" s="12">
+      <c r="AC27" s="11">
         <f>IF('01_Apprenants'!B27="","",COUNTIF(E27:Z27,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD27" s="12">
+      <c r="AD27" s="11">
         <f>IF(SUMPRODUCT(((E27:Y27="Partielle")+(E27:Y27="Rien"))*((F27:Z27="Partielle")+(F27:Z27="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n">
+      <c r="A28" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="11">
         <f>IF('01_Apprenants'!B28="","",'01_Apprenants'!B28)</f>
         <v/>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="11">
         <f>IF('01_Apprenants'!C28="","",'01_Apprenants'!C28)</f>
         <v/>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="11">
         <f>IF('01_Apprenants'!D28="","",'01_Apprenants'!D28)</f>
         <v/>
       </c>
@@ -10355,36 +10355,36 @@
       <c r="X28" s="18" t="n"/>
       <c r="Y28" s="18" t="n"/>
       <c r="Z28" s="18" t="n"/>
-      <c r="AA28" s="12">
+      <c r="AA28" s="11">
         <f>IF('01_Apprenants'!B28="","",COUNTIF(E28:Z28,"V*"))</f>
         <v/>
       </c>
-      <c r="AB28" s="12">
+      <c r="AB28" s="11">
         <f>IF('01_Apprenants'!B28="","",COUNTIF(E28:Z28,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC28" s="12">
+      <c r="AC28" s="11">
         <f>IF('01_Apprenants'!B28="","",COUNTIF(E28:Z28,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD28" s="12">
+      <c r="AD28" s="11">
         <f>IF(SUMPRODUCT(((E28:Y28="Partielle")+(E28:Y28="Rien"))*((F28:Z28="Partielle")+(F28:Z28="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n">
+      <c r="A29" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="11">
         <f>IF('01_Apprenants'!B29="","",'01_Apprenants'!B29)</f>
         <v/>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="11">
         <f>IF('01_Apprenants'!C29="","",'01_Apprenants'!C29)</f>
         <v/>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="11">
         <f>IF('01_Apprenants'!D29="","",'01_Apprenants'!D29)</f>
         <v/>
       </c>
@@ -10410,36 +10410,36 @@
       <c r="X29" s="18" t="n"/>
       <c r="Y29" s="18" t="n"/>
       <c r="Z29" s="18" t="n"/>
-      <c r="AA29" s="12">
+      <c r="AA29" s="11">
         <f>IF('01_Apprenants'!B29="","",COUNTIF(E29:Z29,"V*"))</f>
         <v/>
       </c>
-      <c r="AB29" s="12">
+      <c r="AB29" s="11">
         <f>IF('01_Apprenants'!B29="","",COUNTIF(E29:Z29,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC29" s="12">
+      <c r="AC29" s="11">
         <f>IF('01_Apprenants'!B29="","",COUNTIF(E29:Z29,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD29" s="12">
+      <c r="AD29" s="11">
         <f>IF(SUMPRODUCT(((E29:Y29="Partielle")+(E29:Y29="Rien"))*((F29:Z29="Partielle")+(F29:Z29="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n">
+      <c r="A30" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="11">
         <f>IF('01_Apprenants'!B30="","",'01_Apprenants'!B30)</f>
         <v/>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="11">
         <f>IF('01_Apprenants'!C30="","",'01_Apprenants'!C30)</f>
         <v/>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="11">
         <f>IF('01_Apprenants'!D30="","",'01_Apprenants'!D30)</f>
         <v/>
       </c>
@@ -10465,36 +10465,36 @@
       <c r="X30" s="18" t="n"/>
       <c r="Y30" s="18" t="n"/>
       <c r="Z30" s="18" t="n"/>
-      <c r="AA30" s="12">
+      <c r="AA30" s="11">
         <f>IF('01_Apprenants'!B30="","",COUNTIF(E30:Z30,"V*"))</f>
         <v/>
       </c>
-      <c r="AB30" s="12">
+      <c r="AB30" s="11">
         <f>IF('01_Apprenants'!B30="","",COUNTIF(E30:Z30,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC30" s="12">
+      <c r="AC30" s="11">
         <f>IF('01_Apprenants'!B30="","",COUNTIF(E30:Z30,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD30" s="12">
+      <c r="AD30" s="11">
         <f>IF(SUMPRODUCT(((E30:Y30="Partielle")+(E30:Y30="Rien"))*((F30:Z30="Partielle")+(F30:Z30="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n">
+      <c r="A31" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="11">
         <f>IF('01_Apprenants'!B31="","",'01_Apprenants'!B31)</f>
         <v/>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="11">
         <f>IF('01_Apprenants'!C31="","",'01_Apprenants'!C31)</f>
         <v/>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="11">
         <f>IF('01_Apprenants'!D31="","",'01_Apprenants'!D31)</f>
         <v/>
       </c>
@@ -10520,36 +10520,36 @@
       <c r="X31" s="18" t="n"/>
       <c r="Y31" s="18" t="n"/>
       <c r="Z31" s="18" t="n"/>
-      <c r="AA31" s="12">
+      <c r="AA31" s="11">
         <f>IF('01_Apprenants'!B31="","",COUNTIF(E31:Z31,"V*"))</f>
         <v/>
       </c>
-      <c r="AB31" s="12">
+      <c r="AB31" s="11">
         <f>IF('01_Apprenants'!B31="","",COUNTIF(E31:Z31,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC31" s="12">
+      <c r="AC31" s="11">
         <f>IF('01_Apprenants'!B31="","",COUNTIF(E31:Z31,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD31" s="12">
+      <c r="AD31" s="11">
         <f>IF(SUMPRODUCT(((E31:Y31="Partielle")+(E31:Y31="Rien"))*((F31:Z31="Partielle")+(F31:Z31="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n">
+      <c r="A32" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="11">
         <f>IF('01_Apprenants'!B32="","",'01_Apprenants'!B32)</f>
         <v/>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="11">
         <f>IF('01_Apprenants'!C32="","",'01_Apprenants'!C32)</f>
         <v/>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="11">
         <f>IF('01_Apprenants'!D32="","",'01_Apprenants'!D32)</f>
         <v/>
       </c>
@@ -10575,36 +10575,36 @@
       <c r="X32" s="18" t="n"/>
       <c r="Y32" s="18" t="n"/>
       <c r="Z32" s="18" t="n"/>
-      <c r="AA32" s="12">
+      <c r="AA32" s="11">
         <f>IF('01_Apprenants'!B32="","",COUNTIF(E32:Z32,"V*"))</f>
         <v/>
       </c>
-      <c r="AB32" s="12">
+      <c r="AB32" s="11">
         <f>IF('01_Apprenants'!B32="","",COUNTIF(E32:Z32,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC32" s="12">
+      <c r="AC32" s="11">
         <f>IF('01_Apprenants'!B32="","",COUNTIF(E32:Z32,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD32" s="12">
+      <c r="AD32" s="11">
         <f>IF(SUMPRODUCT(((E32:Y32="Partielle")+(E32:Y32="Rien"))*((F32:Z32="Partielle")+(F32:Z32="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n">
+      <c r="A33" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="11">
         <f>IF('01_Apprenants'!B33="","",'01_Apprenants'!B33)</f>
         <v/>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="11">
         <f>IF('01_Apprenants'!C33="","",'01_Apprenants'!C33)</f>
         <v/>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="11">
         <f>IF('01_Apprenants'!D33="","",'01_Apprenants'!D33)</f>
         <v/>
       </c>
@@ -10630,19 +10630,19 @@
       <c r="X33" s="18" t="n"/>
       <c r="Y33" s="18" t="n"/>
       <c r="Z33" s="18" t="n"/>
-      <c r="AA33" s="12">
+      <c r="AA33" s="11">
         <f>IF('01_Apprenants'!B33="","",COUNTIF(E33:Z33,"V*"))</f>
         <v/>
       </c>
-      <c r="AB33" s="12">
+      <c r="AB33" s="11">
         <f>IF('01_Apprenants'!B33="","",COUNTIF(E33:Z33,"Partielle"))</f>
         <v/>
       </c>
-      <c r="AC33" s="12">
+      <c r="AC33" s="11">
         <f>IF('01_Apprenants'!B33="","",COUNTIF(E33:Z33,"Rien"))</f>
         <v/>
       </c>
-      <c r="AD33" s="12">
+      <c r="AD33" s="11">
         <f>IF(SUMPRODUCT(((E33:Y33="Partielle")+(E33:Y33="Rien"))*((F33:Z33="Partielle")+(F33:Z33="Rien")))&gt;0,"OUI","")</f>
         <v/>
       </c>
@@ -13280,18 +13280,18 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <f>IF('01_Apprenants'!B4="","",'01_Apprenants'!B4)</f>
         <v/>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <f>IF('01_Apprenants'!C4="","",'01_Apprenants'!C4)</f>
         <v/>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <f>IF('01_Apprenants'!D4="","",'01_Apprenants'!D4)</f>
         <v/>
       </c>
@@ -13308,7 +13308,7 @@
       <c r="O4" s="18" t="n"/>
       <c r="P4" s="18" t="n"/>
       <c r="Q4" s="18" t="n"/>
-      <c r="R4" s="12">
+      <c r="R4" s="11">
         <f>IF('01_Apprenants'!B4="","",SUM(E4:Q4))</f>
         <v/>
       </c>
@@ -13316,18 +13316,18 @@
       <c r="T4" s="15" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <f>IF('01_Apprenants'!B5="","",'01_Apprenants'!B5)</f>
         <v/>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <f>IF('01_Apprenants'!C5="","",'01_Apprenants'!C5)</f>
         <v/>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11">
         <f>IF('01_Apprenants'!D5="","",'01_Apprenants'!D5)</f>
         <v/>
       </c>
@@ -13344,7 +13344,7 @@
       <c r="O5" s="18" t="n"/>
       <c r="P5" s="18" t="n"/>
       <c r="Q5" s="18" t="n"/>
-      <c r="R5" s="12">
+      <c r="R5" s="11">
         <f>IF('01_Apprenants'!B5="","",SUM(E5:Q5))</f>
         <v/>
       </c>
@@ -13352,18 +13352,18 @@
       <c r="T5" s="15" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <f>IF('01_Apprenants'!B6="","",'01_Apprenants'!B6)</f>
         <v/>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <f>IF('01_Apprenants'!C6="","",'01_Apprenants'!C6)</f>
         <v/>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="11">
         <f>IF('01_Apprenants'!D6="","",'01_Apprenants'!D6)</f>
         <v/>
       </c>
@@ -13380,7 +13380,7 @@
       <c r="O6" s="18" t="n"/>
       <c r="P6" s="18" t="n"/>
       <c r="Q6" s="18" t="n"/>
-      <c r="R6" s="12">
+      <c r="R6" s="11">
         <f>IF('01_Apprenants'!B6="","",SUM(E6:Q6))</f>
         <v/>
       </c>
@@ -13388,18 +13388,18 @@
       <c r="T6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <f>IF('01_Apprenants'!B7="","",'01_Apprenants'!B7)</f>
         <v/>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <f>IF('01_Apprenants'!C7="","",'01_Apprenants'!C7)</f>
         <v/>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <f>IF('01_Apprenants'!D7="","",'01_Apprenants'!D7)</f>
         <v/>
       </c>
@@ -13416,7 +13416,7 @@
       <c r="O7" s="18" t="n"/>
       <c r="P7" s="18" t="n"/>
       <c r="Q7" s="18" t="n"/>
-      <c r="R7" s="12">
+      <c r="R7" s="11">
         <f>IF('01_Apprenants'!B7="","",SUM(E7:Q7))</f>
         <v/>
       </c>
@@ -13424,18 +13424,18 @@
       <c r="T7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <f>IF('01_Apprenants'!B8="","",'01_Apprenants'!B8)</f>
         <v/>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <f>IF('01_Apprenants'!C8="","",'01_Apprenants'!C8)</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <f>IF('01_Apprenants'!D8="","",'01_Apprenants'!D8)</f>
         <v/>
       </c>
@@ -13452,7 +13452,7 @@
       <c r="O8" s="18" t="n"/>
       <c r="P8" s="18" t="n"/>
       <c r="Q8" s="18" t="n"/>
-      <c r="R8" s="12">
+      <c r="R8" s="11">
         <f>IF('01_Apprenants'!B8="","",SUM(E8:Q8))</f>
         <v/>
       </c>
@@ -13460,18 +13460,18 @@
       <c r="T8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <f>IF('01_Apprenants'!B9="","",'01_Apprenants'!B9)</f>
         <v/>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="11">
         <f>IF('01_Apprenants'!C9="","",'01_Apprenants'!C9)</f>
         <v/>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11">
         <f>IF('01_Apprenants'!D9="","",'01_Apprenants'!D9)</f>
         <v/>
       </c>
@@ -13488,7 +13488,7 @@
       <c r="O9" s="18" t="n"/>
       <c r="P9" s="18" t="n"/>
       <c r="Q9" s="18" t="n"/>
-      <c r="R9" s="12">
+      <c r="R9" s="11">
         <f>IF('01_Apprenants'!B9="","",SUM(E9:Q9))</f>
         <v/>
       </c>
@@ -13496,18 +13496,18 @@
       <c r="T9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <f>IF('01_Apprenants'!B10="","",'01_Apprenants'!B10)</f>
         <v/>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="11">
         <f>IF('01_Apprenants'!C10="","",'01_Apprenants'!C10)</f>
         <v/>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <f>IF('01_Apprenants'!D10="","",'01_Apprenants'!D10)</f>
         <v/>
       </c>
@@ -13524,7 +13524,7 @@
       <c r="O10" s="18" t="n"/>
       <c r="P10" s="18" t="n"/>
       <c r="Q10" s="18" t="n"/>
-      <c r="R10" s="12">
+      <c r="R10" s="11">
         <f>IF('01_Apprenants'!B10="","",SUM(E10:Q10))</f>
         <v/>
       </c>
@@ -13532,18 +13532,18 @@
       <c r="T10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <f>IF('01_Apprenants'!B11="","",'01_Apprenants'!B11)</f>
         <v/>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="11">
         <f>IF('01_Apprenants'!C11="","",'01_Apprenants'!C11)</f>
         <v/>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <f>IF('01_Apprenants'!D11="","",'01_Apprenants'!D11)</f>
         <v/>
       </c>
@@ -13560,7 +13560,7 @@
       <c r="O11" s="18" t="n"/>
       <c r="P11" s="18" t="n"/>
       <c r="Q11" s="18" t="n"/>
-      <c r="R11" s="12">
+      <c r="R11" s="11">
         <f>IF('01_Apprenants'!B11="","",SUM(E11:Q11))</f>
         <v/>
       </c>
@@ -13568,18 +13568,18 @@
       <c r="T11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <f>IF('01_Apprenants'!B12="","",'01_Apprenants'!B12)</f>
         <v/>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="11">
         <f>IF('01_Apprenants'!C12="","",'01_Apprenants'!C12)</f>
         <v/>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <f>IF('01_Apprenants'!D12="","",'01_Apprenants'!D12)</f>
         <v/>
       </c>
@@ -13596,7 +13596,7 @@
       <c r="O12" s="18" t="n"/>
       <c r="P12" s="18" t="n"/>
       <c r="Q12" s="18" t="n"/>
-      <c r="R12" s="12">
+      <c r="R12" s="11">
         <f>IF('01_Apprenants'!B12="","",SUM(E12:Q12))</f>
         <v/>
       </c>
@@ -13604,18 +13604,18 @@
       <c r="T12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <f>IF('01_Apprenants'!B13="","",'01_Apprenants'!B13)</f>
         <v/>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <f>IF('01_Apprenants'!C13="","",'01_Apprenants'!C13)</f>
         <v/>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <f>IF('01_Apprenants'!D13="","",'01_Apprenants'!D13)</f>
         <v/>
       </c>
@@ -13632,7 +13632,7 @@
       <c r="O13" s="18" t="n"/>
       <c r="P13" s="18" t="n"/>
       <c r="Q13" s="18" t="n"/>
-      <c r="R13" s="12">
+      <c r="R13" s="11">
         <f>IF('01_Apprenants'!B13="","",SUM(E13:Q13))</f>
         <v/>
       </c>
@@ -13640,18 +13640,18 @@
       <c r="T13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <f>IF('01_Apprenants'!B14="","",'01_Apprenants'!B14)</f>
         <v/>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <f>IF('01_Apprenants'!C14="","",'01_Apprenants'!C14)</f>
         <v/>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="11">
         <f>IF('01_Apprenants'!D14="","",'01_Apprenants'!D14)</f>
         <v/>
       </c>
@@ -13668,7 +13668,7 @@
       <c r="O14" s="18" t="n"/>
       <c r="P14" s="18" t="n"/>
       <c r="Q14" s="18" t="n"/>
-      <c r="R14" s="12">
+      <c r="R14" s="11">
         <f>IF('01_Apprenants'!B14="","",SUM(E14:Q14))</f>
         <v/>
       </c>
@@ -13676,18 +13676,18 @@
       <c r="T14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <f>IF('01_Apprenants'!B15="","",'01_Apprenants'!B15)</f>
         <v/>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="11">
         <f>IF('01_Apprenants'!C15="","",'01_Apprenants'!C15)</f>
         <v/>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <f>IF('01_Apprenants'!D15="","",'01_Apprenants'!D15)</f>
         <v/>
       </c>
@@ -13704,7 +13704,7 @@
       <c r="O15" s="18" t="n"/>
       <c r="P15" s="18" t="n"/>
       <c r="Q15" s="18" t="n"/>
-      <c r="R15" s="12">
+      <c r="R15" s="11">
         <f>IF('01_Apprenants'!B15="","",SUM(E15:Q15))</f>
         <v/>
       </c>
@@ -13712,18 +13712,18 @@
       <c r="T15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <f>IF('01_Apprenants'!B16="","",'01_Apprenants'!B16)</f>
         <v/>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="11">
         <f>IF('01_Apprenants'!C16="","",'01_Apprenants'!C16)</f>
         <v/>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="11">
         <f>IF('01_Apprenants'!D16="","",'01_Apprenants'!D16)</f>
         <v/>
       </c>
@@ -13740,7 +13740,7 @@
       <c r="O16" s="18" t="n"/>
       <c r="P16" s="18" t="n"/>
       <c r="Q16" s="18" t="n"/>
-      <c r="R16" s="12">
+      <c r="R16" s="11">
         <f>IF('01_Apprenants'!B16="","",SUM(E16:Q16))</f>
         <v/>
       </c>
@@ -13748,18 +13748,18 @@
       <c r="T16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <f>IF('01_Apprenants'!B17="","",'01_Apprenants'!B17)</f>
         <v/>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <f>IF('01_Apprenants'!C17="","",'01_Apprenants'!C17)</f>
         <v/>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="11">
         <f>IF('01_Apprenants'!D17="","",'01_Apprenants'!D17)</f>
         <v/>
       </c>
@@ -13776,7 +13776,7 @@
       <c r="O17" s="18" t="n"/>
       <c r="P17" s="18" t="n"/>
       <c r="Q17" s="18" t="n"/>
-      <c r="R17" s="12">
+      <c r="R17" s="11">
         <f>IF('01_Apprenants'!B17="","",SUM(E17:Q17))</f>
         <v/>
       </c>
@@ -13784,18 +13784,18 @@
       <c r="T17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <f>IF('01_Apprenants'!B18="","",'01_Apprenants'!B18)</f>
         <v/>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="11">
         <f>IF('01_Apprenants'!C18="","",'01_Apprenants'!C18)</f>
         <v/>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="11">
         <f>IF('01_Apprenants'!D18="","",'01_Apprenants'!D18)</f>
         <v/>
       </c>
@@ -13812,7 +13812,7 @@
       <c r="O18" s="18" t="n"/>
       <c r="P18" s="18" t="n"/>
       <c r="Q18" s="18" t="n"/>
-      <c r="R18" s="12">
+      <c r="R18" s="11">
         <f>IF('01_Apprenants'!B18="","",SUM(E18:Q18))</f>
         <v/>
       </c>
@@ -13820,18 +13820,18 @@
       <c r="T18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="11">
         <f>IF('01_Apprenants'!B19="","",'01_Apprenants'!B19)</f>
         <v/>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="11">
         <f>IF('01_Apprenants'!C19="","",'01_Apprenants'!C19)</f>
         <v/>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="11">
         <f>IF('01_Apprenants'!D19="","",'01_Apprenants'!D19)</f>
         <v/>
       </c>
@@ -13848,7 +13848,7 @@
       <c r="O19" s="18" t="n"/>
       <c r="P19" s="18" t="n"/>
       <c r="Q19" s="18" t="n"/>
-      <c r="R19" s="12">
+      <c r="R19" s="11">
         <f>IF('01_Apprenants'!B19="","",SUM(E19:Q19))</f>
         <v/>
       </c>
@@ -13856,18 +13856,18 @@
       <c r="T19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="11">
         <f>IF('01_Apprenants'!B20="","",'01_Apprenants'!B20)</f>
         <v/>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="11">
         <f>IF('01_Apprenants'!C20="","",'01_Apprenants'!C20)</f>
         <v/>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="11">
         <f>IF('01_Apprenants'!D20="","",'01_Apprenants'!D20)</f>
         <v/>
       </c>
@@ -13884,7 +13884,7 @@
       <c r="O20" s="18" t="n"/>
       <c r="P20" s="18" t="n"/>
       <c r="Q20" s="18" t="n"/>
-      <c r="R20" s="12">
+      <c r="R20" s="11">
         <f>IF('01_Apprenants'!B20="","",SUM(E20:Q20))</f>
         <v/>
       </c>
@@ -13892,18 +13892,18 @@
       <c r="T20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="11">
         <f>IF('01_Apprenants'!B21="","",'01_Apprenants'!B21)</f>
         <v/>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="11">
         <f>IF('01_Apprenants'!C21="","",'01_Apprenants'!C21)</f>
         <v/>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="11">
         <f>IF('01_Apprenants'!D21="","",'01_Apprenants'!D21)</f>
         <v/>
       </c>
@@ -13920,7 +13920,7 @@
       <c r="O21" s="18" t="n"/>
       <c r="P21" s="18" t="n"/>
       <c r="Q21" s="18" t="n"/>
-      <c r="R21" s="12">
+      <c r="R21" s="11">
         <f>IF('01_Apprenants'!B21="","",SUM(E21:Q21))</f>
         <v/>
       </c>
@@ -13928,18 +13928,18 @@
       <c r="T21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="11">
         <f>IF('01_Apprenants'!B22="","",'01_Apprenants'!B22)</f>
         <v/>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="11">
         <f>IF('01_Apprenants'!C22="","",'01_Apprenants'!C22)</f>
         <v/>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="11">
         <f>IF('01_Apprenants'!D22="","",'01_Apprenants'!D22)</f>
         <v/>
       </c>
@@ -13956,7 +13956,7 @@
       <c r="O22" s="18" t="n"/>
       <c r="P22" s="18" t="n"/>
       <c r="Q22" s="18" t="n"/>
-      <c r="R22" s="12">
+      <c r="R22" s="11">
         <f>IF('01_Apprenants'!B22="","",SUM(E22:Q22))</f>
         <v/>
       </c>
@@ -13964,18 +13964,18 @@
       <c r="T22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="11">
         <f>IF('01_Apprenants'!B23="","",'01_Apprenants'!B23)</f>
         <v/>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="11">
         <f>IF('01_Apprenants'!C23="","",'01_Apprenants'!C23)</f>
         <v/>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="11">
         <f>IF('01_Apprenants'!D23="","",'01_Apprenants'!D23)</f>
         <v/>
       </c>
@@ -13992,7 +13992,7 @@
       <c r="O23" s="18" t="n"/>
       <c r="P23" s="18" t="n"/>
       <c r="Q23" s="18" t="n"/>
-      <c r="R23" s="12">
+      <c r="R23" s="11">
         <f>IF('01_Apprenants'!B23="","",SUM(E23:Q23))</f>
         <v/>
       </c>
@@ -14000,18 +14000,18 @@
       <c r="T23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="11">
         <f>IF('01_Apprenants'!B24="","",'01_Apprenants'!B24)</f>
         <v/>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="11">
         <f>IF('01_Apprenants'!C24="","",'01_Apprenants'!C24)</f>
         <v/>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="11">
         <f>IF('01_Apprenants'!D24="","",'01_Apprenants'!D24)</f>
         <v/>
       </c>
@@ -14028,7 +14028,7 @@
       <c r="O24" s="18" t="n"/>
       <c r="P24" s="18" t="n"/>
       <c r="Q24" s="18" t="n"/>
-      <c r="R24" s="12">
+      <c r="R24" s="11">
         <f>IF('01_Apprenants'!B24="","",SUM(E24:Q24))</f>
         <v/>
       </c>
@@ -14036,18 +14036,18 @@
       <c r="T24" s="15" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="n">
+      <c r="A25" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="11">
         <f>IF('01_Apprenants'!B25="","",'01_Apprenants'!B25)</f>
         <v/>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="11">
         <f>IF('01_Apprenants'!C25="","",'01_Apprenants'!C25)</f>
         <v/>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="11">
         <f>IF('01_Apprenants'!D25="","",'01_Apprenants'!D25)</f>
         <v/>
       </c>
@@ -14064,7 +14064,7 @@
       <c r="O25" s="18" t="n"/>
       <c r="P25" s="18" t="n"/>
       <c r="Q25" s="18" t="n"/>
-      <c r="R25" s="12">
+      <c r="R25" s="11">
         <f>IF('01_Apprenants'!B25="","",SUM(E25:Q25))</f>
         <v/>
       </c>
@@ -14072,18 +14072,18 @@
       <c r="T25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="11">
         <f>IF('01_Apprenants'!B26="","",'01_Apprenants'!B26)</f>
         <v/>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="11">
         <f>IF('01_Apprenants'!C26="","",'01_Apprenants'!C26)</f>
         <v/>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="11">
         <f>IF('01_Apprenants'!D26="","",'01_Apprenants'!D26)</f>
         <v/>
       </c>
@@ -14100,7 +14100,7 @@
       <c r="O26" s="18" t="n"/>
       <c r="P26" s="18" t="n"/>
       <c r="Q26" s="18" t="n"/>
-      <c r="R26" s="12">
+      <c r="R26" s="11">
         <f>IF('01_Apprenants'!B26="","",SUM(E26:Q26))</f>
         <v/>
       </c>
@@ -14108,18 +14108,18 @@
       <c r="T26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n">
+      <c r="A27" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="11">
         <f>IF('01_Apprenants'!B27="","",'01_Apprenants'!B27)</f>
         <v/>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="11">
         <f>IF('01_Apprenants'!C27="","",'01_Apprenants'!C27)</f>
         <v/>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="11">
         <f>IF('01_Apprenants'!D27="","",'01_Apprenants'!D27)</f>
         <v/>
       </c>
@@ -14136,7 +14136,7 @@
       <c r="O27" s="18" t="n"/>
       <c r="P27" s="18" t="n"/>
       <c r="Q27" s="18" t="n"/>
-      <c r="R27" s="12">
+      <c r="R27" s="11">
         <f>IF('01_Apprenants'!B27="","",SUM(E27:Q27))</f>
         <v/>
       </c>
@@ -14144,18 +14144,18 @@
       <c r="T27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n">
+      <c r="A28" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="11">
         <f>IF('01_Apprenants'!B28="","",'01_Apprenants'!B28)</f>
         <v/>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="11">
         <f>IF('01_Apprenants'!C28="","",'01_Apprenants'!C28)</f>
         <v/>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="11">
         <f>IF('01_Apprenants'!D28="","",'01_Apprenants'!D28)</f>
         <v/>
       </c>
@@ -14172,7 +14172,7 @@
       <c r="O28" s="18" t="n"/>
       <c r="P28" s="18" t="n"/>
       <c r="Q28" s="18" t="n"/>
-      <c r="R28" s="12">
+      <c r="R28" s="11">
         <f>IF('01_Apprenants'!B28="","",SUM(E28:Q28))</f>
         <v/>
       </c>
@@ -14180,18 +14180,18 @@
       <c r="T28" s="15" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n">
+      <c r="A29" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="11">
         <f>IF('01_Apprenants'!B29="","",'01_Apprenants'!B29)</f>
         <v/>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="11">
         <f>IF('01_Apprenants'!C29="","",'01_Apprenants'!C29)</f>
         <v/>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="11">
         <f>IF('01_Apprenants'!D29="","",'01_Apprenants'!D29)</f>
         <v/>
       </c>
@@ -14208,7 +14208,7 @@
       <c r="O29" s="18" t="n"/>
       <c r="P29" s="18" t="n"/>
       <c r="Q29" s="18" t="n"/>
-      <c r="R29" s="12">
+      <c r="R29" s="11">
         <f>IF('01_Apprenants'!B29="","",SUM(E29:Q29))</f>
         <v/>
       </c>
@@ -14216,18 +14216,18 @@
       <c r="T29" s="15" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n">
+      <c r="A30" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="11">
         <f>IF('01_Apprenants'!B30="","",'01_Apprenants'!B30)</f>
         <v/>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="11">
         <f>IF('01_Apprenants'!C30="","",'01_Apprenants'!C30)</f>
         <v/>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="11">
         <f>IF('01_Apprenants'!D30="","",'01_Apprenants'!D30)</f>
         <v/>
       </c>
@@ -14244,7 +14244,7 @@
       <c r="O30" s="18" t="n"/>
       <c r="P30" s="18" t="n"/>
       <c r="Q30" s="18" t="n"/>
-      <c r="R30" s="12">
+      <c r="R30" s="11">
         <f>IF('01_Apprenants'!B30="","",SUM(E30:Q30))</f>
         <v/>
       </c>
@@ -14252,18 +14252,18 @@
       <c r="T30" s="15" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n">
+      <c r="A31" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="11">
         <f>IF('01_Apprenants'!B31="","",'01_Apprenants'!B31)</f>
         <v/>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="11">
         <f>IF('01_Apprenants'!C31="","",'01_Apprenants'!C31)</f>
         <v/>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="11">
         <f>IF('01_Apprenants'!D31="","",'01_Apprenants'!D31)</f>
         <v/>
       </c>
@@ -14280,7 +14280,7 @@
       <c r="O31" s="18" t="n"/>
       <c r="P31" s="18" t="n"/>
       <c r="Q31" s="18" t="n"/>
-      <c r="R31" s="12">
+      <c r="R31" s="11">
         <f>IF('01_Apprenants'!B31="","",SUM(E31:Q31))</f>
         <v/>
       </c>
@@ -14288,18 +14288,18 @@
       <c r="T31" s="15" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n">
+      <c r="A32" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="11">
         <f>IF('01_Apprenants'!B32="","",'01_Apprenants'!B32)</f>
         <v/>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="11">
         <f>IF('01_Apprenants'!C32="","",'01_Apprenants'!C32)</f>
         <v/>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="11">
         <f>IF('01_Apprenants'!D32="","",'01_Apprenants'!D32)</f>
         <v/>
       </c>
@@ -14316,7 +14316,7 @@
       <c r="O32" s="18" t="n"/>
       <c r="P32" s="18" t="n"/>
       <c r="Q32" s="18" t="n"/>
-      <c r="R32" s="12">
+      <c r="R32" s="11">
         <f>IF('01_Apprenants'!B32="","",SUM(E32:Q32))</f>
         <v/>
       </c>
@@ -14324,18 +14324,18 @@
       <c r="T32" s="15" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n">
+      <c r="A33" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="11">
         <f>IF('01_Apprenants'!B33="","",'01_Apprenants'!B33)</f>
         <v/>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="11">
         <f>IF('01_Apprenants'!C33="","",'01_Apprenants'!C33)</f>
         <v/>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="11">
         <f>IF('01_Apprenants'!D33="","",'01_Apprenants'!D33)</f>
         <v/>
       </c>
@@ -14352,7 +14352,7 @@
       <c r="O33" s="18" t="n"/>
       <c r="P33" s="18" t="n"/>
       <c r="Q33" s="18" t="n"/>
-      <c r="R33" s="12">
+      <c r="R33" s="11">
         <f>IF('01_Apprenants'!B33="","",SUM(E33:Q33))</f>
         <v/>
       </c>
@@ -14509,18 +14509,18 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <f>IF('01_Apprenants'!B4="","",'01_Apprenants'!B4)</f>
         <v/>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <f>IF('01_Apprenants'!C4="","",'01_Apprenants'!C4)</f>
         <v/>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <f>IF('01_Apprenants'!D4="","",'01_Apprenants'!D4)</f>
         <v/>
       </c>
@@ -14536,7 +14536,7 @@
       <c r="N4" s="18" t="n"/>
       <c r="O4" s="18" t="n"/>
       <c r="P4" s="18" t="n"/>
-      <c r="Q4" s="12">
+      <c r="Q4" s="11">
         <f>IF('01_Apprenants'!B4="","",COUNTIF(E4:P4,"V"))</f>
         <v/>
       </c>
@@ -14546,18 +14546,18 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <f>IF('01_Apprenants'!B5="","",'01_Apprenants'!B5)</f>
         <v/>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <f>IF('01_Apprenants'!C5="","",'01_Apprenants'!C5)</f>
         <v/>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11">
         <f>IF('01_Apprenants'!D5="","",'01_Apprenants'!D5)</f>
         <v/>
       </c>
@@ -14573,7 +14573,7 @@
       <c r="N5" s="18" t="n"/>
       <c r="O5" s="18" t="n"/>
       <c r="P5" s="18" t="n"/>
-      <c r="Q5" s="12">
+      <c r="Q5" s="11">
         <f>IF('01_Apprenants'!B5="","",COUNTIF(E5:P5,"V"))</f>
         <v/>
       </c>
@@ -14583,18 +14583,18 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <f>IF('01_Apprenants'!B6="","",'01_Apprenants'!B6)</f>
         <v/>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <f>IF('01_Apprenants'!C6="","",'01_Apprenants'!C6)</f>
         <v/>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="11">
         <f>IF('01_Apprenants'!D6="","",'01_Apprenants'!D6)</f>
         <v/>
       </c>
@@ -14610,7 +14610,7 @@
       <c r="N6" s="18" t="n"/>
       <c r="O6" s="18" t="n"/>
       <c r="P6" s="18" t="n"/>
-      <c r="Q6" s="12">
+      <c r="Q6" s="11">
         <f>IF('01_Apprenants'!B6="","",COUNTIF(E6:P6,"V"))</f>
         <v/>
       </c>
@@ -14620,18 +14620,18 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <f>IF('01_Apprenants'!B7="","",'01_Apprenants'!B7)</f>
         <v/>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <f>IF('01_Apprenants'!C7="","",'01_Apprenants'!C7)</f>
         <v/>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <f>IF('01_Apprenants'!D7="","",'01_Apprenants'!D7)</f>
         <v/>
       </c>
@@ -14647,7 +14647,7 @@
       <c r="N7" s="18" t="n"/>
       <c r="O7" s="18" t="n"/>
       <c r="P7" s="18" t="n"/>
-      <c r="Q7" s="12">
+      <c r="Q7" s="11">
         <f>IF('01_Apprenants'!B7="","",COUNTIF(E7:P7,"V"))</f>
         <v/>
       </c>
@@ -14657,18 +14657,18 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <f>IF('01_Apprenants'!B8="","",'01_Apprenants'!B8)</f>
         <v/>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <f>IF('01_Apprenants'!C8="","",'01_Apprenants'!C8)</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <f>IF('01_Apprenants'!D8="","",'01_Apprenants'!D8)</f>
         <v/>
       </c>
@@ -14684,7 +14684,7 @@
       <c r="N8" s="18" t="n"/>
       <c r="O8" s="18" t="n"/>
       <c r="P8" s="18" t="n"/>
-      <c r="Q8" s="12">
+      <c r="Q8" s="11">
         <f>IF('01_Apprenants'!B8="","",COUNTIF(E8:P8,"V"))</f>
         <v/>
       </c>
@@ -14694,18 +14694,18 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <f>IF('01_Apprenants'!B9="","",'01_Apprenants'!B9)</f>
         <v/>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="11">
         <f>IF('01_Apprenants'!C9="","",'01_Apprenants'!C9)</f>
         <v/>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11">
         <f>IF('01_Apprenants'!D9="","",'01_Apprenants'!D9)</f>
         <v/>
       </c>
@@ -14721,7 +14721,7 @@
       <c r="N9" s="18" t="n"/>
       <c r="O9" s="18" t="n"/>
       <c r="P9" s="18" t="n"/>
-      <c r="Q9" s="12">
+      <c r="Q9" s="11">
         <f>IF('01_Apprenants'!B9="","",COUNTIF(E9:P9,"V"))</f>
         <v/>
       </c>
@@ -14731,18 +14731,18 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <f>IF('01_Apprenants'!B10="","",'01_Apprenants'!B10)</f>
         <v/>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="11">
         <f>IF('01_Apprenants'!C10="","",'01_Apprenants'!C10)</f>
         <v/>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <f>IF('01_Apprenants'!D10="","",'01_Apprenants'!D10)</f>
         <v/>
       </c>
@@ -14758,7 +14758,7 @@
       <c r="N10" s="18" t="n"/>
       <c r="O10" s="18" t="n"/>
       <c r="P10" s="18" t="n"/>
-      <c r="Q10" s="12">
+      <c r="Q10" s="11">
         <f>IF('01_Apprenants'!B10="","",COUNTIF(E10:P10,"V"))</f>
         <v/>
       </c>
@@ -14768,18 +14768,18 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <f>IF('01_Apprenants'!B11="","",'01_Apprenants'!B11)</f>
         <v/>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="11">
         <f>IF('01_Apprenants'!C11="","",'01_Apprenants'!C11)</f>
         <v/>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <f>IF('01_Apprenants'!D11="","",'01_Apprenants'!D11)</f>
         <v/>
       </c>
@@ -14795,7 +14795,7 @@
       <c r="N11" s="18" t="n"/>
       <c r="O11" s="18" t="n"/>
       <c r="P11" s="18" t="n"/>
-      <c r="Q11" s="12">
+      <c r="Q11" s="11">
         <f>IF('01_Apprenants'!B11="","",COUNTIF(E11:P11,"V"))</f>
         <v/>
       </c>
@@ -14805,18 +14805,18 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <f>IF('01_Apprenants'!B12="","",'01_Apprenants'!B12)</f>
         <v/>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="11">
         <f>IF('01_Apprenants'!C12="","",'01_Apprenants'!C12)</f>
         <v/>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <f>IF('01_Apprenants'!D12="","",'01_Apprenants'!D12)</f>
         <v/>
       </c>
@@ -14832,7 +14832,7 @@
       <c r="N12" s="18" t="n"/>
       <c r="O12" s="18" t="n"/>
       <c r="P12" s="18" t="n"/>
-      <c r="Q12" s="12">
+      <c r="Q12" s="11">
         <f>IF('01_Apprenants'!B12="","",COUNTIF(E12:P12,"V"))</f>
         <v/>
       </c>
@@ -14842,18 +14842,18 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <f>IF('01_Apprenants'!B13="","",'01_Apprenants'!B13)</f>
         <v/>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <f>IF('01_Apprenants'!C13="","",'01_Apprenants'!C13)</f>
         <v/>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <f>IF('01_Apprenants'!D13="","",'01_Apprenants'!D13)</f>
         <v/>
       </c>
@@ -14869,7 +14869,7 @@
       <c r="N13" s="18" t="n"/>
       <c r="O13" s="18" t="n"/>
       <c r="P13" s="18" t="n"/>
-      <c r="Q13" s="12">
+      <c r="Q13" s="11">
         <f>IF('01_Apprenants'!B13="","",COUNTIF(E13:P13,"V"))</f>
         <v/>
       </c>
@@ -14879,18 +14879,18 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <f>IF('01_Apprenants'!B14="","",'01_Apprenants'!B14)</f>
         <v/>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <f>IF('01_Apprenants'!C14="","",'01_Apprenants'!C14)</f>
         <v/>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="11">
         <f>IF('01_Apprenants'!D14="","",'01_Apprenants'!D14)</f>
         <v/>
       </c>
@@ -14906,7 +14906,7 @@
       <c r="N14" s="18" t="n"/>
       <c r="O14" s="18" t="n"/>
       <c r="P14" s="18" t="n"/>
-      <c r="Q14" s="12">
+      <c r="Q14" s="11">
         <f>IF('01_Apprenants'!B14="","",COUNTIF(E14:P14,"V"))</f>
         <v/>
       </c>
@@ -14916,18 +14916,18 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <f>IF('01_Apprenants'!B15="","",'01_Apprenants'!B15)</f>
         <v/>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="11">
         <f>IF('01_Apprenants'!C15="","",'01_Apprenants'!C15)</f>
         <v/>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <f>IF('01_Apprenants'!D15="","",'01_Apprenants'!D15)</f>
         <v/>
       </c>
@@ -14943,7 +14943,7 @@
       <c r="N15" s="18" t="n"/>
       <c r="O15" s="18" t="n"/>
       <c r="P15" s="18" t="n"/>
-      <c r="Q15" s="12">
+      <c r="Q15" s="11">
         <f>IF('01_Apprenants'!B15="","",COUNTIF(E15:P15,"V"))</f>
         <v/>
       </c>
@@ -14953,18 +14953,18 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <f>IF('01_Apprenants'!B16="","",'01_Apprenants'!B16)</f>
         <v/>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="11">
         <f>IF('01_Apprenants'!C16="","",'01_Apprenants'!C16)</f>
         <v/>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="11">
         <f>IF('01_Apprenants'!D16="","",'01_Apprenants'!D16)</f>
         <v/>
       </c>
@@ -14980,7 +14980,7 @@
       <c r="N16" s="18" t="n"/>
       <c r="O16" s="18" t="n"/>
       <c r="P16" s="18" t="n"/>
-      <c r="Q16" s="12">
+      <c r="Q16" s="11">
         <f>IF('01_Apprenants'!B16="","",COUNTIF(E16:P16,"V"))</f>
         <v/>
       </c>
@@ -14990,18 +14990,18 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <f>IF('01_Apprenants'!B17="","",'01_Apprenants'!B17)</f>
         <v/>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <f>IF('01_Apprenants'!C17="","",'01_Apprenants'!C17)</f>
         <v/>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="11">
         <f>IF('01_Apprenants'!D17="","",'01_Apprenants'!D17)</f>
         <v/>
       </c>
@@ -15017,7 +15017,7 @@
       <c r="N17" s="18" t="n"/>
       <c r="O17" s="18" t="n"/>
       <c r="P17" s="18" t="n"/>
-      <c r="Q17" s="12">
+      <c r="Q17" s="11">
         <f>IF('01_Apprenants'!B17="","",COUNTIF(E17:P17,"V"))</f>
         <v/>
       </c>
@@ -15027,18 +15027,18 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <f>IF('01_Apprenants'!B18="","",'01_Apprenants'!B18)</f>
         <v/>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="11">
         <f>IF('01_Apprenants'!C18="","",'01_Apprenants'!C18)</f>
         <v/>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="11">
         <f>IF('01_Apprenants'!D18="","",'01_Apprenants'!D18)</f>
         <v/>
       </c>
@@ -15054,7 +15054,7 @@
       <c r="N18" s="18" t="n"/>
       <c r="O18" s="18" t="n"/>
       <c r="P18" s="18" t="n"/>
-      <c r="Q18" s="12">
+      <c r="Q18" s="11">
         <f>IF('01_Apprenants'!B18="","",COUNTIF(E18:P18,"V"))</f>
         <v/>
       </c>
@@ -15064,18 +15064,18 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="11">
         <f>IF('01_Apprenants'!B19="","",'01_Apprenants'!B19)</f>
         <v/>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="11">
         <f>IF('01_Apprenants'!C19="","",'01_Apprenants'!C19)</f>
         <v/>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="11">
         <f>IF('01_Apprenants'!D19="","",'01_Apprenants'!D19)</f>
         <v/>
       </c>
@@ -15091,7 +15091,7 @@
       <c r="N19" s="18" t="n"/>
       <c r="O19" s="18" t="n"/>
       <c r="P19" s="18" t="n"/>
-      <c r="Q19" s="12">
+      <c r="Q19" s="11">
         <f>IF('01_Apprenants'!B19="","",COUNTIF(E19:P19,"V"))</f>
         <v/>
       </c>
@@ -15101,18 +15101,18 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="11">
         <f>IF('01_Apprenants'!B20="","",'01_Apprenants'!B20)</f>
         <v/>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="11">
         <f>IF('01_Apprenants'!C20="","",'01_Apprenants'!C20)</f>
         <v/>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="11">
         <f>IF('01_Apprenants'!D20="","",'01_Apprenants'!D20)</f>
         <v/>
       </c>
@@ -15128,7 +15128,7 @@
       <c r="N20" s="18" t="n"/>
       <c r="O20" s="18" t="n"/>
       <c r="P20" s="18" t="n"/>
-      <c r="Q20" s="12">
+      <c r="Q20" s="11">
         <f>IF('01_Apprenants'!B20="","",COUNTIF(E20:P20,"V"))</f>
         <v/>
       </c>
@@ -15138,18 +15138,18 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="11">
         <f>IF('01_Apprenants'!B21="","",'01_Apprenants'!B21)</f>
         <v/>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="11">
         <f>IF('01_Apprenants'!C21="","",'01_Apprenants'!C21)</f>
         <v/>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="11">
         <f>IF('01_Apprenants'!D21="","",'01_Apprenants'!D21)</f>
         <v/>
       </c>
@@ -15165,7 +15165,7 @@
       <c r="N21" s="18" t="n"/>
       <c r="O21" s="18" t="n"/>
       <c r="P21" s="18" t="n"/>
-      <c r="Q21" s="12">
+      <c r="Q21" s="11">
         <f>IF('01_Apprenants'!B21="","",COUNTIF(E21:P21,"V"))</f>
         <v/>
       </c>
@@ -15175,18 +15175,18 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="11">
         <f>IF('01_Apprenants'!B22="","",'01_Apprenants'!B22)</f>
         <v/>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="11">
         <f>IF('01_Apprenants'!C22="","",'01_Apprenants'!C22)</f>
         <v/>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="11">
         <f>IF('01_Apprenants'!D22="","",'01_Apprenants'!D22)</f>
         <v/>
       </c>
@@ -15202,7 +15202,7 @@
       <c r="N22" s="18" t="n"/>
       <c r="O22" s="18" t="n"/>
       <c r="P22" s="18" t="n"/>
-      <c r="Q22" s="12">
+      <c r="Q22" s="11">
         <f>IF('01_Apprenants'!B22="","",COUNTIF(E22:P22,"V"))</f>
         <v/>
       </c>
@@ -15212,18 +15212,18 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="11">
         <f>IF('01_Apprenants'!B23="","",'01_Apprenants'!B23)</f>
         <v/>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="11">
         <f>IF('01_Apprenants'!C23="","",'01_Apprenants'!C23)</f>
         <v/>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="11">
         <f>IF('01_Apprenants'!D23="","",'01_Apprenants'!D23)</f>
         <v/>
       </c>
@@ -15239,7 +15239,7 @@
       <c r="N23" s="18" t="n"/>
       <c r="O23" s="18" t="n"/>
       <c r="P23" s="18" t="n"/>
-      <c r="Q23" s="12">
+      <c r="Q23" s="11">
         <f>IF('01_Apprenants'!B23="","",COUNTIF(E23:P23,"V"))</f>
         <v/>
       </c>
@@ -15249,18 +15249,18 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="11">
         <f>IF('01_Apprenants'!B24="","",'01_Apprenants'!B24)</f>
         <v/>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="11">
         <f>IF('01_Apprenants'!C24="","",'01_Apprenants'!C24)</f>
         <v/>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="11">
         <f>IF('01_Apprenants'!D24="","",'01_Apprenants'!D24)</f>
         <v/>
       </c>
@@ -15276,7 +15276,7 @@
       <c r="N24" s="18" t="n"/>
       <c r="O24" s="18" t="n"/>
       <c r="P24" s="18" t="n"/>
-      <c r="Q24" s="12">
+      <c r="Q24" s="11">
         <f>IF('01_Apprenants'!B24="","",COUNTIF(E24:P24,"V"))</f>
         <v/>
       </c>
@@ -15286,18 +15286,18 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="n">
+      <c r="A25" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="11">
         <f>IF('01_Apprenants'!B25="","",'01_Apprenants'!B25)</f>
         <v/>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="11">
         <f>IF('01_Apprenants'!C25="","",'01_Apprenants'!C25)</f>
         <v/>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="11">
         <f>IF('01_Apprenants'!D25="","",'01_Apprenants'!D25)</f>
         <v/>
       </c>
@@ -15313,7 +15313,7 @@
       <c r="N25" s="18" t="n"/>
       <c r="O25" s="18" t="n"/>
       <c r="P25" s="18" t="n"/>
-      <c r="Q25" s="12">
+      <c r="Q25" s="11">
         <f>IF('01_Apprenants'!B25="","",COUNTIF(E25:P25,"V"))</f>
         <v/>
       </c>
@@ -15323,18 +15323,18 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="11">
         <f>IF('01_Apprenants'!B26="","",'01_Apprenants'!B26)</f>
         <v/>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="11">
         <f>IF('01_Apprenants'!C26="","",'01_Apprenants'!C26)</f>
         <v/>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="11">
         <f>IF('01_Apprenants'!D26="","",'01_Apprenants'!D26)</f>
         <v/>
       </c>
@@ -15350,7 +15350,7 @@
       <c r="N26" s="18" t="n"/>
       <c r="O26" s="18" t="n"/>
       <c r="P26" s="18" t="n"/>
-      <c r="Q26" s="12">
+      <c r="Q26" s="11">
         <f>IF('01_Apprenants'!B26="","",COUNTIF(E26:P26,"V"))</f>
         <v/>
       </c>
@@ -15360,18 +15360,18 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n">
+      <c r="A27" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="11">
         <f>IF('01_Apprenants'!B27="","",'01_Apprenants'!B27)</f>
         <v/>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="11">
         <f>IF('01_Apprenants'!C27="","",'01_Apprenants'!C27)</f>
         <v/>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="11">
         <f>IF('01_Apprenants'!D27="","",'01_Apprenants'!D27)</f>
         <v/>
       </c>
@@ -15387,7 +15387,7 @@
       <c r="N27" s="18" t="n"/>
       <c r="O27" s="18" t="n"/>
       <c r="P27" s="18" t="n"/>
-      <c r="Q27" s="12">
+      <c r="Q27" s="11">
         <f>IF('01_Apprenants'!B27="","",COUNTIF(E27:P27,"V"))</f>
         <v/>
       </c>
@@ -15397,18 +15397,18 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n">
+      <c r="A28" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="11">
         <f>IF('01_Apprenants'!B28="","",'01_Apprenants'!B28)</f>
         <v/>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="11">
         <f>IF('01_Apprenants'!C28="","",'01_Apprenants'!C28)</f>
         <v/>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="11">
         <f>IF('01_Apprenants'!D28="","",'01_Apprenants'!D28)</f>
         <v/>
       </c>
@@ -15424,7 +15424,7 @@
       <c r="N28" s="18" t="n"/>
       <c r="O28" s="18" t="n"/>
       <c r="P28" s="18" t="n"/>
-      <c r="Q28" s="12">
+      <c r="Q28" s="11">
         <f>IF('01_Apprenants'!B28="","",COUNTIF(E28:P28,"V"))</f>
         <v/>
       </c>
@@ -15434,18 +15434,18 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="n">
+      <c r="A29" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="11">
         <f>IF('01_Apprenants'!B29="","",'01_Apprenants'!B29)</f>
         <v/>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="11">
         <f>IF('01_Apprenants'!C29="","",'01_Apprenants'!C29)</f>
         <v/>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="11">
         <f>IF('01_Apprenants'!D29="","",'01_Apprenants'!D29)</f>
         <v/>
       </c>
@@ -15461,7 +15461,7 @@
       <c r="N29" s="18" t="n"/>
       <c r="O29" s="18" t="n"/>
       <c r="P29" s="18" t="n"/>
-      <c r="Q29" s="12">
+      <c r="Q29" s="11">
         <f>IF('01_Apprenants'!B29="","",COUNTIF(E29:P29,"V"))</f>
         <v/>
       </c>
@@ -15471,18 +15471,18 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n">
+      <c r="A30" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="11">
         <f>IF('01_Apprenants'!B30="","",'01_Apprenants'!B30)</f>
         <v/>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="11">
         <f>IF('01_Apprenants'!C30="","",'01_Apprenants'!C30)</f>
         <v/>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="11">
         <f>IF('01_Apprenants'!D30="","",'01_Apprenants'!D30)</f>
         <v/>
       </c>
@@ -15498,7 +15498,7 @@
       <c r="N30" s="18" t="n"/>
       <c r="O30" s="18" t="n"/>
       <c r="P30" s="18" t="n"/>
-      <c r="Q30" s="12">
+      <c r="Q30" s="11">
         <f>IF('01_Apprenants'!B30="","",COUNTIF(E30:P30,"V"))</f>
         <v/>
       </c>
@@ -15508,18 +15508,18 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n">
+      <c r="A31" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="11">
         <f>IF('01_Apprenants'!B31="","",'01_Apprenants'!B31)</f>
         <v/>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="11">
         <f>IF('01_Apprenants'!C31="","",'01_Apprenants'!C31)</f>
         <v/>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="11">
         <f>IF('01_Apprenants'!D31="","",'01_Apprenants'!D31)</f>
         <v/>
       </c>
@@ -15535,7 +15535,7 @@
       <c r="N31" s="18" t="n"/>
       <c r="O31" s="18" t="n"/>
       <c r="P31" s="18" t="n"/>
-      <c r="Q31" s="12">
+      <c r="Q31" s="11">
         <f>IF('01_Apprenants'!B31="","",COUNTIF(E31:P31,"V"))</f>
         <v/>
       </c>
@@ -15545,18 +15545,18 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n">
+      <c r="A32" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="11">
         <f>IF('01_Apprenants'!B32="","",'01_Apprenants'!B32)</f>
         <v/>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="11">
         <f>IF('01_Apprenants'!C32="","",'01_Apprenants'!C32)</f>
         <v/>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="11">
         <f>IF('01_Apprenants'!D32="","",'01_Apprenants'!D32)</f>
         <v/>
       </c>
@@ -15572,7 +15572,7 @@
       <c r="N32" s="18" t="n"/>
       <c r="O32" s="18" t="n"/>
       <c r="P32" s="18" t="n"/>
-      <c r="Q32" s="12">
+      <c r="Q32" s="11">
         <f>IF('01_Apprenants'!B32="","",COUNTIF(E32:P32,"V"))</f>
         <v/>
       </c>
@@ -15582,18 +15582,18 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n">
+      <c r="A33" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="11">
         <f>IF('01_Apprenants'!B33="","",'01_Apprenants'!B33)</f>
         <v/>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="11">
         <f>IF('01_Apprenants'!C33="","",'01_Apprenants'!C33)</f>
         <v/>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="11">
         <f>IF('01_Apprenants'!D33="","",'01_Apprenants'!D33)</f>
         <v/>
       </c>
@@ -15609,7 +15609,7 @@
       <c r="N33" s="18" t="n"/>
       <c r="O33" s="18" t="n"/>
       <c r="P33" s="18" t="n"/>
-      <c r="Q33" s="12">
+      <c r="Q33" s="11">
         <f>IF('01_Apprenants'!B33="","",COUNTIF(E33:P33,"V"))</f>
         <v/>
       </c>
